--- a/workspaces/btc_daily_14days/dxy/dxy_ret_1.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_1.xlsx
@@ -575,46 +575,46 @@
         <v>13</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.339592166363822</v>
+        <v>-6.320142085120281</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.951165779328079</v>
+        <v>-7.930974923507023</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-16.03834217823236</v>
+        <v>-15.99344933934758</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.90808904562486</v>
+        <v>-15.86319620674008</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.754202568387583</v>
+        <v>-8.72870282808735</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.7651120024545719</v>
+        <v>-0.761157617926564</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.8503632655460791</v>
+        <v>-0.8468334358208836</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6.384341695453145</v>
+        <v>6.367533580324448</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.081557589635743</v>
+        <v>-9.057797676182027</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.230099669250826</v>
+        <v>-2.224890582012662</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.267163408869479</v>
+        <v>5.252955075852512</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.401881302374811</v>
+        <v>-2.395857287715813</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.8244403774261</v>
+        <v>-2.816855808770178</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.575436198224246</v>
+        <v>-2.568398571269007</v>
       </c>
     </row>
     <row r="7">
@@ -627,46 +627,46 @@
         <v>18</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.062117235345582</v>
+        <v>3.055967635904466</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.21612304428408</v>
+        <v>-15.17564977556365</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.05543619532638</v>
+        <v>-10.02637168575011</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.29703915950333</v>
+        <v>12.26494158956981</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.908048722236757</v>
+        <v>-4.892772115478294</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.9450648197175013</v>
+        <v>0.9443685276319016</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.700065680386935</v>
+        <v>-4.685890144602453</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.169900669297654</v>
+        <v>-5.155147131848302</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.3329386056155741</v>
+        <v>0.331124931983716</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5183794186088946</v>
+        <v>-0.5178074138464055</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.85030881703737</v>
+        <v>-11.81760688627657</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-11.82093047150504</v>
+        <v>-11.7888968057148</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.679526041474716</v>
+        <v>-6.661223291344101</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.709471194217763</v>
+        <v>4.696558693686512</v>
       </c>
     </row>
     <row r="8">
@@ -679,46 +679,46 @@
         <v>18</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-13.60454943132108</v>
+        <v>-13.56454796026387</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.105011933175497</v>
+        <v>-4.094700379991359</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-15.61099175088193</v>
+        <v>-15.56602545792016</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-15.48073861827317</v>
+        <v>-15.43628153781567</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-16.01915983334534</v>
+        <v>-15.97279320600254</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.613059628854117</v>
+        <v>-4.598342562854739</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.700144433365161</v>
+        <v>-4.685732638649796</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.170023672390244</v>
+        <v>-5.1550241287595</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.230321452273003</v>
+        <v>-5.216726121238814</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.081659366360903</v>
+        <v>-6.065638577206776</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-6.287306280512077</v>
+        <v>-6.269498311692026</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6895804185660737</v>
+        <v>-0.6879051655169803</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.111347075964098</v>
+        <v>-1.108192417782085</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.8613294834676211</v>
+        <v>-0.8589968618677801</v>
       </c>
     </row>
     <row r="9">
@@ -731,46 +731,46 @@
         <v>27</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6415864683581276</v>
+        <v>-0.6371717474538912</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.253160081322385</v>
+        <v>-2.247835456111119</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.351732491623515</v>
+        <v>-6.331839768859609</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.185928048392235</v>
+        <v>1.18448375583958</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6475068333200653</v>
+        <v>0.6480123357133181</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-10.17127026104934</v>
+        <v>-10.14062273520811</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-10.26101048494863</v>
+        <v>-10.23066720214406</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-14.44247020533851</v>
+        <v>-14.40109611432639</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.084922577345544</v>
+        <v>-7.065828699870828</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.936286088434223</v>
+        <v>-7.914715558837159</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.141951863534523</v>
+        <v>-8.118556432372863</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.400259754558455</v>
+        <v>-4.388121053077811</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.536198303428215</v>
+        <v>-8.512111061177983</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.852762784937148</v>
+        <v>2.844706841832981</v>
       </c>
     </row>
     <row r="10">
@@ -783,46 +783,46 @@
         <v>32</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-11.86843832020998</v>
+        <v>-11.83186878254702</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.9800119331749428</v>
+        <v>-0.9781703017814252</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>-4.484713280995663</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.74462750716403</v>
+        <v>-13.70351444352465</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-17.40804872223691</v>
+        <v>-17.35601532732005</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-10.86618845039351</v>
+        <v>-10.83269845514647</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.828425248345404</v>
+        <v>-7.804171008686232</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.088363931106919</v>
+        <v>1.08658826774586</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.28716369649306</v>
+        <v>7.265788729996537</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.3063011086236</v>
+        <v>3.29640094780801</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.100609698001918</v>
+        <v>3.092585709795244</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.136997558431062</v>
+        <v>3.127972512650842</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4156024240028486</v>
+        <v>-0.4140080148406398</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1648800007475586</v>
+        <v>-0.1645524174238915</v>
       </c>
     </row>
     <row r="11">
@@ -835,46 +835,46 @@
         <v>33</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.082319255547603</v>
+        <v>5.070904481371691</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.56165473349312</v>
+        <v>12.52430298616199</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.106179966290476</v>
+        <v>6.091081390129808</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.236433098897287</v>
+        <v>6.220921034758952</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.698011883826496</v>
+        <v>5.684705088902852</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.997843761429166</v>
+        <v>5.983504122096761</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.217273964443294</v>
+        <v>-6.196928121944985</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.653328693265621</v>
+        <v>-3.641416077578562</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.782694176114795</v>
+        <v>-9.755262488306123</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.634201626676</v>
+        <v>-10.60400540780008</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.298882054767468</v>
+        <v>1.295828504544168</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.334460901672728</v>
+        <v>1.330377204666711</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.950963721622422</v>
+        <v>3.939951483307588</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.203833255857113</v>
+        <v>4.191508188636007</v>
       </c>
     </row>
     <row r="12">
@@ -887,46 +887,46 @@
         <v>57</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.892526592070332</v>
+        <v>1.890109049044106</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2809529791060754</v>
+        <v>0.2785354360798493</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.903628132159405</v>
+        <v>6.885477613201978</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.525109334941945</v>
+        <v>3.516985177813979</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.741074084781651</v>
+        <v>4.730024624806973</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2252365253441937</v>
+        <v>-0.2216686067130169</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.201669291590463</v>
+        <v>3.194850437758134</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.249520605336315</v>
+        <v>6.232449137376122</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.9184460675856769</v>
+        <v>0.9152081132884575</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.06687672453757898</v>
+        <v>0.06652708627991188</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1385986787894851</v>
+        <v>-0.1375041590273867</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.412076248782455</v>
+        <v>3.401617378000509</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.5254544887049946</v>
+        <v>-0.523616549268894</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.034304948193366</v>
+        <v>-2.028587505143896</v>
       </c>
     </row>
     <row r="13">
@@ -939,46 +939,46 @@
         <v>60</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-7.493438320209975</v>
+        <v>-7.467165163317873</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-7.438345266506808</v>
+        <v>-7.417192437316217</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.166547306437486</v>
+        <v>-1.160992017963402</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.702960840496658</v>
+        <v>-7.67707685903369</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.09195127776489187</v>
+        <v>0.0945228879513067</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3890774869008595</v>
+        <v>0.3909718583766875</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.701024259066365</v>
+        <v>-4.683972987242846</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.832558343742328</v>
+        <v>-1.825822790738229</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2235620569435071</v>
+        <v>-0.2234855165683243</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.93247425821999</v>
+        <v>3.920227798213098</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.726955530152161</v>
+        <v>3.716239877645371</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.24616954402557</v>
+        <v>-1.2429439361212</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.002120222664579785</v>
+        <v>0.002447455826249723</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.596687134743661</v>
+        <v>3.585447582575398</v>
       </c>
     </row>
     <row r="14">
@@ -991,46 +991,46 @@
         <v>78</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.916818090046576</v>
+        <v>3.908512130772721</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.023193195030458</v>
+        <v>1.018825949373145</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6283244884340107</v>
+        <v>0.6285450563967458</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.369627507163322</v>
+        <v>-4.35250513133132</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.625997440184506</v>
+        <v>-3.611339123590454</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.896349260372617</v>
+        <v>-5.874202097564464</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8511822392936779</v>
+        <v>-0.8451954883274198</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.171481822993059</v>
+        <v>-5.153565978154163</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.379260144415547</v>
+        <v>-1.375479736789167</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.367205842263616</v>
+        <v>-7.344194665406619</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.288675142912865</v>
+        <v>-6.268129449289965</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.257017623088728</v>
+        <v>-6.237519896589333</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.396912653254297</v>
+        <v>-5.379284430528735</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.434585707311342</v>
+        <v>-6.414552417424602</v>
       </c>
     </row>
     <row r="15">
@@ -1043,46 +1043,46 @@
         <v>76</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.453930100842804</v>
+        <v>1.453127315669732</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.157643512121453</v>
+        <v>-0.1584462972945246</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7632772549660274</v>
+        <v>0.7630666116263214</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.209319861257725</v>
+        <v>2.205965951190798</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.986688119869775</v>
+        <v>2.980546696271944</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.980858526845886</v>
+        <v>-1.969874388678903</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.836243479209017</v>
+        <v>5.820438904626982</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.689636132668646</v>
+        <v>6.669526592499921</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.947872801553999</v>
+        <v>7.920869098618532</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>8.413861134645558</v>
+        <v>8.386209342839393</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.254342722819345</v>
+        <v>4.241484263925642</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.291639947204146</v>
+        <v>4.277625002474316</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.552398549149245</v>
+        <v>2.545023369476397</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.445426697473387</v>
+        <v>5.427552845733295</v>
       </c>
     </row>
     <row r="16">
@@ -1095,46 +1095,46 @@
         <v>109</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.117291531219145</v>
+        <v>-1.109053597732256</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.775722011779898</v>
+        <v>2.764417032287177</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.5459909198623052</v>
+        <v>0.546528648707401</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.180831208433112</v>
+        <v>6.163010114078794</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.724978800700285</v>
+        <v>4.711993644882959</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.778457969248912</v>
+        <v>7.755996052140546</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.942474193061841</v>
+        <v>4.928112677307332</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.234920601121011</v>
+        <v>7.210673799566635</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.17540593599918</v>
+        <v>7.148188692323963</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.16142578591726</v>
+        <v>8.131643242991913</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.874546949598027</v>
+        <v>8.843877815997004</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.156080923592086</v>
+        <v>6.13391248144633</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.577595952665838</v>
+        <v>7.551572493312129</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.309741760418504</v>
+        <v>2.301043912850631</v>
       </c>
     </row>
     <row r="17">
@@ -1147,46 +1147,46 @@
         <v>123</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4609179950067173</v>
+        <v>-0.4539736420228451</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3665327822729196</v>
+        <v>0.3627787792539863</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.719392834892865</v>
+        <v>-5.694785510884444</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.963123442122765</v>
+        <v>-3.944742089755096</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.566585307601251</v>
+        <v>-8.530599928319326</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1398172980373147</v>
+        <v>-0.1352859242491178</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.21724625955536</v>
+        <v>2.211193292585925</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.506804914792546</v>
+        <v>-1.501169715622787</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7515316572015394</v>
+        <v>-0.7524264854160663</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.04740631022247</v>
+        <v>-4.03485098293843</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.067977968931785</v>
+        <v>-5.049802233027059</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.775754570317211</v>
+        <v>-1.770834349804787</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.830248625671743</v>
+        <v>-3.816444628165236</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.213862300535297</v>
+        <v>-5.195040222302652</v>
       </c>
     </row>
     <row r="18">
@@ -1199,46 +1199,46 @@
         <v>119</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.073270252983086</v>
+        <v>-2.058484292975862</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.525180000401122</v>
+        <v>-4.509291870847122</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1219680997249739</v>
+        <v>0.1264834394807295</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2522212323324737</v>
+        <v>0.2562077084750314</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.07514455507534</v>
+        <v>3.068904853286867</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8513811705887946</v>
+        <v>0.8525626836344173</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.133190101784571</v>
+        <v>4.118186526348467</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.984277651399594</v>
+        <v>1.976388833167185</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6008406530239512</v>
+        <v>-0.6025094414961814</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.453753473340711</v>
+        <v>-1.449846991235461</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.34426128600397</v>
+        <v>-3.330190365022482</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.153575717700065</v>
+        <v>-4.137980345082262</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.579446271335705</v>
+        <v>-4.560230842012636</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.644360462371928</v>
+        <v>-2.633039812382584</v>
       </c>
     </row>
     <row r="19">
@@ -1248,49 +1248,49 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.058285817721064</v>
+        <v>4.10090592395872</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.067401859929213</v>
+        <v>1.094497731078988</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.500119360229178</v>
+        <v>5.578956719983807</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.492441458353916</v>
+        <v>1.496179436618235</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.712640932936914</v>
+        <v>3.755207383984185</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.251532464550991</v>
+        <v>1.253251936838744</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2132388191471506</v>
+        <v>-0.2212747443850347</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.753779275707878</v>
+        <v>-3.822831950490631</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.706112727738571</v>
+        <v>1.757610550445122</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5176392169129542</v>
+        <v>-0.5192187946048037</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6642408351493501</v>
+        <v>0.6705052966776321</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.77487622149981</v>
+        <v>1.80971386393027</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3791500752437287</v>
+        <v>0.3780266611893239</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.313133488902075</v>
+        <v>1.331926455814838</v>
       </c>
     </row>
     <row r="20">
@@ -1303,46 +1303,46 @@
         <v>167</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.997579643861876</v>
+        <v>1.996359957695176</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2127963643118846</v>
+        <v>-0.2136507514376689</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6076650709086096</v>
+        <v>-0.6038579510029223</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.917797642537209</v>
+        <v>1.916090081903739</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4170307581636408</v>
+        <v>-0.4127782404239611</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4786227833040542</v>
+        <v>0.4803951576767176</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.404862622060755</v>
+        <v>-1.400459681178674</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.27242889486665</v>
+        <v>-4.260266014205534</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.531006515786025</v>
+        <v>-2.527866254576281</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3849572184036774</v>
+        <v>-0.3850607167374918</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.791054261182936</v>
+        <v>-1.785549367452944</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.555162055919759</v>
+        <v>-3.546531512509432</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.777025556986757</v>
+        <v>-5.760592456836534</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.929159431246831</v>
+        <v>-1.923534453352815</v>
       </c>
     </row>
     <row r="21">
@@ -1352,49 +1352,49 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.135822426170243</v>
+        <v>-6.170971624945381</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.098389416618019</v>
+        <v>-5.119258495458297</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8574965338104832</v>
+        <v>-0.8662952867048617</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.908518188200993</v>
+        <v>3.921149047256286</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.356851940016085</v>
+        <v>5.375004589172647</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.681223334090575</v>
+        <v>1.68322402383231</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2710668860220125</v>
+        <v>0.2699740190779707</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.119905225490932</v>
+        <v>3.129657169385283</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.399612280751228</v>
+        <v>2.416099963979015</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.546257590967883</v>
+        <v>1.555392768369003</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.338992429618379</v>
+        <v>1.342408991376594</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.04707454182213411</v>
+        <v>0.04639826277259118</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.614387620815613</v>
+        <v>1.615561641245691</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.073879041377225</v>
+        <v>-1.08121908409111</v>
       </c>
     </row>
     <row r="22">
@@ -1407,46 +1407,46 @@
         <v>155</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.861400389467441</v>
+        <v>6.851212593909956</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.137269997690368</v>
+        <v>-3.129449621704715</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3063322526740393</v>
+        <v>-0.3023707705904712</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.275533783159254</v>
+        <v>6.262236776564045</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.801628697119419</v>
+        <v>3.794463307215224</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.064926920351205</v>
+        <v>-1.059512455139995</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.435841437838945</v>
+        <v>1.433691756272403</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.619694903778957</v>
+        <v>-1.614136803799489</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.321762807566451</v>
+        <v>-2.320297980304332</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.529591359049597</v>
+        <v>-2.52526187500964</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7976258552163387</v>
+        <v>-0.7945313283594828</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1157858773800058</v>
+        <v>-0.1149868806915535</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1069933147836508</v>
+        <v>0.1099197986861711</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9347588692912225</v>
+        <v>-0.9306814496827371</v>
       </c>
     </row>
     <row r="23">
@@ -1459,46 +1459,46 @@
         <v>138</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.57902544790597</v>
+        <v>2.576900839898606</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.380374252014811</v>
+        <v>-3.368540034016853</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.471133852982845</v>
+        <v>3.465855135701048</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.920352144844486</v>
+        <v>-2.912701537388273</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5602226352789756</v>
+        <v>-0.5578154190806401</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.185893792785222</v>
+        <v>1.187095536725714</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.830599426794322</v>
+        <v>1.826398628642671</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.266867683827414</v>
+        <v>4.257765954498851</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.8735973007235245</v>
+        <v>-0.8756976997993462</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.002935536231099</v>
+        <v>-1.001185203667895</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.695412728753297</v>
+        <v>1.692612196652206</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.629232329262102</v>
+        <v>-2.620830732958851</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.600911710913465</v>
+        <v>-1.591809981584902</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.529304220267079</v>
+        <v>-3.516001692786922</v>
       </c>
     </row>
     <row r="24">
@@ -1511,46 +1511,46 @@
         <v>137</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.06130620533751596</v>
+        <v>0.06720172576828531</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.829294636168832</v>
+        <v>2.82461547069471</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.894279944170748</v>
+        <v>3.884860795474779</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.294606069479009</v>
+        <v>3.283651272650197</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.675892883603929</v>
+        <v>5.657020376228793</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.443565318423332</v>
+        <v>7.422812353413001</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.64214930453825</v>
+        <v>6.618528111346613</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.439254116451309</v>
+        <v>5.42141770526581</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.188415819660854</v>
+        <v>3.170636797185736</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.527604895019635</v>
+        <v>4.510292634055538</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.319182519151916</v>
+        <v>4.305539309737959</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.817651152007684</v>
+        <v>5.799776481681882</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9.053941178288731</v>
+        <v>9.029156907233464</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.374967409322728</v>
+        <v>6.359170210312627</v>
       </c>
     </row>
     <row r="25">
@@ -1563,46 +1563,46 @@
         <v>92</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7674312450073515</v>
+        <v>0.7731924762358346</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8441423679568345</v>
+        <v>-0.8352678722760132</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.108815012403092</v>
+        <v>3.098130085763621</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.54354055064158</v>
+        <v>-6.517416201106577</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5602226352789756</v>
+        <v>-0.5614916289415319</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.44253731932271</v>
+        <v>-2.430850162760329</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.800741767495566</v>
+        <v>-5.782297023531271</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.090072468748147</v>
+        <v>-4.075567378834478</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8.508346789696688</v>
+        <v>-8.484393351973367</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-7.185326396321109</v>
+        <v>-7.160605493522908</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.303899191364053</v>
+        <v>-6.278402296101298</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.177843865764345</v>
+        <v>-5.157062617016798</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.1452292744176944</v>
+        <v>-0.142534619266236</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1037075380044072</v>
+        <v>0.1071867130101793</v>
       </c>
     </row>
     <row r="26">
@@ -1615,46 +1615,46 @@
         <v>84</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>10.60179977502812</v>
+        <v>10.55834000265795</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.990226162063891</v>
+        <v>8.951325391728204</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.452500312610134</v>
+        <v>1.445593967266269</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.773229635693781</v>
+        <v>2.762320595111319</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.044332230145464</v>
+        <v>1.034006633275709</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.924082512074193</v>
+        <v>4.90232296650516</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.07053714911804576</v>
+        <v>0.06656426011261374</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4024000889126214</v>
+        <v>-0.4006191386688442</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.044568974395489</v>
+        <v>-4.033047596279722</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.513769177705541</v>
+        <v>-2.50222040035527</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.3318436810560499</v>
+        <v>-0.3260213437205337</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.689893183926934</v>
+        <v>-2.672590567327418</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.871509239594026</v>
+        <v>2.8595357741087</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.923288089987281</v>
+        <v>1.918780915908734</v>
       </c>
     </row>
     <row r="27">
@@ -1667,46 +1667,46 @@
         <v>77</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.142788969560627</v>
+        <v>-3.118393926905597</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8582586864210242</v>
+        <v>-0.8526761929390503</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.642976503086359</v>
+        <v>2.624504349857332</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.370632233096494</v>
+        <v>5.336706104008812</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-5.557399371586143</v>
+        <v>-5.529509597239169</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.2380234827151</v>
+        <v>1.22907463655693</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1452239516755185</v>
+        <v>-0.1498859563375703</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.850686312873954</v>
+        <v>-5.811874549924262</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.288125851357961</v>
+        <v>-3.275471838703972</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2320882336713765</v>
+        <v>-0.2294931276279968</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.170803670345983</v>
+        <v>2.163156145457066</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.4113001336231719</v>
+        <v>-0.3998632946001024</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.788468909938288</v>
+        <v>1.777284691857552</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5800650656958339</v>
+        <v>-0.5703965732687593</v>
       </c>
     </row>
     <row r="28">
@@ -1719,46 +1719,46 @@
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>12.2124440327312</v>
+        <v>12.12071435393493</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.60087041976697</v>
+        <v>10.51197087625113</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.499880639770907</v>
+        <v>-4.468749151685699</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.899039271869242</v>
+        <v>-2.883307049280781</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4962840163531794</v>
+        <v>-0.4943695130751351</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.151530290362956</v>
+        <v>-3.128506808088488</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.210215417275556</v>
+        <v>-6.165928737086226</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7701980046980381</v>
+        <v>-0.7507591946912626</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8110829483515616</v>
+        <v>-0.8117590808735642</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.288081927472454</v>
+        <v>1.27929220468679</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.88894996344429</v>
+        <v>-1.866637590219106</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.103343944408252</v>
+        <v>1.108922037714564</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.269074290606909</v>
+        <v>-2.252509043818577</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.385481389201416</v>
+        <v>5.350153464928297</v>
       </c>
     </row>
     <row r="29">
@@ -1768,49 +1768,49 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.730442276804951</v>
+        <v>2.770082811574625</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.358743276457837</v>
+        <v>-3.363604305539091</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.21653727067698</v>
+        <v>2.234823999125418</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.8542530898516034</v>
+        <v>0.8667528789176728</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.669242752086198</v>
+        <v>-2.69158033810244</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.892632202185595</v>
+        <v>-6.9581162135743</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-6.150362855747296</v>
+        <v>-6.210492016943604</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.912530821660653</v>
+        <v>3.928385190335462</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.8213453449432819</v>
+        <v>0.8370822738501431</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.01327779071372959</v>
+        <v>-0.01304291117781986</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.800527938475582</v>
+        <v>2.812506794807675</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.337258106095803</v>
+        <v>1.33173843700159</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.9053769581226589</v>
+        <v>0.9114838260567097</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3503057240117116</v>
+        <v>-0.3539463568185255</v>
       </c>
     </row>
     <row r="30">
@@ -1823,46 +1823,46 @@
         <v>37</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.263318436546783</v>
+        <v>4.204434126165452</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.753660581822842</v>
+        <v>-2.752540161540743</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.662281522391382</v>
+        <v>7.598666548596768</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.089831952296173</v>
+        <v>5.042400827020721</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.956816142629378</v>
+        <v>9.886229664857254</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>15.7560894157432</v>
+        <v>15.6596634857504</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.500394039137149</v>
+        <v>7.466821660370016</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.595242551785205</v>
+        <v>1.59423285618319</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.889715896489598</v>
+        <v>-3.872172435404565</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.034866563710359</v>
+        <v>-2.019594917729783</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4746943140980449</v>
+        <v>0.4783544606553392</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.4997377871247508</v>
+        <v>0.5127376180007346</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.09349270265792597</v>
+        <v>0.09248300705591106</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3432140349342134</v>
+        <v>0.3422043393321985</v>
       </c>
     </row>
     <row r="31">
@@ -1875,46 +1875,46 @@
         <v>29</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.217576251244459</v>
+        <v>-4.230970163579997</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.380874002139798</v>
+        <v>-2.382712382264252</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.224018570805356</v>
+        <v>-6.191715605760805</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-9.542041300266845</v>
+        <v>-9.475596990053283</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.183910791201036</v>
+        <v>-3.17051687886547</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.394621753779454</v>
+        <v>-6.334744715554336</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-3.019852664315472</v>
+        <v>-2.971202570757605</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-10.45255330447632</v>
+        <v>-10.33493769367706</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-10.49029737670513</v>
+        <v>-10.39593757985934</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-11.36367837568655</v>
+        <v>-11.24606276488728</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.610666396609275</v>
+        <v>-4.554264365066935</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.373730126146462</v>
+        <v>2.376670516416475</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.506027291534608</v>
+        <v>-1.491859956597416</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.739064579947964</v>
+        <v>-4.690414486390097</v>
       </c>
     </row>
     <row r="32">
@@ -1924,49 +1924,49 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.038892865664522</v>
+        <v>-7.090326580464556</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>4.985897157734861</v>
+        <v>5.348076232785232</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.591028451138271</v>
+        <v>4.90605995428858</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.369627507163287</v>
+        <v>-4.534644008813459</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-4.908048722235456</v>
+        <v>-5.073065223885628</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.025756851843845</v>
+        <v>7.29415512024211</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.031932225480574</v>
+        <v>7.209421402969767</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.20111246306276</v>
+        <v>11.50414276609305</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.00374894051679</v>
+        <v>11.44314287991072</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.199078300943434</v>
+        <v>1.069208171073299</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.9488704311713221</v>
+        <v>0.86445484675572</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.983253588516753</v>
+        <v>0.898838004101151</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4720898866627152</v>
+        <v>0.4785833931562138</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7672657643935423</v>
+        <v>0.7283047254325012</v>
       </c>
     </row>
     <row r="33">
@@ -2213,10 +2213,8 @@
           <t>X &gt; -0.009573</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2205~2211</t>
-        </is>
+      <c r="B6" t="n">
+        <v>2205</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>0.7856209289985259</v>
@@ -2267,10 +2265,8 @@
           <t>X &gt; -0.00893</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2192~2198</t>
-        </is>
+      <c r="B7" t="n">
+        <v>2192</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.8277627716917522</v>
@@ -2321,10 +2317,8 @@
           <t>X &gt; -0.008287</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2174~2180</t>
-        </is>
+      <c r="B8" t="n">
+        <v>2174</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.8093139733680061</v>
@@ -2375,10 +2369,8 @@
           <t>X &gt; -0.007644</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2156~2162</t>
-        </is>
+      <c r="B9" t="n">
+        <v>2156</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>0.9293183865430308</v>
@@ -2429,10 +2421,8 @@
           <t>X &gt; -0.007001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2129~2135</t>
-        </is>
+      <c r="B10" t="n">
+        <v>2129</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>0.9491846306097003</v>
@@ -2483,10 +2473,8 @@
           <t>X &gt; -0.006358</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2097~2103</t>
-        </is>
+      <c r="B11" t="n">
+        <v>2097</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>1.144222164811424</v>
@@ -2537,10 +2525,8 @@
           <t>X &gt; -0.005715</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2064~2070</t>
-        </is>
+      <c r="B12" t="n">
+        <v>2064</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>1.081440906843163</v>
@@ -2591,10 +2577,8 @@
           <t>X &gt; -0.005072</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2007~2013</t>
-        </is>
+      <c r="B13" t="n">
+        <v>2007</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>1.05847424809604</v>
@@ -2645,10 +2629,8 @@
           <t>X &gt; -0.004429</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1947~1953</t>
-        </is>
+      <c r="B14" t="n">
+        <v>1947</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>1.321205817014814</v>
@@ -2699,10 +2681,8 @@
           <t>X &gt; -0.003786</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1869~1875</t>
-        </is>
+      <c r="B15" t="n">
+        <v>1869</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>1.213228346456695</v>
@@ -2753,10 +2733,8 @@
           <t>X &gt; -0.003143</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1793~1799</t>
-        </is>
+      <c r="B16" t="n">
+        <v>1793</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>1.203059734264734</v>
@@ -2807,10 +2785,8 @@
           <t>X &gt; -0.0025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1684~1690</t>
-        </is>
+      <c r="B17" t="n">
+        <v>1684</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>1.352715525943871</v>
@@ -2861,10 +2837,8 @@
           <t>X &gt; -0.001857</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1561~1567</t>
-        </is>
+      <c r="B18" t="n">
+        <v>1561</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>1.495074762112935</v>
@@ -2915,10 +2889,8 @@
           <t>X &gt; -0.001214</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1442~1448</t>
-        </is>
+      <c r="B19" t="n">
+        <v>1442</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>1.788329635591133</v>
@@ -2969,10 +2941,8 @@
           <t>X &gt; -0.0005706</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1300~1303</t>
-        </is>
+      <c r="B20" t="n">
+        <v>1300</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>1.535725148707911</v>
@@ -3023,10 +2993,8 @@
           <t>X &gt; 7.239e-05</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1133~1136</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1133</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>1.467829285423825</v>
@@ -3077,10 +3045,8 @@
           <t>X &gt; 0.0007154</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>983~985</t>
-        </is>
+      <c r="B22" t="n">
+        <v>983</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>2.633465233089517</v>
@@ -3131,10 +3097,8 @@
           <t>X &gt; 0.001358</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>828~830</t>
-        </is>
+      <c r="B23" t="n">
+        <v>828</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>1.843911077380383</v>
@@ -3185,10 +3149,8 @@
           <t>X &gt; 0.002001</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>690~692</t>
-        </is>
+      <c r="B24" t="n">
+        <v>690</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>1.697313124876729</v>
@@ -3239,10 +3201,8 @@
           <t>X &gt; 0.002644</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>553~555</t>
-        </is>
+      <c r="B25" t="n">
+        <v>553</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>2.101156274384614</v>
@@ -3293,10 +3253,8 @@
           <t>X &gt; 0.003287</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>461~463</t>
-        </is>
+      <c r="B26" t="n">
+        <v>461</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>2.366172910891535</v>
@@ -3347,10 +3305,8 @@
           <t>X &gt; 0.00393</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>377~379</t>
-        </is>
+      <c r="B27" t="n">
+        <v>377</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.540862471346756</v>
@@ -3401,10 +3357,8 @@
           <t>X &gt; 0.004573</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>300~302</t>
-        </is>
+      <c r="B28" t="n">
+        <v>300</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>1.48007161356486</v>
@@ -3455,10 +3409,8 @@
           <t>X &gt; 0.005217</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>232~234</t>
-        </is>
+      <c r="B29" t="n">
+        <v>232</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>-1.638737465509124</v>
@@ -3509,10 +3461,8 @@
           <t>X &gt; 0.00586</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>166~167</t>
-        </is>
+      <c r="B30" t="n">
+        <v>166</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>-3.391641913024351</v>
@@ -3563,10 +3513,8 @@
           <t>X &gt; 0.006503</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>129~130</t>
-        </is>
+      <c r="B31" t="n">
+        <v>129</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>-5.570361397133055</v>
@@ -3617,10 +3565,8 @@
           <t>X &gt; 0.007146</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>100~101</t>
-        </is>
+      <c r="B32" t="n">
+        <v>100</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>-5.958784854863438</v>
@@ -3671,10 +3617,8 @@
           <t>X &gt; 0.007789</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>79~79</t>
-        </is>
+      <c r="B33" t="n">
+        <v>79</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>-5.657995282235291</v>
@@ -3725,10 +3669,8 @@
           <t>X &gt; 0.008432</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>63~63</t>
-        </is>
+      <c r="B34" t="n">
+        <v>63</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>-9.636295463067121</v>
@@ -3779,10 +3721,8 @@
           <t>X &gt; 0.009075</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>46~46</t>
-        </is>
+      <c r="B35" t="n">
+        <v>46</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>-9.015177450644757</v>
@@ -3967,10 +3907,8 @@
           <t>X &lt; -0.009573</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>46~46</t>
-        </is>
+      <c r="B6" t="n">
+        <v>46</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>1.854387766746541</v>
@@ -4021,10 +3959,8 @@
           <t>X &lt; -0.00893</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>59~59</t>
-        </is>
+      <c r="B7" t="n">
+        <v>59</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>0.04893456114596262</v>
@@ -4075,10 +4011,8 @@
           <t>X &lt; -0.008287</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>77~77</t>
-        </is>
+      <c r="B8" t="n">
+        <v>77</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>0.7533149265432684</v>
@@ -4129,10 +4063,8 @@
           <t>X &lt; -0.007644</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>95~95</t>
-        </is>
+      <c r="B9" t="n">
+        <v>95</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>-1.96712253073629</v>
@@ -4183,10 +4115,8 @@
           <t>X &lt; -0.007001</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>122~122</t>
-        </is>
+      <c r="B10" t="n">
+        <v>122</v>
       </c>
       <c r="C10" s="4" t="n">
         <v>-1.673766189062434</v>
@@ -4237,10 +4167,8 @@
           <t>X &lt; -0.006358</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>154~154</t>
-        </is>
+      <c r="B11" t="n">
+        <v>154</v>
       </c>
       <c r="C11" s="4" t="n">
         <v>-3.792139618911271</v>
@@ -4291,10 +4219,8 @@
           <t>X &lt; -0.005715</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>187~187</t>
-        </is>
+      <c r="B12" t="n">
+        <v>187</v>
       </c>
       <c r="C12" s="4" t="n">
         <v>-2.226058641065592</v>
@@ -4345,10 +4271,8 @@
           <t>X &lt; -0.005072</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>244~244</t>
-        </is>
+      <c r="B13" t="n">
+        <v>244</v>
       </c>
       <c r="C13" s="4" t="n">
         <v>-1.26393012348867</v>
@@ -4399,10 +4323,8 @@
           <t>X &lt; -0.004429</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>304~304</t>
-        </is>
+      <c r="B14" t="n">
+        <v>304</v>
       </c>
       <c r="C14" s="4" t="n">
         <v>-2.493438320209975</v>
@@ -4453,10 +4375,8 @@
           <t>X &lt; -0.003786</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>382~382</t>
-        </is>
+      <c r="B15" t="n">
+        <v>382</v>
       </c>
       <c r="C15" s="4" t="n">
         <v>-1.184537796649764</v>
@@ -4507,10 +4427,8 @@
           <t>X &lt; -0.003143</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>458~458</t>
-        </is>
+      <c r="B16" t="n">
+        <v>458</v>
       </c>
       <c r="C16" s="4" t="n">
         <v>-0.7467134293802786</v>
@@ -4561,10 +4479,8 @@
           <t>X &lt; -0.0025</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>567~567</t>
-        </is>
+      <c r="B17" t="n">
+        <v>567</v>
       </c>
       <c r="C17" s="4" t="n">
         <v>-0.8179533113916335</v>
@@ -4615,10 +4531,8 @@
           <t>X &lt; -0.001857</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>690~690</t>
-        </is>
+      <c r="B18" t="n">
+        <v>690</v>
       </c>
       <c r="C18" s="4" t="n">
         <v>-0.7543078854273659</v>
@@ -4669,10 +4583,8 @@
           <t>X &lt; -0.001214</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>809~809</t>
-        </is>
+      <c r="B19" t="n">
+        <v>809</v>
       </c>
       <c r="C19" s="4" t="n">
         <v>-0.9483208912853698</v>
@@ -4723,10 +4635,8 @@
           <t>X &lt; -0.0005706</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>951~954</t>
-        </is>
+      <c r="B20" t="n">
+        <v>951</v>
       </c>
       <c r="C20" s="4" t="n">
         <v>-0.1873586556397484</v>
@@ -4777,10 +4687,8 @@
           <t>X &lt; 7.239e-05</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1118~1121</t>
-        </is>
+      <c r="B21" t="n">
+        <v>1118</v>
       </c>
       <c r="C21" s="4" t="n">
         <v>0.1381406271584424</v>
@@ -4831,10 +4739,8 @@
           <t>X &lt; 0.0007154</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1268~1272</t>
-        </is>
+      <c r="B22" t="n">
+        <v>1268</v>
       </c>
       <c r="C22" s="4" t="n">
         <v>-0.6066458673797896</v>
@@ -4885,10 +4791,8 @@
           <t>X &lt; 0.001358</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1423~1427</t>
-        </is>
+      <c r="B23" t="n">
+        <v>1423</v>
       </c>
       <c r="C23" s="4" t="n">
         <v>0.2045294443310226</v>
@@ -4939,10 +4843,8 @@
           <t>X &lt; 0.002001</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>1561~1565</t>
-        </is>
+      <c r="B24" t="n">
+        <v>1561</v>
       </c>
       <c r="C24" s="4" t="n">
         <v>0.4139099226015261</v>
@@ -4993,10 +4895,8 @@
           <t>X &lt; 0.002644</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>1698~1702</t>
-        </is>
+      <c r="B25" t="n">
+        <v>1698</v>
       </c>
       <c r="C25" s="4" t="n">
         <v>0.3855276022342125</v>
@@ -5047,10 +4947,8 @@
           <t>X &lt; 0.003287</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>1790~1794</t>
-        </is>
+      <c r="B26" t="n">
+        <v>1790</v>
       </c>
       <c r="C26" s="4" t="n">
         <v>0.4051124044277046</v>
@@ -5101,10 +4999,8 @@
           <t>X &lt; 0.00393</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>1874~1878</t>
-        </is>
+      <c r="B27" t="n">
+        <v>1874</v>
       </c>
       <c r="C27" s="4" t="n">
         <v>0.8611942676494522</v>
@@ -5155,10 +5051,8 @@
           <t>X &lt; 0.004573</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>1951~1955</t>
-        </is>
+      <c r="B28" t="n">
+        <v>1951</v>
       </c>
       <c r="C28" s="4" t="n">
         <v>0.7034926260815908</v>
@@ -5209,10 +5103,8 @@
           <t>X &lt; 0.005217</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2019~2023</t>
-        </is>
+      <c r="B29" t="n">
+        <v>2019</v>
       </c>
       <c r="C29" s="4" t="n">
         <v>1.090348135548801</v>
@@ -5263,10 +5155,8 @@
           <t>X &lt; 0.00586</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2085~2090</t>
-        </is>
+      <c r="B30" t="n">
+        <v>2085</v>
       </c>
       <c r="C30" s="4" t="n">
         <v>1.142925316153665</v>
@@ -5317,10 +5207,8 @@
           <t>X &lt; 0.006503</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2122~2127</t>
-        </is>
+      <c r="B31" t="n">
+        <v>2122</v>
       </c>
       <c r="C31" s="4" t="n">
         <v>1.19720577946093</v>
@@ -5371,10 +5259,8 @@
           <t>X &lt; 0.007146</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2151~2156</t>
-        </is>
+      <c r="B32" t="n">
+        <v>2151</v>
       </c>
       <c r="C32" s="4" t="n">
         <v>1.124372440457932</v>
@@ -5425,10 +5311,8 @@
           <t>X &lt; 0.007789</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2172~2178</t>
-        </is>
+      <c r="B33" t="n">
+        <v>2172</v>
       </c>
       <c r="C33" s="4" t="n">
         <v>1.041915215143561</v>
@@ -5479,10 +5363,8 @@
           <t>X &lt; 0.008432</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2188~2194</t>
-        </is>
+      <c r="B34" t="n">
+        <v>2188</v>
       </c>
       <c r="C34" s="4" t="n">
         <v>1.107290941412629</v>
@@ -5533,10 +5415,8 @@
           <t>X &lt; 0.009075</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2205~2211</t>
-        </is>
+      <c r="B35" t="n">
+        <v>2205</v>
       </c>
       <c r="C35" s="4" t="n">
         <v>1.011762946185321</v>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_1.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_1.xlsx
@@ -479,7 +479,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-1 is approximately at value x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-1 is approximately at value x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -568,1509 +568,1509 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.009251</t>
+          <t>X ≈ -0.008186</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-6.320142085120281</v>
+        <v>-10.34279440362248</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-7.930974923507023</v>
+        <v>-6.703325084065966</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-15.99344933934758</v>
+        <v>-12.34781939271741</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.86319620674008</v>
+        <v>-1.720442818013666</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-8.72870282808735</v>
+        <v>-12.7609880793614</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-0.761157617926564</v>
+        <v>-12.46753349365233</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-0.8468334358208836</v>
+        <v>-17.80944172481885</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>6.367533580324448</v>
+        <v>-13.02488189233319</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-9.057797676182027</v>
+        <v>-7.832247166736138</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-2.224890582012662</v>
+        <v>-3.425248858529784</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>5.252955075852512</v>
+        <v>-8.889970606853289</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-2.395857287715813</v>
+        <v>1.66342960911642</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-2.816855808770178</v>
+        <v>6.505620458345774</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-2.568398571269007</v>
+        <v>11.9960705784538</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.008608</t>
+          <t>X ≈ -0.007607</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.055967635904466</v>
+        <v>3.507829733827386</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-15.17564977556365</v>
+        <v>-10.06157211156921</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.02637168575011</v>
+        <v>-10.457849866651</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>12.26494158956981</v>
+        <v>-2.35041561612185</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-4.892772115478294</v>
+        <v>-2.887885149931499</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.9443685276319016</v>
+        <v>-10.57626427203917</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-4.685890144602453</v>
+        <v>-6.67047037646914</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-5.155147131848302</v>
+        <v>-15.12682167564004</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.331124931983716</v>
+        <v>-15.19147556872295</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.5178074138464055</v>
+        <v>-8.052219707831654</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-11.81760688627657</v>
+        <v>-12.25582660266288</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-11.7888968057148</v>
+        <v>-12.22445537003126</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-6.661223291344101</v>
+        <v>-16.64657319073943</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>4.696558693686512</v>
+        <v>-12.42498205312457</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.007966</t>
+          <t>X ≈ -0.007029</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-13.56454796026387</v>
+        <v>0.1501145601323159</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-4.094700379991359</v>
+        <v>9.039655624010116</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-15.56602545792016</v>
+        <v>-4.473804991109645</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-15.43628153781567</v>
+        <v>-4.345344075917346</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-15.97279320600254</v>
+        <v>-10.13467171495891</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.598342562854739</v>
+        <v>-4.587873658497386</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.685732638649796</v>
+        <v>-4.673769618913255</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.1550241287595</v>
+        <v>-5.141404987419115</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-5.216726121238814</v>
+        <v>2.681277666055188</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.065638577206776</v>
+        <v>-6.054086327858833</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-6.269498311692026</v>
+        <v>-3.630555646737783</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.6879051655169803</v>
+        <v>1.663452553447868</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-1.108192417782085</v>
+        <v>-4.018077611927886</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.8589968618677801</v>
+        <v>4.101333736352132</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.007323</t>
+          <t>X ≈ -0.00645</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.6371717474538912</v>
+        <v>-22.10571241067961</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-2.247835456111119</v>
+        <v>-14.65329427080071</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-6.331839768859609</v>
+        <v>-12.02843917803234</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>1.18448375583958</v>
+        <v>-17.94731296782901</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.6480123357133181</v>
+        <v>-15.46509656439901</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-10.14062273520811</v>
+        <v>-15.17247503446453</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-10.23066720214406</v>
+        <v>-12.23606819048806</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-14.40109611432639</v>
+        <v>-6.654133184230346</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-7.065828699870828</v>
+        <v>-3.690355011255519</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-7.914715558837159</v>
+        <v>-4.540347023256572</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-8.118556432372863</v>
+        <v>-4.746091639295315</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.388121053077811</v>
+        <v>-7.74172001522345</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-8.512111061177983</v>
+        <v>-11.19328844209044</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>2.844706841832981</v>
+        <v>-7.94013356827427</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.006679</t>
+          <t>X ≈ -0.005871</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-11.83186878254702</v>
+        <v>-0.4787935182670537</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.9781703017814252</v>
+        <v>1.903134699422417</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-4.484713280995663</v>
+        <v>-2.478702268720973</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-13.70351444352465</v>
+        <v>-0.3547712249667327</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-17.35601532732005</v>
+        <v>-0.89166859303743</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-10.83269845514647</v>
+        <v>-6.583249560434467</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-7.804171008686232</v>
+        <v>-10.66265046772075</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>1.08658826774586</v>
+        <v>-5.141073923184436</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>7.265788729996537</v>
+        <v>-9.198393458813285</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>3.29640094780801</v>
+        <v>-10.04978783992553</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>3.092585709795244</v>
+        <v>-2.263061341187736</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>3.127972512650842</v>
+        <v>-2.229290749431257</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-0.4140080148406398</v>
+        <v>-2.649947945654489</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.1645524174238915</v>
+        <v>-2.424982053122754</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.006037</t>
+          <t>X ≈ -0.005293</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>5.070904481371691</v>
+        <v>4.880300496988752</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>12.52430298616199</v>
+        <v>6.544333202202196</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>6.091081390129808</v>
+        <v>9.42210568308537</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.220921034758952</v>
+        <v>6.283852986393413</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>5.684705088902852</v>
+        <v>7.384245974112169</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>5.983504122096761</v>
+        <v>2.774850586843236</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.196928121944985</v>
+        <v>4.327171856022005</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-3.641416077578562</v>
+        <v>3.861588431084265</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-9.755262488306123</v>
+        <v>0.527078990674795</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-10.60400540780008</v>
+        <v>-0.3218453096999738</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.295828504544168</v>
+        <v>1.111423999051283</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>1.330377204666711</v>
+        <v>2.78454618253911</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>3.939951483307588</v>
+        <v>0.7262502506829236</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>4.191508188636007</v>
+        <v>0.9520671272043657</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.005393</t>
+          <t>X ≈ -0.004713</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.890109049044106</v>
+        <v>0.5478430079612551</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2785354360798493</v>
+        <v>-2.568129296999551</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>6.885477613201978</v>
+        <v>1.570158611776606</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.516985177813979</v>
+        <v>-1.322080420886593</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>4.730024624806973</v>
+        <v>5.698684491354868</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-0.2216686067130169</v>
+        <v>4.484956365935133</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3.194850437758134</v>
+        <v>-0.1357801030647323</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>6.232449137376122</v>
+        <v>3.935804425268778</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.9152081132884575</v>
+        <v>3.87586796844483</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.06652708627991188</v>
+        <v>7.568533107555353</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-0.1375041590273867</v>
+        <v>7.365779378827561</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3.401617378000509</v>
+        <v>4.373334580158605</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-0.523616549268894</v>
+        <v>3.954409670322541</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-2.028587505143896</v>
+        <v>8.726533098393084</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.00475</t>
+          <t>X ≈ -0.004135</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-7.467165163317873</v>
+        <v>2.682418576056989</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-7.417192437316217</v>
+        <v>-0.06800684833436321</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-1.160992017963402</v>
+        <v>1.830473409854591</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-7.67707685903369</v>
+        <v>-2.624562871720059</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.0945228879513067</v>
+        <v>-2.015631474778701</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.3909718583766875</v>
+        <v>-4.013280360836205</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.683972987242846</v>
+        <v>0.4900424458222261</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.825822790738229</v>
+        <v>-5.71446457304674</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.2234855165683243</v>
+        <v>-1.185433083642096</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>3.920227798213098</v>
+        <v>-6.627566426287565</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>3.716239877645371</v>
+        <v>-6.834059230294692</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.2429439361212</v>
+        <v>-5.6527032794205</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.002447455826249723</v>
+        <v>-3.77604472600536</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>3.585447582575398</v>
+        <v>-4.700844122087744</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.004108</t>
+          <t>X ≈ -0.003556</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.908512130772721</v>
+        <v>-1.388874797056417</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>1.018825949373145</v>
+        <v>2.422547052149866</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.6285450563967458</v>
+        <v>3.113212304902277</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.35250513133132</v>
+        <v>2.160220762042663</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.611339123590454</v>
+        <v>3.792309652767344</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-5.874202097564464</v>
+        <v>1.921111684127403</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-0.8451954883274198</v>
+        <v>5.091339926166725</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-5.153565978154163</v>
+        <v>5.711359901864022</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.375479736789167</v>
+        <v>5.651799220914818</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-7.344194665406619</v>
+        <v>8.061723920932039</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-6.268129449289965</v>
+        <v>5.687080921692839</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-6.237519896589333</v>
+        <v>3.550266785748967</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-5.379284430528735</v>
+        <v>-0.1288209334927899</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-6.414552417424602</v>
+        <v>3.357626642528928</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.003464</t>
+          <t>X ≈ -0.002978</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.453127315669732</v>
+        <v>0.1971614232604608</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.1584462972945246</v>
+        <v>3.041138157444692</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7630666116263214</v>
+        <v>0.868194776444561</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>2.205965951190798</v>
+        <v>4.559933229576863</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.980546696271944</v>
+        <v>2.242998741122825</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-1.969874388678903</v>
+        <v>2.540639614131024</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>5.820438904626982</v>
+        <v>3.347400699163686</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>6.669526592499921</v>
+        <v>3.773164187044522</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>7.920869098618532</v>
+        <v>1.929960445625341</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>8.386209342839393</v>
+        <v>1.973449528309644</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.241484263925642</v>
+        <v>4.445644658250089</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>4.277625002474316</v>
+        <v>3.588961447411812</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>2.545023369476397</v>
+        <v>4.062540692186332</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>5.427552845733295</v>
+        <v>0.7178750897343846</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X ≈ -0.002822</t>
+          <t>X ≈ -0.002399</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>109</v>
+        <v>146</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-1.109053597732256</v>
+        <v>0.2580428638756374</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>2.764417032287177</v>
+        <v>3.430401457365342</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.546528648707401</v>
+        <v>-3.78894721527444</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>6.163010114078794</v>
+        <v>-3.660190680886764</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>4.711993644882959</v>
+        <v>-2.831864035719086</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>7.755996052140546</v>
+        <v>1.564131379715413</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4.928112677307332</v>
+        <v>0.7959844148887996</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>7.210673799566635</v>
+        <v>1.01343344914914</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>7.148188692323963</v>
+        <v>2.320572070833713</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>8.131643242991913</v>
+        <v>2.156540625615065</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>8.843877815997004</v>
+        <v>-2.153450438408946</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6.13391248144633</v>
+        <v>2.672041861126253</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>7.551572493312129</v>
+        <v>2.252823743134542</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>2.301043912850631</v>
+        <v>0.4243330153704008</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.002178</t>
+          <t>X ≈ -0.001819</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>123</v>
+        <v>153</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.4539736420228451</v>
+        <v>-6.050983223051198</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.3627787792539863</v>
+        <v>-5.704785925472898</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-5.694785510884444</v>
+        <v>-2.841925986617348</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-3.944742089755096</v>
+        <v>0.5448162538756947</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-8.530599928319326</v>
+        <v>-3.902494613569026</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-0.1352859242491178</v>
+        <v>1.608537183719605</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>2.211193292585925</v>
+        <v>5.437022696372331</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-1.501169715622787</v>
+        <v>3.015094610210916</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.7524264854160663</v>
+        <v>2.954960407195372</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-4.03485098293843</v>
+        <v>0.1487910726781436</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-5.049802233027059</v>
+        <v>0.5973130495150656</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.770834349804787</v>
+        <v>-1.32775539205344</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-3.816444628165236</v>
+        <v>-2.401523236025675</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-5.195040222302652</v>
+        <v>-1.523021268809025</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001535</t>
+          <t>X ≈ -0.001241</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-2.058484292975862</v>
+        <v>2.333847474953743</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-4.509291870847122</v>
+        <v>-0.6773459564076134</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.1264834394807295</v>
+        <v>3.767499539974182</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.2562077084750314</v>
+        <v>-0.9467286503341938</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>3.068904853286867</v>
+        <v>-0.1085509282912724</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.8525626836344173</v>
+        <v>-3.963115324509715</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4.118186526348467</v>
+        <v>-1.272371023007722</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>1.976388833167185</v>
+        <v>-3.826139807777693</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.6025094414961814</v>
+        <v>-0.4189360711319949</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-1.449846991235461</v>
+        <v>1.881633068571773</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-3.330190365022482</v>
+        <v>2.370236360724363</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-4.137980345082262</v>
+        <v>2.405254434471296</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-4.560230842012636</v>
+        <v>0.2937566205365414</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-2.633039812382584</v>
+        <v>0.519462391321845</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.0008923</t>
+          <t>X ≈ -0.000662</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>4.10090592395872</v>
+        <v>-1.418420492372555</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>1.094497731078988</v>
+        <v>-0.3338291282626145</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.578956719983807</v>
+        <v>-1.816855497157938</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.496179436618235</v>
+        <v>1.024778864785667</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>3.755207383984185</v>
+        <v>4.820301284782111</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.253251936838744</v>
+        <v>2.409333255205588</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.2212747443850347</v>
+        <v>-0.3849931923982055</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-3.822831950490631</v>
+        <v>-1.401108768457355</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.757610550445122</v>
+        <v>1.554523338273555</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.5192187946048037</v>
+        <v>-0.9293297032584888</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.6705052966776321</v>
+        <v>-0.5919729141799621</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>1.80971386393027</v>
+        <v>-0.0144013832256249</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3780266611893239</v>
+        <v>-2.069415622968407</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>1.331926455814838</v>
+        <v>0.6402353381814692</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -0.0002491</t>
+          <t>X ≈ -8.33e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>167</v>
+        <v>1492</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.996359957695176</v>
+        <v>0.8259206478950034</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.2136507514376689</v>
+        <v>1.487070618571884</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.6038579510029223</v>
+        <v>0.8243742771186433</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.916090081903739</v>
+        <v>0.3223963535556962</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.4127782404239611</v>
+        <v>-0.2464599356172812</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.4803951576767176</v>
+        <v>0.5563707839540655</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>-1.400459681178674</v>
+        <v>0.4719491383059093</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-4.260266014205534</v>
+        <v>0.07136047874593032</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-2.527866254576281</v>
+        <v>1.619514977103485</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3850607167374918</v>
+        <v>1.170207645268249</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-1.785549367452944</v>
+        <v>0.2657243464800771</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-3.546531512509432</v>
+        <v>0.7399425333421448</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-5.760592456836534</v>
+        <v>0.7219364521467</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-1.923534453352815</v>
+        <v>-0.1247139566080051</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0003939</t>
+          <t>X ≈ 0.0004955</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>150</v>
+        <v>169</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.170971624945381</v>
+        <v>-6.306920111761215</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.119258495458297</v>
+        <v>-5.559863712286273</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.8662952867048617</v>
+        <v>-4.183933107866217</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>3.921149047256286</v>
+        <v>0.08188777640210532</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>5.375004589172647</v>
+        <v>3.089852442040652</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.68322402383231</v>
+        <v>-0.1590277470585022</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2699740190779707</v>
+        <v>-4.383192508092137</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>3.129657169385283</v>
+        <v>-3.670052950449971</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>2.416099963979015</v>
+        <v>-3.731035106972683</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>1.555392768369003</v>
+        <v>-0.4389420689830814</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.342408991376594</v>
+        <v>1.131504701750814</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.04639826277259118</v>
+        <v>-0.6092650748878867</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.615561641245691</v>
+        <v>1.929163953455379</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-1.08121908409111</v>
+        <v>0.9714676510192604</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001037</t>
+          <t>X ≈ 0.001074</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>6.851212593909956</v>
+        <v>4.003614311970161</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.129449621704715</v>
+        <v>-3.235970565010156</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.3023707705904712</v>
+        <v>-1.939369040963768</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>6.262236776564045</v>
+        <v>3.265264629140994</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>3.794463307215224</v>
+        <v>-1.218868069462417</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-1.059512455139995</v>
+        <v>-3.178468738145604</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>1.433691756272403</v>
+        <v>-1.008895718644055</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-1.614136803799489</v>
+        <v>-0.3470830042727258</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.320297980304332</v>
+        <v>-3.232923917857647</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-2.52526187500964</v>
+        <v>-3.517870962775014</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.7945313283594828</v>
+        <v>-2.027656866798047</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.1149868806915535</v>
+        <v>-1.993278714442724</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1099197986861711</v>
+        <v>-2.413429567756133</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.9306814496827371</v>
+        <v>-2.187693917529536</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.00168</t>
+          <t>X ≈ 0.001653</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.576900839898606</v>
+        <v>-1.876640732769133</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-3.368540034016853</v>
+        <v>-2.272712136751416</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>3.465855135701048</v>
+        <v>5.013672160747483</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-2.912701537388273</v>
+        <v>2.692652436132285</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.5578154190806401</v>
+        <v>3.994147085430299</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.187095536725714</v>
+        <v>6.12676746528922</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>1.826398628642671</v>
+        <v>5.434591186491744</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4.257765954498851</v>
+        <v>6.813847292770703</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-0.8756976997993462</v>
+        <v>0.00439887857914556</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-1.001185203667895</v>
+        <v>0.3814739472799644</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>1.692612196652206</v>
+        <v>3.857754384111942</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-2.620830732958851</v>
+        <v>-1.015842923655505</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.591809981584902</v>
+        <v>0.4044970205771321</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-3.516001692786922</v>
+        <v>-1.210258126742417</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002322</t>
+          <t>X ≈ 0.002231</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>137</v>
+        <v>151</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.06720172576828531</v>
+        <v>-2.138905089144828</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>2.82461547069471</v>
+        <v>-3.748607598468865</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>3.884860795474779</v>
+        <v>1.140487219317897</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>3.283651272650197</v>
+        <v>-0.7133996151152502</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>5.657020376228793</v>
+        <v>2.054546817866886</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>7.422812353413001</v>
+        <v>3.670340991811223</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>6.618528111346613</v>
+        <v>2.928707894717832</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>5.42141770526581</v>
+        <v>3.128802804085907</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>3.170636797185736</v>
+        <v>0.4188140250465295</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>4.510292634055538</v>
+        <v>1.555650195604088</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>4.305539309737959</v>
+        <v>0.6886973817147606</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>5.799776481681882</v>
+        <v>1.385327189699183</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>9.029156907233464</v>
+        <v>2.95193130327327</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>6.359170210312627</v>
+        <v>1.853163642241483</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.002966</t>
+          <t>X ≈ 0.00281</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>92</v>
+        <v>120</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.7731924762358346</v>
+        <v>-0.8050853524714938</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.8352678722760132</v>
+        <v>-0.7507271696854332</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>3.098130085763621</v>
+        <v>-2.809843240257216</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-6.517416201106577</v>
+        <v>-4.343517674335395</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.5614916289415319</v>
+        <v>3.427898281598374</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-2.430850162760329</v>
+        <v>-0.4322510921821774</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-5.782297023531271</v>
+        <v>-3.844945235741193</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-4.075567378834478</v>
+        <v>-3.482676224611801</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8.484393351973367</v>
+        <v>-8.543658381134485</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-7.160605493522908</v>
+        <v>-5.22691051079768</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-6.278402296101298</v>
+        <v>-7.931611669057865</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.157062617016798</v>
+        <v>-5.397233516702492</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.142534619266236</v>
+        <v>0.8492822966507063</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.1071867130101793</v>
+        <v>4.408351280210631</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.003609</t>
+          <t>X ≈ 0.00339</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>10.55834000265795</v>
+        <v>3.169117336399815</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>8.951325391728204</v>
+        <v>1.570721822337021</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.445593967266269</v>
+        <v>-0.7066166433836543</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>2.762320595111319</v>
+        <v>-1.518640319195441</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>1.034006633275709</v>
+        <v>-3.937566395422088</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4.90232296650516</v>
+        <v>-5.522759446752531</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.06656426011261374</v>
+        <v>-8.44097426216323</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.4006191386688442</v>
+        <v>-6.092739117693412</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-4.033047596279722</v>
+        <v>-10.87070240629177</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-2.50222040035527</v>
+        <v>-10.77722497620643</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.3260213437205337</v>
+        <v>-11.92532236088172</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-2.672590567327418</v>
+        <v>-10.0041517556962</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>2.8595357741087</v>
+        <v>-7.594113929764326</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.918780915908734</v>
+        <v>-9.255170732367979</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.004252</t>
+          <t>X ≈ 0.003968</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-3.118393926905597</v>
+        <v>3.215182302001708</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.8526761929390503</v>
+        <v>6.805965326193359</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2.624504349857332</v>
+        <v>9.840231747133977</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.336706104008812</v>
+        <v>5.391831861169003</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-5.529509597239169</v>
+        <v>1.421686807252257</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>1.22907463655693</v>
+        <v>5.148098642582987</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.1498859563375703</v>
+        <v>-1.802834167141299</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.811874549924262</v>
+        <v>-5.724055534956534</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-3.275471838703972</v>
+        <v>-2.336761829410307</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.2294931276279968</v>
+        <v>-0.8878300510276276</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.163156145457066</v>
+        <v>3.505169940137471</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.3998632946001024</v>
+        <v>3.539548092492794</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.777284691857552</v>
+        <v>4.268822526535708</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.5703965732687593</v>
+        <v>3.345132889405917</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.004895</t>
+          <t>X ≈ 0.004547</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>12.12071435393493</v>
+        <v>6.310066271477332</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>10.51197087625113</v>
+        <v>9.099106177904261</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-4.468749151685699</v>
+        <v>-3.001643052534511</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-2.883307049280781</v>
+        <v>0.05440014554836381</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.4943695130751351</v>
+        <v>-4.866528826951445</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-3.128506808088488</v>
+        <v>-0.1905738194706785</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-6.165928737086226</v>
+        <v>4.132775751048456</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.7507591946912626</v>
+        <v>5.144774755780446</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8117590808735642</v>
+        <v>5.083792599257713</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.27929220468679</v>
+        <v>8.645638508810123</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-1.866637590219106</v>
+        <v>5.499760879961741</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.108922037714564</v>
+        <v>2.592962561728832</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-2.252509043818577</v>
+        <v>5.113988179003655</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>5.350153464928297</v>
+        <v>3.869135593936065</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.005539</t>
+          <t>X ≈ 0.005125</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.770082811574625</v>
+        <v>3.586208466468221</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-3.363604305539091</v>
+        <v>6.831668098952548</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.234823999125418</v>
+        <v>-0.8217671603200856</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.8667528789176728</v>
+        <v>-0.6936463938360902</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-2.69158033810244</v>
+        <v>2.412126630057685</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-6.9581162135743</v>
+        <v>-2.151353820064237</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-6.210492016943604</v>
+        <v>-2.232723348398608</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>3.928385190335462</v>
+        <v>0.9482180843314225</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.8370822738501431</v>
+        <v>-2.771300657557212</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.01304291117781986</v>
+        <v>-3.621219453887072</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>2.812506794807675</v>
+        <v>-1.386896221903392</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.33173843700159</v>
+        <v>-2.572030264670019</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.9114838260567097</v>
+        <v>-4.211693313105414</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.3539463568185255</v>
+        <v>0.892091117608949</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.006181</t>
+          <t>X ≈ 0.005704</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4.204434126165452</v>
+        <v>2.249767804788071</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.752540161540743</v>
+        <v>-7.271556813300975</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>7.598666548596768</v>
+        <v>0.1992334647009173</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>5.042400827020721</v>
+        <v>-2.825681429267135</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>9.886229664857254</v>
+        <v>-6.535320788016897</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>15.6596634857504</v>
+        <v>-9.376877027840621</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>7.466821660370016</v>
+        <v>-6.366938199813568</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.59423285618319</v>
+        <v>1.993514251578723</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-3.872172435404565</v>
+        <v>1.932532095055926</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-2.019594917729783</v>
+        <v>2.669914886027748</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.4783544606553392</v>
+        <v>2.465213727767555</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.5127376180007346</v>
+        <v>5.674195054726027</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>0.09248300705591106</v>
+        <v>5.254044201412668</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.3422043393321985</v>
+        <v>3.892478264337583</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.006824</t>
+          <t>X ≈ 0.006284</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-4.230970163579997</v>
+        <v>0.1321092511163968</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.382712382264252</v>
+        <v>-6.687790373348783</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-6.191715605760805</v>
+        <v>0.7738511187485031</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-9.475596990053283</v>
+        <v>3.522880554620954</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3.17051687886547</v>
+        <v>8.230868102043623</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-6.334744715554336</v>
+        <v>11.13548840269608</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-2.971202570757605</v>
+        <v>11.10719943671886</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-10.33493769367706</v>
+        <v>5.376972898195312</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-10.39593757985934</v>
+        <v>0.05283284693572909</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-11.24606276488728</v>
+        <v>1.834492997974209</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-4.554264365066935</v>
+        <v>4.261370787082406</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.376670516416475</v>
+        <v>4.295748939437807</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-1.491859956597416</v>
+        <v>1.244019138755981</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-4.690414486390097</v>
+        <v>1.469754788982463</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.007468</t>
+          <t>X ≈ 0.006863</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-7.090326580464556</v>
+        <v>0.4294272112399611</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>5.348076232785232</v>
+        <v>1.781889264001613</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>4.90605995428858</v>
+        <v>1.387117879246574</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-4.534644008813459</v>
+        <v>4.43657041528445</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-5.073065223885628</v>
+        <v>9.750061873100556</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>7.29415512024211</v>
+        <v>4.191212816486235</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>7.209421402969767</v>
+        <v>4.141255164273076</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>11.50414276609305</v>
+        <v>-8.090519361866612</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>11.44314287991072</v>
+        <v>-5.210325047801106</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>1.069208171073299</v>
+        <v>-6.060243844131051</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>-0.3825920612146874</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.898838004101151</v>
+        <v>-0.3482139088594494</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.4785833931562138</v>
+        <v>-3.709541232761097</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.7283047254325012</v>
+        <v>-6.424982053122797</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.00811</t>
+          <t>X ≈ 0.007441</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>10.00656167979002</v>
+        <v>-2.397997290899198</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>8.394988066825768</v>
+        <v>10.55687521194633</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-4.499880639770822</v>
+        <v>6.458400123487579</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>1.880372492836678</v>
+        <v>-4.49484626415677</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>13.84195127776451</v>
+        <v>-5.060775397130854</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-1.004418504035336</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>7.80465949820789</v>
+        <v>4.576985011767619</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>7.337476099426432</v>
+        <v>15.22102747909199</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>13.52647621324409</v>
+        <v>11.45634161886547</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>12.67635102821612</v>
+        <v>3.199015415128301</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>12.47159770389862</v>
+        <v>2.994314256868051</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>6.25598086124397</v>
+        <v>3.028692409223432</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.4142737497008468</v>
+        <v>-1.095162147793673</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.1645524174246447</v>
+        <v>2.834277206136555</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.008754</t>
+          <t>X ≈ 0.00802</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-11.31696773197469</v>
+        <v>6.609993060374777</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-12.92854134493894</v>
+        <v>4.998806967310912</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>10.20600171317035</v>
+        <v>9.149490128010413</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.453901904601388</v>
+        <v>4.734260726144235</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>3.915480689529218</v>
+        <v>13.28688026395761</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.669430313931592</v>
+        <v>-13.68847297913455</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-7.636516972380349</v>
+        <v>-0.1368197020370943</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>3.66100551119105</v>
+        <v>-0.6038883458238331</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.600005625008798</v>
+        <v>3.880584043107945</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>14.51458632233387</v>
+        <v>3.030665246778085</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>8.427480056839741</v>
+        <v>2.825964088517892</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>8.461863214185229</v>
+        <v>-1.685112304581338</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>8.04160860324027</v>
+        <v>-2.105263157894747</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>14.17368287669311</v>
+        <v>-6.424982053122754</v>
       </c>
     </row>
   </sheetData>
@@ -2121,7 +2121,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-1 is above threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-1 is above threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -2210,1561 +2210,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.009573</t>
+          <t>X &gt; -0.008476</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2205</v>
+        <v>4093</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>0.7856209289985259</v>
+        <v>-0.0454557285372772</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-0.5545822633415796</v>
+        <v>0.2075324683628423</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.4074011331825957</v>
+        <v>0.1671225930112996</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.5376542657900956</v>
+        <v>0.1644337702582988</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.5872022954035856</v>
+        <v>0.2245160070541203</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.683510862538995</v>
+        <v>0.1451817835619096</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.4427310237850719</v>
+        <v>0.07382331348397742</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.2269688530495841</v>
+        <v>0.01045218069040033</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.3775092940022873</v>
+        <v>0.03613664082745061</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-0.3218373775809482</v>
+        <v>0.0539860802038703</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.06217741404350363</v>
+        <v>0.009469060108798999</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-0.195083932593775</v>
+        <v>0.1552695358005067</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-0.04596005976434725</v>
+        <v>0.1641332981162762</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.002681142666105529</v>
+        <v>0.1105664443118854</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.00893</t>
+          <t>X &gt; -0.007897</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2192</v>
+        <v>4074</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.8277627716917522</v>
+        <v>0.00256818771864431</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-0.5108354090614</v>
+        <v>0.2397627809539458</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.5046689507660318</v>
+        <v>0.2254887927483722</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.6349220833735316</v>
+        <v>0.1732243090843113</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.6424517327235577</v>
+        <v>0.2850767772165952</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.6920786956804434</v>
+        <v>0.2040039706672303</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.4503789881896694</v>
+        <v>0.1572258750273576</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.1905512702692178</v>
+        <v>0.07124534401575033</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-0.3260294815167342</v>
+        <v>0.07283258887450472</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-0.3105510218977301</v>
+        <v>0.07021226180327034</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.0313926925090513</v>
+        <v>0.05097356518299279</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-0.1820319008343816</v>
+        <v>0.1482358977560807</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-0.02952682767626413</v>
+        <v>0.1345583702703408</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.01792933440021471</v>
+        <v>0.05513576720125002</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.008287</t>
+          <t>X &gt; -0.007318</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2174</v>
+        <v>4049</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.8093139733680061</v>
+        <v>-0.01907457312421457</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-0.3894156028990068</v>
+        <v>0.30336697268352</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.5918624794952336</v>
+        <v>0.2914516147994846</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.5386293735706218</v>
+        <v>0.1888061806896815</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.688281552993864</v>
+        <v>0.3046677992414644</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.6899898194269269</v>
+        <v>0.270565271251975</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.4929055955448902</v>
+        <v>0.1993825572420889</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.2348118826142596</v>
+        <v>0.165083742507079</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-0.3314705024196698</v>
+        <v>0.1670799842659463</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-0.3088350076129629</v>
+        <v>0.1203631136780245</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1294984847897069</v>
+        <v>0.1269602295930099</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-0.08593090346187182</v>
+        <v>0.2246293978041649</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.02538142271289701</v>
+        <v>0.2381711855395992</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-0.02080816719460898</v>
+        <v>0.1321925578923171</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.007644</t>
+          <t>X &gt; -0.006739</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2156</v>
+        <v>4011</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.9293183865430308</v>
+        <v>-0.02067746194588693</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-0.3584809433499956</v>
+        <v>0.2205998401104949</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.7267613583790364</v>
+        <v>0.3365974016418107</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.67200061494583</v>
+        <v>0.2317624783090082</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.8273814350262967</v>
+        <v>0.4035695448260128</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.7341410174237168</v>
+        <v>0.316593862458781</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.536140979689371</v>
+        <v>0.2455505409603305</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2798105135069875</v>
+        <v>0.2153571336158251</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-0.2906845093126549</v>
+        <v>0.1432606095693671</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-0.2607726401488222</v>
+        <v>0.178859518260019</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1829223912538325</v>
+        <v>0.1625587345295827</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-0.08090514431669504</v>
+        <v>0.2109980639935287</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.03484539726247959</v>
+        <v>0.2784946595619786</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-0.01381030239677727</v>
+        <v>0.09458912613428794</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.007001</t>
+          <t>X &gt; -0.00616</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2129</v>
+        <v>3978</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.9491846306097003</v>
+        <v>0.1625317269199229</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-0.3345201298955445</v>
+        <v>0.3439881019657207</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.8162786108146634</v>
+        <v>0.439173119874404</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.6655012984572792</v>
+        <v>0.3825692881940128</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.8296561957972912</v>
+        <v>0.5352100630774999</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.8720548837088558</v>
+        <v>0.445085384228129</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.6726857523100875</v>
+        <v>0.3490933811156438</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.4659939230661649</v>
+        <v>0.272343855709579</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-0.2047620606771119</v>
+        <v>0.1750628507677661</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-0.1637052569620749</v>
+        <v>0.2180082904747138</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2882018314783181</v>
+        <v>0.2032790619142517</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-0.02628098765321596</v>
+        <v>0.276970838406335</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.1432379873883107</v>
+        <v>0.3736602810689078</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-0.05006204635837008</v>
+        <v>0.1612421801603006</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.006358</t>
+          <t>X &gt; -0.005582</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2097</v>
+        <v>3928</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>1.144222164811424</v>
+        <v>0.1706952356417517</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-0.3246980957990502</v>
+        <v>0.3241415312241571</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.8971711909472049</v>
+        <v>0.4763151182017396</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.884770971200922</v>
+        <v>0.3919549871904451</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.107167635348915</v>
+        <v>0.5533729787612387</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>1.050668191693298</v>
+        <v>0.5345499329127392</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.8020416971607744</v>
+        <v>0.4892632366252627</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.4565237184740099</v>
+        <v>0.3412519231598594</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-0.3187618819940141</v>
+        <v>0.2943787406554961</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.2165061146409784</v>
+        <v>0.3487083430510864</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2454072277080996</v>
+        <v>0.2346734153142194</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-0.07441456514951028</v>
+        <v>0.3088733535264652</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.1517415029206504</v>
+        <v>0.4121481658286186</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-0.04831493530728892</v>
+        <v>0.1941625497285671</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.005715</t>
+          <t>X &gt; -0.005003</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2064</v>
+        <v>3867</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>1.081440906843163</v>
+        <v>0.09640355709451853</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-0.5301327061210941</v>
+        <v>0.2260211040378053</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.8141290220649253</v>
+        <v>0.3351997252723606</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.7994546184405422</v>
+        <v>0.2990132292511305</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>1.033980263271751</v>
+        <v>0.4456193576812382</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.971800175364173</v>
+        <v>0.4992103053229258</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.9139438308964785</v>
+        <v>0.4287221386725335</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.5220431047481071</v>
+        <v>0.2857203671776034</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-0.1678875990442563</v>
+        <v>0.2907080100500821</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-0.05042691082592654</v>
+        <v>0.359285993120352</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2286127014796193</v>
+        <v>0.2208431113038927</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-0.09687489867854993</v>
+        <v>0.2698208470434693</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.09117419218772227</v>
+        <v>0.4071933618006582</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.1161028050214981</v>
+        <v>0.1822069823052317</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.005072</t>
+          <t>X &gt; -0.004424</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2007</v>
+        <v>3801</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>1.05847424809604</v>
+        <v>0.08856482945515864</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.553099364868217</v>
+        <v>0.2745383169997737</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.6416990919728391</v>
+        <v>0.3137560824127803</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.7222751257229163</v>
+        <v>0.3271616588509971</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.9290103935121508</v>
+        <v>0.3544059141604521</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.005695402358896</v>
+        <v>0.4300024021394577</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.8491647194908367</v>
+        <v>0.438524071836099</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.3598641591278806</v>
+        <v>0.2223408491996892</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-0.198648164865368</v>
+        <v>0.2284558245057298</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-0.05374847427139429</v>
+        <v>0.2341056959478394</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.2390106392219664</v>
+        <v>0.09677949813456621</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-0.1962341711103903</v>
+        <v>0.1985680434692512</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.1086346168329797</v>
+        <v>0.3456000241625503</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.06178709604941446</v>
+        <v>0.03384457144972686</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &gt; -0.004429</t>
+          <t>X &gt; -0.003845</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1947</v>
+        <v>3714</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1.321205817014814</v>
+        <v>0.02780411972054253</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-0.3415710729591837</v>
+        <v>0.282562395993871</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.697251976716629</v>
+        <v>0.2782271627877222</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.9811149403533221</v>
+        <v>0.3963054483393265</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.9547264953784307</v>
+        <v>0.4099237528351196</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.024639117119513</v>
+        <v>0.5340857624999487</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>1.019677437726088</v>
+        <v>0.4373172601675961</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.4272196891699807</v>
+        <v>0.3614097968936676</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-0.1978827611148901</v>
+        <v>0.2615760008678407</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-0.1762130743479418</v>
+        <v>0.3948395340292876</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.13185411415499</v>
+        <v>0.2591335555856631</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-0.1639780920653777</v>
+        <v>0.3356333652493788</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.1119069484510575</v>
+        <v>0.442149053043714</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.1741826177327681</v>
+        <v>0.1447540804259759</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003786</t>
+          <t>X &gt; -0.003267</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1869</v>
+        <v>3622</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1.213228346456695</v>
+        <v>0.06378823356468644</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-0.3983452665075617</v>
+        <v>0.228206076732036</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.7001193602291806</v>
+        <v>0.2062176009228622</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.203705826170008</v>
+        <v>0.3515014149708264</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.145284611097843</v>
+        <v>0.3240100303630769</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.31255223362318</v>
+        <v>0.4988548445569023</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1.097505200290108</v>
+        <v>0.3191035425331634</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.6601256720759636</v>
+        <v>0.2255192917425717</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.1487374619695814</v>
+        <v>0.1246625452509633</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.1229322247973599</v>
+        <v>0.2000981304966842</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.3989481312490071</v>
+        <v>0.1212618941605257</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.08949235242519649</v>
+        <v>0.2539806113327714</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.3410738438820005</v>
+        <v>0.4566518798690424</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.08625015079369547</v>
+        <v>0.06314605289602326</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &gt; -0.003143</t>
+          <t>X &gt; -0.002688</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1793</v>
+        <v>3510</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>1.203059734264734</v>
+        <v>0.05953245087353309</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.408513878699523</v>
+        <v>0.138448699797614</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.6974512112575297</v>
+        <v>0.1850946825016493</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.161222965321393</v>
+        <v>0.2172152715987821</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>1.067493245524375</v>
+        <v>0.2627773421564967</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.45168465040787</v>
+        <v>0.433703877550542</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.8973139222479531</v>
+        <v>0.2224741175922418</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.4054048299386395</v>
+        <v>0.1123180871061606</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.4907843658204953</v>
+        <v>0.06705759800254896</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.2273238047459785</v>
+        <v>0.1435125588285828</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2360743185979075</v>
+        <v>-0.0167241085682619</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.08803028081726438</v>
+        <v>0.1475652684151498</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.2476549013581959</v>
+        <v>0.3415921798748727</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.1401519712450181</v>
+        <v>0.04225441411371378</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &gt; -0.0025</t>
+          <t>X &gt; -0.002109</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1684</v>
+        <v>3364</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>1.352715525943871</v>
+        <v>0.05091695732469503</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.6138876728192031</v>
+        <v>-0.004424398479692115</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.7072199519451488</v>
+        <v>0.3575709360912214</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.8374730845526486</v>
+        <v>0.3854974562191416</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.8315962481787125</v>
+        <v>0.3970869857860535</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.043626489606879</v>
+        <v>0.3846425174684782</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.6364130527102603</v>
+        <v>0.1975833615264548</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.03507873163466257</v>
+        <v>0.07320903750500918</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.9852309592514672</v>
+        <v>-0.03074653785754577</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.7683733345579924</v>
+        <v>0.0561457045625815</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.3210816084902746</v>
+        <v>0.07601133856513798</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.4907569797998832</v>
+        <v>0.03800118323803758</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.2251046102350145</v>
+        <v>0.2586433664872629</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-0.2981628687310121</v>
+        <v>0.02567193023039493</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.001857</t>
+          <t>X &gt; -0.00153</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1561</v>
+        <v>3211</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.495074762112935</v>
+        <v>0.3416646146269358</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.69084473470582</v>
+        <v>0.2671904609503741</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.211670094115583</v>
+        <v>0.5100228293252371</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>1.214290808088755</v>
+        <v>0.3779061214195565</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>1.569296523456906</v>
+        <v>0.6019564920773419</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.136519652261782</v>
+        <v>0.3263255184225642</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.5123272298372825</v>
+        <v>-0.05206915115850563</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.08044285134454299</v>
+        <v>-0.06696800784659729</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-1.003574937651052</v>
+        <v>-0.1730116149653256</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.5109891252365273</v>
+        <v>0.05173127250973408</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.05152097755586738</v>
+        <v>0.05117198578552262</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3898924592934208</v>
+        <v>0.10307771890281</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.05787733864737987</v>
+        <v>0.3853968670118562</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.08768973504176358</v>
+        <v>0.09946515958356628</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.001214</t>
+          <t>X &gt; -0.0009514</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1442</v>
+        <v>3067</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.788329635591133</v>
+        <v>0.2481288037736391</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3757301652184282</v>
+        <v>0.3115377854040986</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.301224332604868</v>
+        <v>0.3570796776025631</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.293355918251045</v>
+        <v>0.4400996027148167</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>1.445542437985502</v>
+        <v>0.6353158231934515</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.159952994332969</v>
+        <v>0.5277208498155375</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.2147563170184057</v>
+        <v>0.005225752508366099</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.07601871026218987</v>
+        <v>0.1095304398841108</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-1.036672575683248</v>
+        <v>-0.1614651129477238</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.433510563479345</v>
+        <v>-0.0341852122091808</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.3305942436909675</v>
+        <v>-0.05771137580273944</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.08058423570889772</v>
+        <v>-0.005012743125838881</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.4389833535562104</v>
+        <v>0.3896995065594453</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.31221595982921</v>
+        <v>0.07974569386126262</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0005706</t>
+          <t>X &gt; -0.0003727</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1300</v>
+        <v>2883</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.535725148707911</v>
+        <v>0.3544919915956655</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.5363242892755409</v>
+        <v>0.3527266553710291</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8339643333680868</v>
+        <v>0.4958254535844944</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>1.271201349321714</v>
+        <v>0.4027839647609355</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>1.193255959268726</v>
+        <v>0.368219976876297</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>1.149761879074639</v>
+        <v>0.407631816658494</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.2623843252640015</v>
+        <v>0.03013046491308558</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.3332485821319935</v>
+        <v>0.2059430705933778</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-1.3418942709988</v>
+        <v>-0.2709836266572978</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.4241485874640887</v>
+        <v>0.02294506401456431</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.293465497903199</v>
+        <v>-0.02361351834127134</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.2870629512079503</v>
+        <v>-0.004413537514203369</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.4456416999532209</v>
+        <v>0.546646153744021</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.2008321979600112</v>
+        <v>0.04397389554183206</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 7.239e-05</t>
+          <t>X &gt; 0.0002061</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1133</v>
+        <v>1391</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.467829285423825</v>
+        <v>-0.1511669265916922</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.5838851726108558</v>
+        <v>-0.863981607098907</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.045894008116505</v>
+        <v>0.143420820433569</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>1.176147140724005</v>
+        <v>0.489008490942247</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.429979446778596</v>
+        <v>1.02753157244814</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>1.24842405248458</v>
+        <v>0.2480929674816394</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.5074813676964283</v>
+        <v>-0.443768500365195</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>1.010315605599232</v>
+        <v>0.350297655091147</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-1.167086396985184</v>
+        <v>-2.298750640899641</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4299099947115295</v>
+        <v>-1.207619832628495</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.5999045822054683</v>
+        <v>-0.3339600994436793</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.1933706319671131</v>
+        <v>-0.8028170297626929</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.360417608323807</v>
+        <v>0.3586280910432293</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.513955967394466</v>
+        <v>0.2249101107881017</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007154</t>
+          <t>X &gt; 0.0007849</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>983</v>
+        <v>1222</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2.633465233089517</v>
+        <v>0.7001606415700437</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1081860363689131</v>
+        <v>-0.2145511031900185</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>1.337682812005831</v>
+        <v>0.7418846615814232</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.7572760461361696</v>
+        <v>0.5453124195488712</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.8279918869015717</v>
+        <v>0.7423169841002348</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>1.182076142309441</v>
+        <v>0.3043968960882637</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.5437235877297653</v>
+        <v>0.1010454581502316</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.6869165877275023</v>
+        <v>0.9063035899000269</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-1.713859493775239</v>
+        <v>-2.100668746655494</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.7328554824654248</v>
+        <v>-1.313926331856052</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.4866027903685719</v>
+        <v>-0.5366307634386658</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.2157977483243698</v>
+        <v>-0.8295848533092069</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>1.321484134327598</v>
+        <v>0.1414263228372903</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.7573702682315471</v>
+        <v>0.1216627913944279</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001358</t>
+          <t>X &gt; 0.001364</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>828</v>
+        <v>1045</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>1.843911077380383</v>
+        <v>0.1406282973970079</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.7142651752595057</v>
+        <v>0.2972108535010562</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.644697673482192</v>
+        <v>1.196030025553185</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>-0.2732419649946465</v>
+        <v>0.0846123802208183</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2726741693307773</v>
+        <v>1.074498567335247</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>1.601697196179806</v>
+        <v>0.894317678154664</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.3771232663238351</v>
+        <v>0.2890450641718445</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.117669336141361</v>
+        <v>1.118599692453685</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.600335380958803</v>
+        <v>-1.90888964110259</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3973204693683812</v>
+        <v>-0.9406266192506294</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.7264286217729747</v>
+        <v>-0.2840837583720557</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>-0.6324807256339611</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>1.548286636772545</v>
+        <v>0.5741626794258394</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>1.073370287889411</v>
+        <v>0.512816989939445</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.002001</t>
+          <t>X &gt; 0.001942</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>690</v>
+        <v>882</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>1.697313124876729</v>
+        <v>0.51343425195153</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>1.530826217114786</v>
+        <v>0.7721512700669848</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.28046618103842</v>
+        <v>0.4905020572576433</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.2546499494840759</v>
+        <v>-0.3973723466653141</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.4387720870130636</v>
+        <v>0.5349263355331146</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1.684617528070625</v>
+        <v>-0.07267701039741326</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.08726819386006213</v>
+        <v>-0.6618891965290032</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.4896500124698662</v>
+        <v>0.06607660985541486</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-1.745262917190693</v>
+        <v>-2.262479242812489</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.2765475225084728</v>
+        <v>-1.18496039741899</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.5331919067971356</v>
+        <v>-1.049525501257413</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.8574301366063253</v>
+        <v>-0.5616326096730688</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.176305960444033</v>
+        <v>0.6055181243151182</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.991244684024672</v>
+        <v>0.8312537745416506</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.002644</t>
+          <t>X &gt; 0.002521</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>553</v>
+        <v>731</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2.101156274384614</v>
+        <v>1.061318301890715</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.210303382141085</v>
+        <v>1.705987917329516</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.6352544953643147</v>
+        <v>0.3562369964216714</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.4957536332894463</v>
+        <v>-0.3320917481209307</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.8539946681814357</v>
+        <v>0.2210238829580078</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.2630394248664558</v>
+        <v>-0.8458585676251928</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.530783539766801</v>
+        <v>-1.403585722901468</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.7321441537381688</v>
+        <v>-0.5665795533850826</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.963125956737834</v>
+        <v>-2.816344199647936</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.462437398546946</v>
+        <v>-1.751078317455224</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-0.4013679380543991</v>
+        <v>-1.40858385328039</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3669847807089681</v>
+        <v>-0.9638089840987973</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>0.1208281242840883</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.9091365518339884</v>
+        <v>0.6201615857281411</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.003287</t>
+          <t>X &gt; 0.0031</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>461</v>
+        <v>611</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>2.366172910891535</v>
+        <v>1.427878757739265</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.618530183456436</v>
+        <v>2.188485152095133</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1437478699483989</v>
+        <v>0.978053082185113</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.7059664453204775</v>
+        <v>0.4557496776495</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.9123683766631387</v>
+        <v>-0.4088041495081924</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.8006486267355797</v>
+        <v>-0.9270908050280724</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.6823253174103385</v>
+        <v>-0.9241043128511137</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-0.06491001771026816</v>
+        <v>0.006139923778917478</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.861267821463073</v>
+        <v>-1.69150344387316</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.3252758698315645</v>
+        <v>-1.068427150186658</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.7714892440287286</v>
+        <v>-0.1274654606563459</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.5889526616778511</v>
+        <v>-0.09308730830102263</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.6025375301255806</v>
+        <v>-0.02223979827563483</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>1.069178602098177</v>
+        <v>-0.1238363902749597</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.00393</t>
+          <t>X &gt; 0.003679</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>377</v>
+        <v>505</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.540862471346756</v>
+        <v>1.062391056079825</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.01530217064125594</v>
+        <v>2.318154286658228</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.1463186344937739</v>
+        <v>1.331666925571824</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.2477867408577907</v>
+        <v>0.8701760928288351</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-1.346043445190638</v>
+        <v>0.3318865397331408</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>-0.1132522871653308</v>
+        <v>0.03754459303686275</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.8491866556382632</v>
+        <v>0.6536941319550067</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.009889892529834299</v>
+        <v>1.28630067307806</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-1.377369940602065</v>
+        <v>0.2352195066543032</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.1597727788792866</v>
+        <v>0.969459126166015</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>1.016027412121396</v>
+        <v>2.348916383747408</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.315662558856744</v>
+        <v>1.987254932142335</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>0.0996519797420774</v>
+        <v>1.567104078828926</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>0.8798772907982126</v>
+        <v>1.792839729055459</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.004573</t>
+          <t>X &gt; 0.004258</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>300</v>
+        <v>418</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.48007161356486</v>
+        <v>0.6143220647037424</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>0.1996238284151701</v>
+        <v>1.3840883525923</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.8574965338105613</v>
+        <v>-0.4392544607341762</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-1.058369229017636</v>
+        <v>-0.07093407905057347</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-0.2722871328315151</v>
+        <v>0.1050620821394546</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.4577828642540496</v>
+        <v>-1.026135316796896</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-1.028673835125446</v>
+        <v>1.164981122436771</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>1.504142766093054</v>
+        <v>2.745393950826895</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.8901904534225764</v>
+        <v>0.7705361962179964</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>0.2596843615494961</v>
+        <v>1.356024098452721</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>0.7215977038985741</v>
+        <v>2.108260739235597</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.755980861244005</v>
+        <v>1.66416999206939</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.3309404163675538</v>
+        <v>1.004784688995208</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.252114249242062</v>
+        <v>1.469754788982513</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.005217</t>
+          <t>X &gt; 0.004836</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>232</v>
+        <v>350</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-1.638737465509124</v>
+        <v>-0.4922796668979856</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-2.822960651122955</v>
+        <v>-0.1148293963254545</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.2009740610838833</v>
+        <v>0.05858103710131957</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.5234736610094757</v>
+        <v>-0.09528472840122504</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.2071940213807864</v>
+        <v>1.070971173048541</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.325015533076737</v>
+        <v>-1.188472979134559</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.4770732913113349</v>
+        <v>0.5883810231636346</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.165062306322945</v>
+        <v>2.279228537293058</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.9131789591697057</v>
+        <v>-0.06746790494401012</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.03916621316315627</v>
+        <v>-0.06024384413100137</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.480218393553756</v>
+        <v>1.449340711894514</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.945636033657806</v>
+        <v>1.483718864249838</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.2322779744370465</v>
+        <v>0.2064251537935746</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.05096482395471469</v>
+        <v>1.003589375448676</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.00586</t>
+          <t>X &gt; 0.005415</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>166</v>
+        <v>268</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-3.391641913024351</v>
+        <v>-1.740175289793612</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.608005945150282</v>
+        <v>-2.240250271746334</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>-0.6076650709085456</v>
+        <v>0.3279413064615966</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-1.076214333510627</v>
+        <v>0.08779607967958469</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.7805740322555224</v>
+        <v>0.6606176376950046</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>3.220718516684983</v>
+        <v>-0.8938601845217562</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>3.135984799412704</v>
+        <v>1.451554748790898</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.463982123522783</v>
+        <v>2.686478004244009</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-1.609065955430609</v>
+        <v>0.7598242059301867</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.04955258624167413</v>
+        <v>1.029308394674963</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>0.9505133665491883</v>
+        <v>2.317144549847605</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.189715801003054</v>
+        <v>2.72465703056114</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.03776772560449615</v>
+        <v>1.558237520531314</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>0.2119536066717913</v>
+        <v>1.037704514041422</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.006503</t>
+          <t>X &gt; 0.005994</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>129</v>
+        <v>205</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-5.570361397133055</v>
+        <v>-2.966352923738235</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-2.566550394712699</v>
+        <v>-0.6940438711709973</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>-2.961419101309289</v>
+        <v>0.3674954236856109</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-2.831165968701789</v>
+        <v>0.9831574604778552</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-1.831125645312412</v>
+        <v>2.87205237340158</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.3470408930469659</v>
+        <v>1.71311572342502</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>1.893806785029597</v>
+        <v>3.85431111836202</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>1.426623386248096</v>
+        <v>2.899437596526504</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.959957895283047</v>
+        <v>0.3994310497598335</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.5154983150378669</v>
+        <v>0.5251220095275215</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>1.085938789169901</v>
+        <v>2.271640363462453</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.67070954341456</v>
+        <v>1.818213637768999</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.07512646287918301</v>
+        <v>0.4224530283580279</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1745948693971044</v>
+        <v>0.1603838005357758</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.007146</t>
+          <t>X &gt; 0.006573</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>100</v>
+        <v>167</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-5.958784854863438</v>
+        <v>-3.671392221010542</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-2.619863418322744</v>
+        <v>0.6698026383065852</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>-2.024633115018347</v>
+        <v>0.2750312535515462</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>-0.9042809725098522</v>
+        <v>0.4052563971399081</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-1.442702187582022</v>
+        <v>1.652681129758491</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>1.389393215480176</v>
+        <v>-0.4308972215588014</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>3.304659498207883</v>
+        <v>2.203953297418551</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>4.837476099426389</v>
+        <v>2.335687048841386</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1.776476213244081</v>
+        <v>0.4782977066898653</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>3.92635102821616</v>
+        <v>0.2271813055695873</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>2.721597703898581</v>
+        <v>1.818887332938147</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.755980861244012</v>
+        <v>1.254463090083881</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.3357262502991034</v>
+        <v>0.2355098415608978</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>1.585447582575391</v>
+        <v>-0.1375569034221584</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.007789</t>
+          <t>X &gt; 0.007152</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-5.657995282235291</v>
+        <v>-4.71972200068361</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-4.737923325579295</v>
+        <v>0.3855098167003277</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-3.866969247365759</v>
+        <v>-0.009261568054711233</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.0607522396721194</v>
+        <v>-0.6253050811827663</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.47766897540005</v>
+        <v>-0.4173259775620437</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-0.1802270376843893</v>
+        <v>-1.612489261359798</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>2.266684814663591</v>
+        <v>1.708703196117391</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>3.06532420069221</v>
+        <v>5.001033048571252</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.7931440399204703</v>
+        <v>1.93253209505599</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>4.68584469910224</v>
+        <v>1.834492997974259</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>3.215268589974528</v>
+        <v>2.381671538962181</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.249651747319959</v>
+        <v>1.66416999206939</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>0.2977515667548118</v>
+        <v>1.244019138755981</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.813295683841218</v>
+        <v>1.469754788982513</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.008432</t>
+          <t>X &gt; 0.00773</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-9.636295463067121</v>
+        <v>-5.311104709779634</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-8.073265901428201</v>
+        <v>-2.205309670767996</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-3.706229846120031</v>
+        <v>-1.656684829107938</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>-0.401373538909354</v>
+        <v>0.3603327673106094</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-4.114397928584701</v>
+        <v>0.7654394406300113</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.9449487710357261</v>
+        <v>-1.767375208980184</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.8602150537634472</v>
+        <v>0.97810311099893</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>1.980333242283528</v>
+        <v>2.397826920042384</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-4.429872993105121</v>
+        <v>-0.4933439157256814</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>2.656509758374895</v>
+        <v>1.486925967189748</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.86445484675572</v>
+        <v>2.225621035344645</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.486139591402747</v>
+        <v>1.316602961284879</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>0.4785833931562493</v>
+        <v>1.839848334386559</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>2.315606312734133</v>
+        <v>1.122187758198002</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.009075</t>
+          <t>X &gt; 0.008309</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-9.015177450644757</v>
+        <v>-8.433296982915309</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-6.27892497665249</v>
+        <v>-4.092102123598181</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-8.847706726727345</v>
+        <v>-4.48687350835322</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-2.195714463685064</v>
+        <v>-0.7852197933362888</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-7.08196176571375</v>
+        <v>-2.513985536908166</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.91113234591495</v>
+        <v>1.35481706415549</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>4.000311672120937</v>
+        <v>1.270106704889322</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>1.359215229861171</v>
+        <v>3.183990442054963</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-7.39743683023417</v>
+        <v>-1.63889647637258</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-1.725822884827323</v>
+        <v>1.08261329872613</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-1.930576209144903</v>
+        <v>2.068388330942135</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.2777199916787936</v>
+        <v>2.102766483297458</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-2.316447662744373</v>
+        <v>2.873091820460239</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-2.066726330468086</v>
+        <v>3.098827470686771</v>
       </c>
     </row>
   </sheetData>
@@ -3815,7 +3815,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Measures the winrate at horizon h days, given that DXY Ret-1 is below threshold x, minus the unconditional baseline winrate.</t>
+          <t>Measures the winrate at horizon h, given that DXY Ret-1 is below threshold x, minus the unconditional baseline winrate.</t>
         </is>
       </c>
     </row>
@@ -3904,1561 +3904,1561 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.009573</t>
+          <t>X &lt; -0.008476</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1.854387766746541</v>
+        <v>2.280988731370414</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-14.97457715056554</v>
+        <v>-8.85400688550294</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-11.0216197702056</v>
+        <v>-6.867825889305607</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-15.23919272455463</v>
+        <v>-6.737600745717245</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-15.7776139396268</v>
+        <v>-9.656842679765312</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-17.6540850453894</v>
+        <v>-5.788040078701655</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-6.869253545270368</v>
+        <v>-2.301321866539247</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-7.336436944051869</v>
+        <v>0.8030380611025834</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-3.049610743277654</v>
+        <v>-0.4484202858963826</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.899735928305581</v>
+        <v>-1.298339082226242</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.2433368343333626</v>
+        <v>0.8779121404659378</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-8.417932182234246</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-11.01209983665741</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-8.58846546090286</v>
+        <v>-4.044029672170367</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.00893</t>
+          <t>X &lt; -0.007897</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>59</v>
+        <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.04893456114596262</v>
+        <v>-0.05373156451493344</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-13.42704583147931</v>
+        <v>-8.46103416243313</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-12.12699928383862</v>
+        <v>-7.884931760780404</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-15.3865766597057</v>
+        <v>-5.812959044376505</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-14.23008262054057</v>
+        <v>-10.23474374310327</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-13.93264068282491</v>
+        <v>-7.024748354244885</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.542798128910754</v>
+        <v>-5.167711140695516</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-4.315066273454967</v>
+        <v>-1.751284638851189</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-4.376066159637269</v>
+        <v>-1.812266795373965</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-3.531276090427902</v>
+        <v>-1.69131180529606</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>1.348716347966381</v>
+        <v>-0.9251391771484876</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-7.091476765874631</v>
+        <v>-4.774256170424231</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-9.20664663105682</v>
+        <v>-4.223533237329868</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-7.262010044543246</v>
+        <v>-1.085176227880041</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.008287</t>
+          <t>X &lt; -0.007318</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.7533149265432684</v>
+        <v>0.6440839694656475</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-13.84527167343397</v>
+        <v>-8.779602123598181</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-11.64273778262797</v>
+        <v>-8.39312350835322</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-8.915082052617869</v>
+        <v>-5.137898364764858</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-12.05090586509264</v>
+        <v>-8.801187917860553</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-10.45476262867567</v>
+        <v>-7.722563888225466</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.344691151142761</v>
+        <v>-5.463524247491634</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.513173251222966</v>
+        <v>-4.368092891278373</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3.275471838703972</v>
+        <v>-4.429075047801149</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.826895725030596</v>
+        <v>-2.935243844131008</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-3.139945002391201</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-8.192071086807935</v>
+        <v>-6.230566850035878</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-8.612325697752837</v>
+        <v>-6.650717703349287</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-4.466500469372662</v>
+        <v>-3.299982053122754</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.007644</t>
+          <t>X &lt; -0.006739</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
+        <v>166</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.96712253073629</v>
+        <v>0.5311321622367373</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-11.9997487752795</v>
+        <v>-4.694511762152402</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.39461748187609</v>
+        <v>-7.498921701124303</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-10.15910119137385</v>
+        <v>-4.959058003319079</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-12.80278556434076</v>
+        <v>-9.11180538774007</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-9.347448889782989</v>
+        <v>-7.007202442442335</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.221656291265795</v>
+        <v>-5.284683886045855</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.636208111099926</v>
+        <v>-4.546933252724159</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.644576418334857</v>
+        <v>-2.800686493584287</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.442070024415422</v>
+        <v>-3.650605289914147</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-2.594191769785631</v>
+        <v>-3.252896809620111</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-6.770334928229673</v>
+        <v>-4.42333793437323</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-7.190589539174574</v>
+        <v>-6.048308064795073</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-3.782973470056184</v>
+        <v>-1.605704944689016</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.007001</t>
+          <t>X &lt; -0.00616</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
+        <v>199</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-1.673766189062434</v>
+        <v>-3.234684874755459</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-9.842716851207022</v>
+        <v>-6.353408656261493</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-11.05725768895115</v>
+        <v>-8.255717729458745</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.648316031753481</v>
+        <v>-7.120467460242246</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-9.826081509120741</v>
+        <v>-10.17131982740829</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-9.52863957140508</v>
+        <v>-8.36640810933099</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.334684764087193</v>
+        <v>-6.441068217340884</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-6.801868162868693</v>
+        <v>-4.898086609871342</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-4.403851655608371</v>
+        <v>-2.94901851513783</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-4.434304709488757</v>
+        <v>-3.798937311467689</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.819385902658794</v>
+        <v>-3.501125906913821</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-6.244019138755988</v>
+        <v>-4.974285443000703</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-7.483945880848431</v>
+        <v>-6.901973984756324</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.316191761686895</v>
+        <v>-2.65613783201723</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.006358</t>
+          <t>X &lt; -0.005582</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>154</v>
+        <v>249</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-3.792139618911271</v>
+        <v>-2.681719243385764</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-8.001115829278127</v>
+        <v>-4.694511762152402</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-9.694685834576021</v>
+        <v>-7.097315275421494</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-8.915082052617869</v>
+        <v>-5.762270854724697</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-11.40155521574199</v>
+        <v>-8.308592536334444</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-9.805411979325029</v>
+        <v>-8.011218506699358</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-6.643392449844058</v>
+        <v>-7.292716014559907</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-5.162523900573611</v>
+        <v>-4.948539678426961</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-1.976770540002668</v>
+        <v>-4.206308983544119</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-2.826895725030596</v>
+        <v>-5.056227779873979</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-2.382298399997524</v>
+        <v>-3.252896809620111</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.295967190704047</v>
+        <v>-4.42333793437323</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.014923100350245</v>
+        <v>-6.048308064795073</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-1.869097871970062</v>
+        <v>-2.609721008946046</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.005715</t>
+          <t>X &lt; -0.005003</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>187</v>
+        <v>310</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-2.226058641065592</v>
+        <v>-1.190593449889185</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-4.372391612318616</v>
+        <v>-2.479198897791733</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-6.906297752070287</v>
+        <v>-3.841712218030636</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-6.241285261174021</v>
+        <v>-3.388906429280993</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-8.383984551112498</v>
+        <v>-5.217518563021841</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-7.017023896819296</v>
+        <v>-5.887886468870626</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-6.566998255802808</v>
+        <v>-5.004854892652922</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-4.895144221429227</v>
+        <v>-3.213859020310629</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.351866032745221</v>
+        <v>-3.274841176833405</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.201991217773148</v>
+        <v>-4.124759973163265</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-1.732947750646879</v>
+        <v>-2.393977260455721</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.302842668167749</v>
+        <v>-3.004760398422981</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.257856637401424</v>
+        <v>-4.715233832381543</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-0.7995791553925145</v>
+        <v>-1.90885302086469</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.005072</t>
+          <t>X &lt; -0.004424</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>244</v>
+        <v>376</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-1.26393012348867</v>
+        <v>-0.88517134968329</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-3.285339802026691</v>
+        <v>-2.496357442747119</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-3.680208508623281</v>
+        <v>-2.891128827502158</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.959791441589559</v>
+        <v>-3.026861130722303</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-5.317884787809263</v>
+        <v>-3.29919323700949</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-5.430278915667373</v>
+        <v>-4.065648994608438</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.285504436218346</v>
+        <v>-4.150359353874606</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-2.293671441557223</v>
+        <v>-1.957853529576248</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.354671327739524</v>
+        <v>-2.018835686099024</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-3.204796512767452</v>
+        <v>-2.070882142003349</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-1.36036950921617</v>
+        <v>-0.6798386194124788</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.73582241744451</v>
+        <v>-1.709290254291197</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.385585225110724</v>
+        <v>-3.193270894838655</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-1.086683564965583</v>
+        <v>-0.04200332971850429</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X &lt; -0.004429</t>
+          <t>X &lt; -0.003845</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>304</v>
+        <v>463</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-2.493438320209975</v>
+        <v>-0.2130974560203143</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-4.105011933174232</v>
+        <v>-2.040266270466439</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-3.18409116608661</v>
+        <v>-2.003072212456892</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-4.69857487558437</v>
+        <v>-2.952760675779977</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-4.250153985393389</v>
+        <v>-3.059084786111086</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.281659416098783</v>
+        <v>-4.057607084769742</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-4.366393133371062</v>
+        <v>-3.278386558506753</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.201997584784145</v>
+        <v>-2.665541595382045</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.934050102545378</v>
+        <v>-1.862592866375657</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-1.797333182310155</v>
+        <v>-2.928494384087813</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-0.3573496645224665</v>
+        <v>-1.837299214054269</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-1.638755980861255</v>
+        <v>-2.450869225845821</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-2.716905328648259</v>
+        <v>-3.302985521923794</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.164552417424602</v>
+        <v>-0.9174226578743685</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003786</t>
+          <t>X &lt; -0.003267</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>382</v>
+        <v>555</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-1.184537796649764</v>
+        <v>-0.4088439584622776</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-3.057891514326066</v>
+        <v>-1.299309330805386</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-2.405639802074482</v>
+        <v>-1.153540175019884</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-4.63140761187536</v>
+        <v>-2.10439611251261</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-4.122708408099363</v>
+        <v>-1.921964944887577</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-4.610606784519831</v>
+        <v>-3.066032356693938</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-3.648220082943944</v>
+        <v>-1.889481454698839</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-2.806502958165233</v>
+        <v>-1.275469017404497</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-1.820382425499368</v>
+        <v>-0.6157304532065595</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-2.932287715239333</v>
+        <v>-1.105288889176052</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-1.566360411284663</v>
+        <v>-0.5892693267155309</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-2.579097672787405</v>
+        <v>-1.455792075261108</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-3.261132388444345</v>
+        <v>-2.776843829475411</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-1.440730427895808</v>
+        <v>-0.2087658369065366</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>X &lt; -0.003143</t>
+          <t>X &lt; -0.002688</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>458</v>
+        <v>667</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.7467134293802786</v>
+        <v>-0.3070029870560944</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-2.576627653698253</v>
+        <v>-0.5688637427885936</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-1.879793303526284</v>
+        <v>-0.8137100900623579</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.496265061748474</v>
+        <v>-0.983335021436524</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.942983220052085</v>
+        <v>-1.22177449956969</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-4.173925561812403</v>
+        <v>-2.123800769784694</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-2.075253165547572</v>
+        <v>-1.009110829200772</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-1.232392896206797</v>
+        <v>-0.426704210618702</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.2016897256205468</v>
+        <v>-0.1878362921789574</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-1.051814910648474</v>
+        <v>-0.5879799760650428</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.6015464009049083</v>
+        <v>0.2567941280435804</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-1.440525688974326</v>
+        <v>-0.6083779444886446</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-2.297461522626655</v>
+        <v>-1.628228947727095</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.301015299520671</v>
+        <v>-0.0531679601692332</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X &lt; -0.0025</t>
+          <t>X &lt; -0.002109</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>567</v>
+        <v>813</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.8179533113916335</v>
+        <v>-0.2053932753067969</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1.547692709188347</v>
+        <v>0.1514403118261711</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.413460886684398</v>
+        <v>-1.350342143039562</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.635941440143917</v>
+        <v>-1.466119459475799</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.468895283082048</v>
+        <v>-1.512404092522303</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.876920717500425</v>
+        <v>-1.461032522911808</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.7270865335381416</v>
+        <v>-0.6847342720918803</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.3930316549819466</v>
+        <v>-0.1677930757802173</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>1.213865983967189</v>
+        <v>0.263229687746211</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.7164744850062803</v>
+        <v>-0.09468418853445826</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>1.217188532822739</v>
+        <v>-0.1763841167823514</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.01700378893360721</v>
+        <v>-0.01900473441471462</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.4032508220112945</v>
+        <v>-0.931160507777328</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.1992041963320119</v>
+        <v>0.03258252252300053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.001857</t>
+          <t>X &lt; -0.00153</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>690</v>
+        <v>966</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-0.7543078854273659</v>
+        <v>-1.135160336952566</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-1.206461208536552</v>
+        <v>-0.7794727240122583</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-2.181040060060674</v>
+        <v>-1.58832278371554</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-2.050786927453174</v>
+        <v>-1.147538633916</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-2.734135678757234</v>
+        <v>-1.892867524485808</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-1.567128523650261</v>
+        <v>-0.974375482428357</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.2025868786037037</v>
+        <v>0.2866698518872468</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.05486740377421739</v>
+        <v>0.3371995517858082</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.8634327349832134</v>
+        <v>0.6902960702112679</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.131619986276597</v>
+        <v>-0.05610305738152732</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.0984092981014868</v>
+        <v>-0.05376487816759834</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.3019901532487452</v>
+        <v>-0.2264260632863966</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.012099836657413</v>
+        <v>-1.164175260285106</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.7623785043811253</v>
+        <v>-0.2138019288991515</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.001214</t>
+          <t>X &lt; -0.0009514</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>809</v>
+        <v>1110</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.9483208912853698</v>
+        <v>-0.6823548794552181</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-1.694628744051855</v>
+        <v>-0.7647639941017772</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.842278662020512</v>
+        <v>-0.8897512061949442</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.712025529413012</v>
+        <v>-1.119238292822409</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.879618561543282</v>
+        <v>-1.657527845918104</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.211348440885715</v>
+        <v>-1.360153816283017</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.434449362237558</v>
+        <v>0.08391280286808467</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.3380941463979639</v>
+        <v>-0.2032997258107443</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.6479224431575545</v>
+        <v>0.5450706356520882</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.3258121361843322</v>
+        <v>0.1953817184252458</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.4069560661879521</v>
+        <v>0.2607075628653206</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.8670104860983869</v>
+        <v>0.1150677134204727</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-1.534483885671222</v>
+        <v>-0.9750420276736165</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-1.037543764767001</v>
+        <v>-0.118675746816443</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0005706</t>
+          <t>X &lt; -0.0003727</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>951</v>
+        <v>1294</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.1873586556397484</v>
+        <v>-0.7860007762970653</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-1.27482325392895</v>
+        <v>-0.7022716151235997</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-0.7262957341104439</v>
+        <v>-1.02000139741331</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-1.224973419113006</v>
+        <v>-0.8127346513596265</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-1.029642013640107</v>
+        <v>-0.7346913847326633</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8370218788594528</v>
+        <v>-0.8225253674242339</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.3361060390883921</v>
+        <v>0.01726350289357015</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.28319546405735</v>
+        <v>-0.3727635384278329</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.810054387430867</v>
+        <v>0.6879016291456566</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>-0.3548661805981084</v>
+        <v>0.03543516821466852</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.2448241219146396</v>
+        <v>0.139375985263122</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.4667082143862373</v>
+        <v>0.09659364379128021</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.248921488922761</v>
+        <v>-1.129482182113762</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.6837427433972678</v>
+        <v>-0.01076257862506935</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 7.239e-05</t>
+          <t>X &lt; 0.0002061</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1118</v>
+        <v>2786</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.1381406271584424</v>
+        <v>0.07722350434936942</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-1.116608721755853</v>
+        <v>0.4696152288168491</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.708622834240046</v>
+        <v>-0.03249068187737691</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.7567818336575272</v>
+        <v>-0.2048946067118891</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.9383787846797418</v>
+        <v>-0.4731692103775558</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.640936846964081</v>
+        <v>-0.08466990541744934</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.07718402987604378</v>
+        <v>0.2604191622504857</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.8768096148593258</v>
+        <v>-0.1350162437138991</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.3121904989583797</v>
+        <v>1.185232100174488</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.3593632574981243</v>
+        <v>0.6422651164424664</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.4748308675299882</v>
+        <v>0.206908708616325</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.9267715963073755</v>
+        <v>0.4408822173959805</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-1.923665520720562</v>
+        <v>-0.1383388013040729</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.8689352439004523</v>
+        <v>-0.07178750897343633</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007154</t>
+          <t>X &lt; 0.0007849</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1268</v>
+        <v>2955</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.6066458673797896</v>
+        <v>-0.2879335743940032</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-1.589288662733985</v>
+        <v>0.1251718305178855</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.7262957341104439</v>
+        <v>-0.2695995542371534</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.2029608404966581</v>
+        <v>-0.1885754656761023</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.1910675901600243</v>
+        <v>-0.2696847105681854</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.3653237656519011</v>
+        <v>-0.0889519328050028</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1002569824846162</v>
+        <v>-0.004800421081640138</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.4024924292911578</v>
+        <v>-0.33677956807675</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.5593243643062493</v>
+        <v>0.9045398170637142</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-0.133444408447879</v>
+        <v>0.5805131683732228</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.2595195266285657</v>
+        <v>0.2597338346608637</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8109482726142545</v>
+        <v>0.3808636538532042</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-1.502729226454235</v>
+        <v>-0.02013583596092161</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.8940476855634074</v>
+        <v>-0.01212249305506674</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001358</t>
+          <t>X &lt; 0.001364</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1423</v>
+        <v>3132</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.2045294443310226</v>
+        <v>-0.04538594457446976</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-1.757429592599607</v>
+        <v>-0.0647223082527475</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.6806795185374597</v>
+        <v>-0.3639827092446524</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.5007298859691147</v>
+        <v>0.006408960075908965</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.2426170100700489</v>
+        <v>-0.3234183256337246</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.4410202393201104</v>
+        <v>-0.2635932062624349</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2450939761336031</v>
+        <v>-0.06149668216339421</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.5341929047811789</v>
+        <v>-0.3373607370400009</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.2463219355442234</v>
+        <v>0.6710903171972618</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.3934245678567692</v>
+        <v>0.3491949313791949</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.3176729833384471</v>
+        <v>0.1305892878799284</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.7352472089314261</v>
+        <v>0.2467783956565199</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-1.327195098015501</v>
+        <v>-0.1553458552803448</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.8980380112404873</v>
+        <v>-0.1350714528673223</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.002001</t>
+          <t>X &lt; 0.001942</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1561</v>
+        <v>3295</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.4139099226015261</v>
+        <v>-0.1359841092030365</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-1.900539089723758</v>
+        <v>-0.173796526018748</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.3145771253938321</v>
+        <v>-0.09825365363166583</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1990625886833257</v>
+        <v>0.1392644417746567</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.1718234822373574</v>
+        <v>-0.1099591171337195</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.2975077429862907</v>
+        <v>0.05254214025075044</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.3845317026807393</v>
+        <v>0.2101825837716262</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>-0.1113730054329451</v>
+        <v>0.01575859312029593</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.147320203013912</v>
+        <v>0.6381598006836953</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-0.4470505063106955</v>
+        <v>0.350789802428551</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-0.1402948792216279</v>
+        <v>0.3148002977907254</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.9017286717054418</v>
+        <v>0.184355806924998</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-1.350573365577965</v>
+        <v>-0.1276594509221027</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-1.129478746700705</v>
+        <v>-0.1882597465977227</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.002644</t>
+          <t>X &lt; 0.002521</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1698</v>
+        <v>3446</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>0.3855276022342125</v>
+        <v>-0.2239715860899096</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-1.519818043632519</v>
+        <v>-0.3305280495241121</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.02420866692717283</v>
+        <v>-0.044037039467554</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.4482338324371469</v>
+        <v>0.1019503613497932</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.6148654963308928</v>
+        <v>-0.01512326393643093</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.3247633682416193</v>
+        <v>0.2112426007664254</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.8863281233547724</v>
+        <v>0.3293132380240138</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.3342427073041137</v>
+        <v>0.1519317321283395</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.390820716477478</v>
+        <v>0.6285622312484023</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-0.04778183480559051</v>
+        <v>0.4035242718110155</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.2177764222995151</v>
+        <v>0.3311698134974677</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.3616661975795168</v>
+        <v>0.2369505513562302</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>-0.513596880954573</v>
+        <v>0.007245743125913862</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.5252709097685369</v>
+        <v>-0.09880677744079946</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.003287</t>
+          <t>X &lt; 0.0031</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1790</v>
+        <v>3566</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.4051124044277046</v>
+        <v>-0.2437795652099695</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-1.485168008982491</v>
+        <v>-0.3448985441798342</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.1823936077208117</v>
+        <v>-0.1372231587028736</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.08968129997157348</v>
+        <v>-0.04775077103234793</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.5546045665047572</v>
+        <v>0.1008639293266924</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1831501831501825</v>
+        <v>0.1896701543277217</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.5443473465913939</v>
+        <v>0.1889463572116199</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.1079724742172488</v>
+        <v>0.02982844130841045</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-0.06457230878602616</v>
+        <v>0.3203386318404071</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-0.4127454581195877</v>
+        <v>0.2142659597905592</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.1155467467428011</v>
+        <v>0.05335143918907193</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.6078584244702796</v>
+        <v>0.04746005579371371</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.494536172928143</v>
+        <v>0.03557329749175153</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.4927647079273925</v>
+        <v>0.0528642732933946</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.00393</t>
+          <t>X &lt; 0.003679</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1874</v>
+        <v>3672</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.8611942676494522</v>
+        <v>-0.1452289039727077</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-1.016620026890948</v>
+        <v>-0.2898207547768905</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.2392034922845596</v>
+        <v>-0.153811840328224</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.209712215946368</v>
+        <v>-0.09034401693877214</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.5765093182330858</v>
+        <v>-0.01589469959471757</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.3947180291116865</v>
+        <v>0.02451332765272696</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.5229768571003319</v>
+        <v>-0.06019703161344125</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>0.08521184796128978</v>
+        <v>-0.1466240223278561</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.2421705635273526</v>
+        <v>-0.002275007007028762</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.506254192881336</v>
+        <v>-0.1026812761223113</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.1249659615249641</v>
+        <v>-0.2921558867449434</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.7003091174340312</v>
+        <v>-0.2425428979400692</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.3442737497008892</v>
+        <v>-0.1846137011712372</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.3846698133691078</v>
+        <v>-0.2158317263253693</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.004573</t>
+          <t>X &lt; 0.004258</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1951</v>
+        <v>3759</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7034926260815908</v>
+        <v>-0.06712292708607492</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-1.010382777164004</v>
+        <v>-0.1255327417992902</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.3338789510220153</v>
+        <v>0.07788233028797009</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.4129811884888497</v>
+        <v>0.03676814704824949</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.3349180296826617</v>
+        <v>0.01743595362112416</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.427756386835668</v>
+        <v>0.1434719683482371</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>0.4964753549853853</v>
+        <v>-0.1006009407187278</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.1471707787721712</v>
+        <v>-0.2755049098706692</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.3617018829688092</v>
+        <v>-0.05623365566511751</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.4953480505965331</v>
+        <v>-0.1208337989542869</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.03479943018535181</v>
+        <v>-0.2043389417851458</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.6884635832004307</v>
+        <v>-0.1550550180762897</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.2605852251107237</v>
+        <v>-0.08156876717907835</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.3919998802641729</v>
+        <v>-0.1334151470307035</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.005217</t>
+          <t>X &lt; 0.004836</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2019</v>
+        <v>3827</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.090348135548801</v>
+        <v>0.04644196842343717</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.6200885520570765</v>
+        <v>0.03872925508308356</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.1713996370457949</v>
+        <v>0.02303264388869763</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.3016527696532947</v>
+        <v>0.03709348660411393</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>0.3069784651100278</v>
+        <v>-0.06969013486629194</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.3078311789008339</v>
+        <v>0.1376304765019043</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.2725289989493618</v>
+        <v>-0.02534755821430679</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.167469498991025</v>
+        <v>-0.1793455002008884</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.3768373376955765</v>
+        <v>0.0349776661863288</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.4356667759381452</v>
+        <v>0.03477051243385887</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.09640427434078447</v>
+        <v>-0.1030651068298383</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.627987471264646</v>
+        <v>-0.1062524076227191</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-0.3276400863345614</v>
+        <v>0.01072430292030191</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.1986039280734389</v>
+        <v>-0.06229587596048702</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.00586</t>
+          <t>X &lt; 0.005415</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2085</v>
+        <v>3909</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.142925316153665</v>
+        <v>0.1211247857921833</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-0.7078827465713573</v>
+        <v>0.1819473788259103</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.2369614654923424</v>
+        <v>0.005214291544682226</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.3193677081476878</v>
+        <v>0.02170241389227812</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.2115685026448872</v>
+        <v>-0.01751197301887686</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.07838843079117908</v>
+        <v>0.0895370057719731</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>0.06770401711645491</v>
+        <v>-0.07180170598460478</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.03800282777667263</v>
+        <v>-0.1557285873192455</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.3384663154915444</v>
+        <v>-0.02381508357018447</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.4223079756152543</v>
+        <v>-0.04184363968429494</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.004455935948158185</v>
+        <v>-0.1299756772378302</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.5660124305624024</v>
+        <v>-0.157951150726241</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.2884348235263943</v>
+        <v>-0.0778276777738327</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.2035212423646442</v>
+        <v>-0.04227547855124669</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.006503</t>
+          <t>X &lt; 0.005994</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2122</v>
+        <v>3972</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.19720577946093</v>
+        <v>0.154626138140344</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.7434698551300443</v>
+        <v>0.06305730396897502</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3661278228525973</v>
+        <v>0.008355020024481519</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.4023518064238942</v>
+        <v>-0.02356622459907243</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>0.3810909110508334</v>
+        <v>-0.1210685711268766</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>0.3494308271397841</v>
+        <v>-0.06124823102516785</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>0.1964751143885053</v>
+        <v>-0.1710905329905046</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.009582724103019302</v>
+        <v>-0.1216908048027534</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>-0.3999943749912092</v>
+        <v>0.007175580813388649</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>-0.4501195600191323</v>
+        <v>0.001124365124525184</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>0.003950645075050829</v>
+        <v>-0.08884437346038965</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.5472206453473234</v>
+        <v>-0.06549387570271392</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>-0.2817961236999551</v>
+        <v>0.006720001156125477</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>-0.1940057633247037</v>
+        <v>0.02013375755197444</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.007146</t>
+          <t>X &lt; 0.006573</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2151</v>
+        <v>4010</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.124372440457932</v>
+        <v>0.1545886934835465</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.7654943079423191</v>
+        <v>-0.001079989800622627</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2774848518803879</v>
+        <v>0.01561405383583292</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.2685914167698868</v>
+        <v>0.01010953521025471</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>0.3331386618090377</v>
+        <v>-0.04177714135482802</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.2595230856100414</v>
+        <v>0.04520434677578322</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>0.1538474332426958</v>
+        <v>-0.06440021214186942</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.1485963239719368</v>
+        <v>-0.06966161637797796</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-0.5345729975265741</v>
+        <v>0.007607704378180813</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-0.5954688417931209</v>
+        <v>0.01848062024367891</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.05741808068823673</v>
+        <v>-0.04765120722548488</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.5078370672278893</v>
+        <v>-0.02418599260816023</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-0.2981027459834209</v>
+        <v>0.0184421071717793</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.2546268014320461</v>
+        <v>0.03387081470766873</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.007789</t>
+          <t>X &lt; 0.007152</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2172</v>
+        <v>4044</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.041915215143561</v>
+        <v>0.15715103060964</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>-0.7073994446526513</v>
+        <v>0.01393979995299333</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.3210559993476352</v>
+        <v>0.02718667911594963</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.2217407205685404</v>
+        <v>0.04749671295535052</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.2801973751015083</v>
+        <v>0.04089623811181298</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.3273812724392897</v>
+        <v>0.0802934309549812</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>0.2219389099726001</v>
+        <v>-0.0291021912092404</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.03608711896441008</v>
+        <v>-0.1369972122660315</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.4189260856064863</v>
+        <v>-0.03620798185894358</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.5793960982206201</v>
+        <v>-0.03257585994128931</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.04851723863015422</v>
+        <v>-0.05046514076530428</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.4942491295563585</v>
+        <v>-0.02690891627413805</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.2905968053842827</v>
+        <v>-0.01289322868921516</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.2451233198187097</v>
+        <v>-0.02043210257873795</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.008432</t>
+          <t>X &lt; 0.00773</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2188</v>
+        <v>4071</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>1.107290941412629</v>
+        <v>0.1390643808270582</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-0.6410192257904512</v>
+        <v>0.08374896628670569</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.2858987585883384</v>
+        <v>0.06971639855515832</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.2338364855440602</v>
+        <v>0.01727959406876778</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.3790980416660616</v>
+        <v>0.007022866453176846</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.2913539997938983</v>
+        <v>0.07269843097041928</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.2772872354341658</v>
+        <v>0.0013942174421544</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>0.0177590752365262</v>
+        <v>-0.03528843947557903</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.3170883691383821</v>
+        <v>0.0399202907660765</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.4825946586847962</v>
+        <v>-0.01116408952977821</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>0.04291217217790688</v>
+        <v>-0.03028619041280223</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.4449323807651169</v>
+        <v>-0.006653272820067002</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.2915007940133592</v>
+        <v>-0.02006937329034741</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.244534135888955</v>
+        <v>-0.00149887945535454</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.009075</t>
+          <t>X &lt; 0.008309</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2205</v>
+        <v>4093</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.011762946185321</v>
+        <v>0.1737356986424601</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-0.7354958770910116</v>
+        <v>0.110090324635685</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.3621727297452253</v>
+        <v>0.1183896495415127</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.2662838451659368</v>
+        <v>0.04257171810133542</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.4062886816541535</v>
+        <v>0.07824589491369949</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>0.2762710435344715</v>
+        <v>-0.0011239955163731</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.2163842605437907</v>
+        <v>0.0006525817766629416</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>0.04580943275972515</v>
+        <v>-0.03834020769701851</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-0.2869295838573649</v>
+        <v>0.06053878821641945</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>-0.3671272326534094</v>
+        <v>0.005169873223152877</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>0.107467269115979</v>
+        <v>-0.014945002391201</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.3763254368982629</v>
+        <v>-0.0156706351396636</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.2272837225023352</v>
+        <v>-0.03127461590424474</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.1333732791026137</v>
+        <v>-0.03602529768664198</v>
       </c>
     </row>
   </sheetData>

--- a/workspaces/btc_daily_14days/dxy/dxy_ret_1.xlsx
+++ b/workspaces/btc_daily_14days/dxy/dxy_ret_1.xlsx
@@ -568,521 +568,521 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X ≈ -0.008186</t>
+          <t>X ≈ -0.008183</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-10.34279440362248</v>
+        <v>-8.040182274133208</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-6.703325084065966</v>
+        <v>-4.080654824883602</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-12.34781939271741</v>
+        <v>-10.01512932659202</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-1.720442818013666</v>
+        <v>-4.346129206448438</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-12.7609880793614</v>
+        <v>-10.37856109458233</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-12.46753349365233</v>
+        <v>-10.10905597178246</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-17.80944172481885</v>
+        <v>-15.7182917782654</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>-13.02488189233319</v>
+        <v>-10.63998949626518</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-7.832247166736138</v>
+        <v>-5.130729301263656</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-3.425248858529784</v>
+        <v>-5.95502520761746</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-8.889970606853289</v>
+        <v>-6.16049728743284</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.66342960911642</v>
+        <v>-0.5509755876135998</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>6.505620458345774</v>
+        <v>4.607991652473089</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>11.9960705784538</v>
+        <v>10.41368337311057</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X ≈ -0.007607</t>
+          <t>X ≈ -0.007604</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>3.507829733827386</v>
+        <v>1.331787226413219</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-10.06157211156921</v>
+        <v>-11.75015151447443</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-10.457849866651</v>
+        <v>-12.14580966700336</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-2.35041561612185</v>
+        <v>-4.346010110696085</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-2.887885149931499</v>
+        <v>-4.835043640257666</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-10.57626427203917</v>
+        <v>-12.24138748304371</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-6.67047037646914</v>
+        <v>-8.465548752659288</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-15.12682167564004</v>
+        <v>-16.61389510106778</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-15.19147556872295</v>
+        <v>-12.81350440536232</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-8.052219707831654</v>
+        <v>-9.797328954564136</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-12.25582660266288</v>
+        <v>-10.00376137302361</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-12.22445537003126</v>
+        <v>-9.948051071918719</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-16.64657319073943</v>
+        <v>-14.19080759393048</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-12.42498205312457</v>
+        <v>-10.09913713970818</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X ≈ -0.007029</t>
+          <t>X ≈ -0.007026</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.1501145601323159</v>
+        <v>1.538951187774408</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>9.039655624010116</v>
+        <v>10.74047343978483</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-4.473804991109645</v>
+        <v>-3.126293489521117</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-4.345344075917346</v>
+        <v>-2.99783637603025</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-10.13467171495891</v>
+        <v>-8.879868859520208</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-4.587873658497386</v>
+        <v>-3.215297692729919</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-4.673769618913255</v>
+        <v>-3.276841240355154</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-5.141404987419115</v>
+        <v>-3.74289680561278</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>2.681277666055188</v>
+        <v>1.617868105517289</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-6.054086327858833</v>
+        <v>-4.604835573237033</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.630555646737783</v>
+        <v>-4.8100138055553</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.663452553447868</v>
+        <v>0.64966755236496</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-4.018077611927886</v>
+        <v>-5.149341286802525</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>4.101333736352132</v>
+        <v>3.206476165902139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X ≈ -0.00645</t>
+          <t>X ≈ -0.006447</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>33</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-22.10571241067961</v>
+        <v>-22.13500761175722</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-14.65329427080071</v>
+        <v>-14.65460251111961</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-12.02843917803234</v>
+        <v>-12.02868868107481</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-17.94731296782901</v>
+        <v>-17.94793345702934</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-15.46509656439901</v>
+        <v>-15.41676574108104</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-15.17247503446453</v>
+        <v>-15.14865503014445</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-12.23606819048806</v>
+        <v>-12.18820575783647</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-6.654133184230346</v>
+        <v>-6.604992082820253</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-3.690355011255519</v>
+        <v>-3.617207197109138</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-4.540347023256572</v>
+        <v>-4.441116934370136</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-4.746091639295315</v>
+        <v>-4.646272352636416</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-7.74172001522345</v>
+        <v>-7.618099279238869</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-11.19328844209044</v>
+        <v>-11.04464585726077</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-7.94013356827427</v>
+        <v>-7.768134808707607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X ≈ -0.005871</t>
+          <t>X ≈ -0.005869</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>50</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-0.4787935182670537</v>
+        <v>-0.5078958276219723</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1.903134699422417</v>
+        <v>1.901962087381754</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-2.478702268720973</v>
+        <v>-2.478881328737586</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-0.3547712249667327</v>
+        <v>-0.3552722958081276</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-0.89166859303743</v>
+        <v>-0.8432513700306785</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-6.583249560434467</v>
+        <v>-6.559385527268617</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-10.66265046772075</v>
+        <v>-10.61478465165989</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-5.141073923184436</v>
+        <v>-5.091929227722844</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-9.198393458813285</v>
+        <v>-9.12526778342896</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-10.04978783992553</v>
+        <v>-9.950576150304315</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-2.263061341187736</v>
+        <v>-2.163238849591352</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-2.229290749431257</v>
+        <v>-2.105664013372902</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-2.649947945654489</v>
+        <v>-2.501300447976753</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.424982053122754</v>
+        <v>-2.252983293556092</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X ≈ -0.005293</t>
+          <t>X ≈ -0.005291</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>61</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>4.880300496988752</v>
+        <v>5.625763442108145</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>6.544333202202196</v>
+        <v>7.289956616108739</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>9.42210568308537</v>
+        <v>10.16075063177259</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>6.283852986393413</v>
+        <v>6.283400145544888</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>7.384245974112169</v>
+        <v>7.432713764667454</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>2.774850586843236</v>
+        <v>2.798765591358304</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4.327171856022005</v>
+        <v>4.375108738112147</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>3.861588431084265</v>
+        <v>3.910769074986945</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.527078990674795</v>
+        <v>0.600235561740341</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-0.3218453096999738</v>
+        <v>-0.2226098357657733</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>1.111423999051283</v>
+        <v>1.211251310747542</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2.78454618253911</v>
+        <v>2.908178167149103</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.7262502506829236</v>
+        <v>0.8748989582743434</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.9520671272043657</v>
+        <v>1.124065886771774</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X ≈ -0.004713</t>
+          <t>X ≈ -0.004712</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.5478430079612551</v>
+        <v>-0.2701834009847985</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.568129296999551</v>
+        <v>-1.848530466810693</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>1.570158611776606</v>
+        <v>0.7357696635488793</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-1.322080420886593</v>
+        <v>-2.112012511636074</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>5.698684491354868</v>
+        <v>4.844699557463706</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4.484956365935133</v>
+        <v>3.628772206163582</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-0.1357801030647323</v>
+        <v>-0.9004871208494478</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>3.935804425268778</v>
+        <v>3.104414668754742</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>3.87586796844483</v>
+        <v>3.068234391417668</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>7.568533107555353</v>
+        <v>6.718986097652348</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>7.365779378827561</v>
+        <v>6.516567420041333</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>4.373334580158605</v>
+        <v>3.592872760361409</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>3.954409670322541</v>
+        <v>3.198728446460521</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>8.726533098393084</v>
+        <v>7.926121184055852</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X ≈ -0.004135</t>
+          <t>X ≈ -0.004134</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>2.682418576056989</v>
+        <v>3.293529802334909</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-0.06800684833436321</v>
+        <v>-0.602399702334111</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>1.830473409854591</v>
+        <v>2.483895771117233</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-2.624562871720059</v>
+        <v>-2.025210346094696</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-2.015631474778701</v>
+        <v>-1.353871681205256</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.013280360836205</v>
+        <v>-3.402561592524435</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.4900424458222261</v>
+        <v>1.178316505610589</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-5.71446457304674</v>
+        <v>-5.091521629441495</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-1.185433083642096</v>
+        <v>-0.4849387202328828</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-6.627566426287565</v>
+        <v>-5.954246785791909</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-6.834059230294692</v>
+        <v>-6.159994272975275</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-5.6527032794205</v>
+        <v>-4.941318823618047</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.77604472600536</v>
+        <v>-3.012754713249251</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-4.700844122087744</v>
+        <v>-3.92740189820725</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X ≈ -0.003556</t>
+          <t>X ≈ -0.003555</t>
         </is>
       </c>
       <c r="B14" t="n">
         <v>92</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-1.388874797056417</v>
+        <v>-1.418408603992923</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2.422547052149866</v>
+        <v>2.421933583432534</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.113212304902277</v>
+        <v>3.113828092416576</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2.160220762042663</v>
+        <v>2.159739297101183</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>3.792309652767344</v>
+        <v>3.840743068306175</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.921111684127403</v>
+        <v>1.945015694450163</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>5.091339926166725</v>
+        <v>5.139272473277956</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5.711359901864022</v>
+        <v>5.760541177177018</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>5.651799220914818</v>
+        <v>5.724964534357241</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>8.061723920932039</v>
+        <v>8.160972685667318</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>5.687080921692839</v>
+        <v>5.786909213737793</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>3.550266785748967</v>
+        <v>3.673891683294961</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-0.1288209334927899</v>
+        <v>0.01982175540577913</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>3.357626642528928</v>
+        <v>3.52962540209608</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X ≈ -0.002978</t>
+          <t>X ≈ -0.002977</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>112</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.1971614232604608</v>
+        <v>0.1680743888136007</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>3.041138157444692</v>
+        <v>3.040740811008313</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.868194776444561</v>
+        <v>0.868198841147489</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.559933229576863</v>
+        <v>4.55947469744028</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>2.242998741122825</v>
+        <v>2.29141479797179</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.540639614131024</v>
+        <v>2.564545493988533</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>3.347400699163686</v>
+        <v>3.395319456616519</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>3.773164187044522</v>
+        <v>3.822332901716941</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>1.929960445625341</v>
+        <v>2.003105257438413</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>1.973449528309644</v>
+        <v>2.072672473611135</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>4.445644658250089</v>
+        <v>4.54546583759641</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>3.588961447411812</v>
+        <v>3.712582582756674</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>4.062540692186332</v>
+        <v>4.211184367832267</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.7178750897343846</v>
+        <v>0.8898738493012601</v>
       </c>
     </row>
     <row r="16">
@@ -1092,985 +1092,985 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.2580428638756374</v>
+        <v>-0.4571550686383006</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>3.430401457365342</v>
+        <v>2.766346155872874</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-3.78894721527444</v>
+        <v>-3.131041046217781</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-3.660190680886764</v>
+        <v>-3.000798515073193</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-2.831864035719086</v>
+        <v>-2.117321558528928</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.564131379715413</v>
+        <v>2.284602730790539</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.7959844148887996</v>
+        <v>1.225705920713914</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>1.01343344914914</v>
+        <v>1.449235546578208</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>2.320572070833713</v>
+        <v>2.789912984449664</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>2.156540625615065</v>
+        <v>2.656792446072984</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-2.153450438408946</v>
+        <v>-1.680816398547393</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>2.672041861126253</v>
+        <v>3.201651117557034</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>2.252823743134542</v>
+        <v>2.807577544156729</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.4243330153704008</v>
+        <v>0.9883960167885846</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X ≈ -0.001819</t>
+          <t>X ≈ -0.00182</t>
         </is>
       </c>
       <c r="B17" t="n">
         <v>153</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-6.050983223051198</v>
+        <v>-5.77681954752763</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-5.704785925472898</v>
+        <v>-5.412163251266044</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-2.841925986617348</v>
+        <v>-3.854462830681996</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.5448162538756947</v>
+        <v>0.1876383633165659</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-3.902494613569026</v>
+        <v>-4.8690400382985</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>1.608537183719605</v>
+        <v>1.274853367249158</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>5.437022696372331</v>
+        <v>5.129030659261232</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>3.015094610210916</v>
+        <v>2.705287865241026</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>2.954960407195372</v>
+        <v>2.669522689469012</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.1487910726781436</v>
+        <v>-0.1174808477199463</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.5973130495150656</v>
+        <v>0.04410490617420493</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-1.32775539205344</v>
+        <v>-1.857356980590431</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-2.401523236025675</v>
+        <v>-2.906291539898398</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>-1.523021268809025</v>
+        <v>-2.004617280484197</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X ≈ -0.001241</t>
+          <t>X ≈ -0.001242</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>2.333847474953743</v>
+        <v>2.584667419458818</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.6773459564076134</v>
+        <v>-0.349980271055351</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.767499539974182</v>
+        <v>4.007282506624783</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-0.9467286503341938</v>
+        <v>-0.613108244597484</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-0.1085509282912724</v>
+        <v>0.256436404721228</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-3.963115324509715</v>
+        <v>-3.545689043572537</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-1.272371023007722</v>
+        <v>-0.891156986532593</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-3.826139807777693</v>
+        <v>-3.39403059217269</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.4189360711319949</v>
+        <v>-0.03523409520745702</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>1.881633068571773</v>
+        <v>1.860439467313725</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>2.370236360724363</v>
+        <v>2.336119730315005</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>2.405254434471296</v>
+        <v>2.39502537789847</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.2937566205365414</v>
+        <v>-0.03931564230025941</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.519462391321845</v>
+        <v>0.2096017404575079</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X ≈ -0.000662</t>
+          <t>X ≈ -0.0006635</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-1.418420492372555</v>
+        <v>-1.712375340870366</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.3338291282626145</v>
+        <v>-0.6197363172847119</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-1.816855497157938</v>
+        <v>-1.55142099502978</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>1.024778864785667</v>
+        <v>0.7239954715319428</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>4.820301284782111</v>
+        <v>4.524717358422123</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>2.409333255205588</v>
+        <v>2.653498409335491</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>-0.3849931923982055</v>
+        <v>-0.08903349292717166</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-1.401108768457355</v>
+        <v>-1.094049463264113</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>1.554523338273555</v>
+        <v>1.555005677883827</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.9293297032584888</v>
+        <v>-1.121091720761626</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.5919729141799621</v>
+        <v>-0.7879532031226049</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.0144013832256249</v>
+        <v>-0.1927801194982806</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-2.069415622968407</v>
+        <v>-2.200063055245415</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.6402353381814692</v>
+        <v>0.1986296096698439</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X ≈ -8.33e-05</t>
+          <t>X ≈ -8.515e-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.8259206478950034</v>
+        <v>0.8628594876332087</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>1.487070618571884</v>
+        <v>1.519864295646542</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.8243742771186433</v>
+        <v>0.8298858517384602</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.3223963535556962</v>
+        <v>0.2919040584946586</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.2464599356172812</v>
+        <v>-0.1967037441645161</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.5563707839540655</v>
+        <v>0.5432933587543687</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.4719491383059093</v>
+        <v>0.4155509456379463</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.07136047874593032</v>
+        <v>-0.01283696975495019</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1.619514977103485</v>
+        <v>1.523417980446574</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>1.170207645268249</v>
+        <v>1.103047980377589</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.2657243464800771</v>
+        <v>0.1640850804065721</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.7399425333421448</v>
+        <v>0.6236200029193526</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.7219364521467</v>
+        <v>0.5642618159523138</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.1247139566080051</v>
+        <v>-0.258341632471037</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X ≈ 0.0004955</t>
+          <t>X ≈ 0.0004932</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-6.306920111761215</v>
+        <v>-5.97473533089051</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-5.559863712286273</v>
+        <v>-5.238305253547985</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-4.183933107866217</v>
+        <v>-3.889438411607671</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.08188777640210532</v>
+        <v>0.873861037841138</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>3.089852442040652</v>
+        <v>3.285584670792751</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.1590277470585022</v>
+        <v>0.07771052051850802</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-4.383192508092137</v>
+        <v>-4.044166580102157</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-3.670052950449971</v>
+        <v>-2.766933338992146</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-3.731035106972683</v>
+        <v>-2.810187939752893</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-0.4389420689830814</v>
+        <v>0.4305199864066367</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>1.131504701750814</v>
+        <v>1.389121538935555</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.6092650748878867</v>
+        <v>-0.2935968409636587</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>1.929163953455379</v>
+        <v>2.798427677638429</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.9714676510192604</v>
+        <v>1.886551590164842</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X ≈ 0.001074</t>
+          <t>X ≈ 0.001072</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>4.003614311970161</v>
+        <v>3.920295838643987</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-3.235970565010156</v>
+        <v>-3.260641999667605</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-1.939369040963768</v>
+        <v>-1.977730528172565</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>3.265264629140994</v>
+        <v>3.189672318510617</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-1.218868069462417</v>
+        <v>-1.22021508306517</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-3.178468738145604</v>
+        <v>-3.439726597857273</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-1.008895718644055</v>
+        <v>-0.6996522715771931</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.3470830042727258</v>
+        <v>-0.6018024202414054</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-3.232923917857647</v>
+        <v>-3.44811410007226</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-3.517870962775014</v>
+        <v>-3.707096737385918</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-2.027656866798047</v>
+        <v>-1.66720939044221</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-1.993278714442724</v>
+        <v>-1.610879357562524</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-2.413429567756133</v>
+        <v>-2.005552587683624</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-2.187693917529536</v>
+        <v>-2.320399023893174</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X ≈ 0.001653</t>
+          <t>X ≈ 0.00165</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-1.876640732769133</v>
+        <v>-1.279435106203039</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-2.272712136751416</v>
+        <v>-1.629390411074795</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>5.013672160747483</v>
+        <v>5.401652898318559</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>2.692652436132285</v>
+        <v>3.058931650880027</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>3.994147085430299</v>
+        <v>3.806757158160011</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>6.12676746528922</v>
+        <v>5.94057851317001</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>5.434591186491744</v>
+        <v>5.262457576666037</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>6.813847292770703</v>
+        <v>6.650522191919208</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.00439887857914556</v>
+        <v>-0.1917135330397031</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3814739472799644</v>
+        <v>0.2167576215505846</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>3.857754384111942</v>
+        <v>3.727174677391879</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-1.015842923655505</v>
+        <v>-1.171356023674086</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.4044970205771321</v>
+        <v>0.286412411494986</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-1.210258126742417</v>
+        <v>-0.9734801879660679</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X ≈ 0.002231</t>
+          <t>X ≈ 0.002229</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-2.138905089144828</v>
+        <v>-2.870000321754873</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-3.748607598468865</v>
+        <v>-4.474219815878605</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>1.140487219317897</v>
+        <v>0.3523615664478612</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.7133996151152502</v>
+        <v>-1.46403098274363</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>2.054546817866886</v>
+        <v>1.653315755820323</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>3.670340991811223</v>
+        <v>3.236162738571551</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>2.928707894717832</v>
+        <v>2.525710355215793</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>3.128802804085907</v>
+        <v>3.358888578889108</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.4188140250465295</v>
+        <v>0.7227307932310438</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>1.555650195604088</v>
+        <v>1.847127886399043</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.6886973817147606</v>
+        <v>0.9879567068967887</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>1.385327189699183</v>
+        <v>1.406832404475601</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>2.95193130327327</v>
+        <v>2.975096027435107</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>1.853163642241483</v>
+        <v>1.916951346966819</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X ≈ 0.00281</t>
+          <t>X ≈ 0.002807</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>120</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.8050853524714938</v>
+        <v>-0.8403904877549166</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.7507271696854332</v>
+        <v>-0.7560651247366081</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-2.809843240257216</v>
+        <v>-2.815308561163327</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-4.343517674335395</v>
+        <v>-4.350708079164868</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>3.427898281598374</v>
+        <v>3.481579020256952</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.4322510921821774</v>
+        <v>-0.4077349144856939</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-3.844945235741193</v>
+        <v>-3.797183010977292</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-3.482676224611801</v>
+        <v>-3.429042658377888</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-8.543658381134485</v>
+        <v>-8.461422167371751</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-5.22691051079768</v>
+        <v>-5.122263739041877</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-7.931611669057865</v>
+        <v>-7.821223080861252</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-5.397233516702492</v>
+        <v>-5.266462338046793</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.8492822966507063</v>
+        <v>0.9979718444285339</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>4.408351280210631</v>
+        <v>4.580350039777237</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X ≈ 0.00339</t>
+          <t>X ≈ 0.003385</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>3.169117336399815</v>
+        <v>2.725371820968917</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>1.570721822337021</v>
+        <v>1.146674363108033</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.7066166433836543</v>
+        <v>-1.149683232017225</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-1.518640319195441</v>
+        <v>-1.971588954275262</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-3.937566395422088</v>
+        <v>-4.362497781903151</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-5.522759446752531</v>
+        <v>-5.992331869894826</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-8.44097426216323</v>
+        <v>-8.904517568999609</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>-6.092739117693412</v>
+        <v>-6.516260932477856</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-10.87070240629177</v>
+        <v>-11.30898262519567</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-10.77722497620643</v>
+        <v>-11.17942157564701</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-11.92532236088172</v>
+        <v>-12.33151210611703</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-10.0041517556962</v>
+        <v>-10.37232562883262</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-7.594113929764326</v>
+        <v>-7.93059958414289</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-9.255170732367979</v>
+        <v>-9.586316626889428</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X ≈ 0.003968</t>
+          <t>X ≈ 0.003964</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>87</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>3.215182302001708</v>
+        <v>3.195237857835558</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>6.805965326193359</v>
+        <v>6.17814708119537</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>9.840231747133977</v>
+        <v>9.239459563715933</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>5.391831861169003</v>
+        <v>4.778417064271679</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>1.421686807252257</v>
+        <v>0.8408920612508624</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5.148098642582987</v>
+        <v>4.568728050905051</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-1.802834167141299</v>
+        <v>-2.395254371224667</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-5.724055534956534</v>
+        <v>-6.320654008287597</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-2.336761829410307</v>
+        <v>-2.898059740744806</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.8878300510276276</v>
+        <v>-1.441103370224077</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>3.505169940137471</v>
+        <v>4.081558792722333</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>3.539548092492794</v>
+        <v>4.144241935931461</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>4.268822526535708</v>
+        <v>4.417512074313599</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>3.345132889405917</v>
+        <v>3.517131648972615</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X ≈ 0.004547</t>
+          <t>X ≈ 0.004542</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>68</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>6.310066271477332</v>
+        <v>6.313417586877726</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9.099106177904261</v>
+        <v>9.142005207604178</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-3.001643052534511</v>
+        <v>-3.016438663063425</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.05440014554836381</v>
+        <v>0.05462184873948672</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-4.866528826951445</v>
+        <v>-4.846391998094823</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-0.1905738194706785</v>
+        <v>-0.1618417733935047</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>4.132775751048456</v>
+        <v>4.189266843263397</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>5.144774755780446</v>
+        <v>5.194022318174206</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>5.083792599257713</v>
+        <v>5.157049709037366</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>8.645638508810123</v>
+        <v>8.744985834104739</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>5.499760879961741</v>
+        <v>5.599668915980374</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>2.592962561728832</v>
+        <v>2.716659182757077</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>5.113988179003655</v>
+        <v>5.262677726781483</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>3.869135593936065</v>
+        <v>4.04113435350277</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X ≈ 0.005125</t>
+          <t>X ≈ 0.00512</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.586208466468221</v>
+        <v>4.11639419920941</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>6.831668098952548</v>
+        <v>7.352494222487316</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>-0.8217671603200856</v>
+        <v>-0.2701594284780242</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.6936463938360902</v>
+        <v>-0.1402753872633156</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>2.412126630057685</v>
+        <v>2.984933303110033</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-2.151353820064237</v>
+        <v>-1.561558286504798</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-2.232723348398608</v>
+        <v>-1.622214375730223</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>0.9482180843314225</v>
+        <v>1.526410695211737</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-2.771300657557212</v>
+        <v>-2.125019745250363</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-3.621219453887072</v>
+        <v>-2.948848326065345</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-1.386896221903392</v>
+        <v>-0.743350219384574</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-2.572030264670019</v>
+        <v>-1.890002759128052</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>-4.211693313105414</v>
+        <v>-3.489979962800341</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>0.892091117608949</v>
+        <v>1.578342007648722</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X ≈ 0.005704</t>
+          <t>X ≈ 0.005699</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.249767804788071</v>
+        <v>2.177388175113016</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-7.271556813300975</v>
+        <v>-7.21828891004288</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.1992334647009173</v>
+        <v>0.2004731016424586</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>-2.825681429267135</v>
+        <v>-2.79464285714284</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-6.535320788016897</v>
+        <v>-6.408891998094781</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-9.376877027840621</v>
+        <v>-9.26110647927581</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-6.366938199813568</v>
+        <v>-6.196762568501292</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>1.993514251578723</v>
+        <v>1.149904671115344</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>1.932532095055926</v>
+        <v>1.112932061978569</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>2.669914886027748</v>
+        <v>1.851603481163565</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.465213727767555</v>
+        <v>1.647463033627538</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>5.674195054726027</v>
+        <v>4.830629770992324</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>5.254044201412668</v>
+        <v>4.435471844428498</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>3.892478264337583</v>
+        <v>3.122016706443908</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X ≈ 0.006284</t>
+          <t>X ≈ 0.006277</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>38</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.1321092511163968</v>
+        <v>0.1214671224814339</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-6.687790373348783</v>
+        <v>-6.724867857411262</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7738511187485031</v>
+        <v>0.7761309963793082</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>3.522880554620954</v>
+        <v>3.537593984962356</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>8.230868102043623</v>
+        <v>8.311502738747322</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>11.13548840269608</v>
+        <v>11.21586720493468</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>11.10719943671886</v>
+        <v>11.15521111570918</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>5.376972898195312</v>
+        <v>5.426220460589029</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.05283284693572909</v>
+        <v>0.1260899567153473</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>1.834492997974209</v>
+        <v>1.933840323268832</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>4.261370787082406</v>
+        <v>4.361278823101124</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>4.295748939437807</v>
+        <v>4.419445560466052</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>1.244019138755981</v>
+        <v>1.392708686533808</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>1.469754788982463</v>
+        <v>1.641753548549175</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X ≈ 0.006863</t>
+          <t>X ≈ 0.006856</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>34</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.4294272112399611</v>
+        <v>0.4310646457012766</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>1.781889264001613</v>
+        <v>1.789064031133634</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.387117879246574</v>
+        <v>1.39532604281893</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>4.43657041528445</v>
+        <v>4.466386554621849</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>9.750061873100556</v>
+        <v>9.859490354846393</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>4.191212816486235</v>
+        <v>4.2499229324889</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>4.141255164273076</v>
+        <v>4.189266843263439</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-8.090519361866612</v>
+        <v>-8.041271799472845</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>-5.210325047801106</v>
+        <v>-5.137067938021453</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>-6.060243844131051</v>
+        <v>-5.960896518836435</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.3825920612146874</v>
+        <v>-0.2826840251960974</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.3482139088594494</v>
+        <v>-0.2245172878311621</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>-3.709541232761097</v>
+        <v>-3.56085168498322</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-6.424982053122797</v>
+        <v>-6.252983293556092</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X ≈ 0.007441</t>
+          <t>X ≈ 0.007434</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>27</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-2.397997290899198</v>
+        <v>-0.6582599730351575</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>10.55687521194633</v>
+        <v>8.869674052920153</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>6.458400123487579</v>
+        <v>8.475936064605449</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-4.49484626415677</v>
+        <v>-2.505291005290978</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-5.060775397130854</v>
+        <v>-2.994540146242898</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.004418504035336</v>
+        <v>-2.721754627424048</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>4.576985011767619</v>
+        <v>0.9212929870541871</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>15.22102747909199</v>
+        <v>11.56657133778199</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>11.45634161886547</v>
+        <v>7.825895024941538</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>3.199015415128301</v>
+        <v>-0.4053409632808567</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.994314256868051</v>
+        <v>-0.6094814108169118</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.028692409223432</v>
+        <v>-0.5513146734520546</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-1.095162147793673</v>
+        <v>-4.650176303719611</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>2.834277206136555</v>
+        <v>-0.6974277380005134</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X ≈ 0.00802</t>
+          <t>X ≈ 0.008012</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>22</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>6.609993060374777</v>
+        <v>2.035342720567527</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>4.998806967310912</v>
+        <v>4.997620180866221</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>9.149490128010413</v>
+        <v>4.603882192551517</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>4.734260726144235</v>
+        <v>0.18831168831165</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>13.28688026395761</v>
+        <v>8.789971638268824</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-13.68847297913455</v>
+        <v>-13.66451557018494</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>-0.1368197020370943</v>
+        <v>-0.0888080230467736</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.6038883458238331</v>
+        <v>-0.5546407834301448</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>3.880584043107945</v>
+        <v>3.953841152887605</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>3.030665246778085</v>
+        <v>3.130012572072658</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.825964088517892</v>
+        <v>2.925872124536568</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-1.685112304581338</v>
+        <v>-1.561415683553122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-2.105263157894747</v>
+        <v>-1.956573610116919</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-6.424982053122754</v>
+        <v>-6.252983293556127</v>
       </c>
     </row>
   </sheetData>
@@ -2210,417 +2210,417 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &gt; -0.008476</t>
+          <t>X &gt; -0.008472</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4093</v>
+        <v>4103</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-0.0454557285372772</v>
+        <v>-0.03197771409981698</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.2075324683628423</v>
+        <v>0.2201983317554621</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>0.1671225930112996</v>
+        <v>0.1799638648899062</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>0.1644337702582988</v>
+        <v>0.1529471015247807</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.2245160070541203</v>
+        <v>0.2362928268079472</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>0.1451817835619096</v>
+        <v>0.1576024723174356</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>0.07382331348397742</v>
+        <v>0.08593207870063679</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.01045218069040033</v>
+        <v>0.02280562025138977</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>0.03613664082745061</v>
+        <v>0.04793693052771886</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>0.0539860802038703</v>
+        <v>0.04105137500334877</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.009469060108798999</v>
+        <v>0.02103220070004852</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0.1552695358005067</v>
+        <v>0.1416072374966291</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>0.1641332981162762</v>
+        <v>0.1500186280542692</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>0.1105664443118854</v>
+        <v>0.09602962382143687</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &gt; -0.007897</t>
+          <t>X &gt; -0.007893</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4074</v>
+        <v>4085</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>0.00256818771864431</v>
+        <v>0.003309356176949052</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>0.2397627809539458</v>
+        <v>0.2391494594958488</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>0.2254887927483722</v>
+        <v>0.2248871641424586</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>0.1732243090843113</v>
+        <v>0.1727716727716668</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.2850767772165952</v>
+        <v>0.2830657449438121</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>0.2040039706672303</v>
+        <v>0.2028411141763868</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>0.1572258750273576</v>
+        <v>0.1555712535905656</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>0.07124534401575033</v>
+        <v>0.06978978477948772</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0.07283258887450472</v>
+        <v>0.07075602285874538</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0.07021226180327034</v>
+        <v>0.06747227548980561</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>0.05097356518299279</v>
+        <v>0.04827027433197628</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>0.1482358977560807</v>
+        <v>0.1446590100430143</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>0.1345583702703408</v>
+        <v>0.1303751728671116</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>0.05513576720125002</v>
+        <v>0.05056627804733438</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &gt; -0.007318</t>
+          <t>X &gt; -0.007315</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4049</v>
+        <v>4059</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-0.01907457312421457</v>
+        <v>-0.005200233531390097</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>0.30336697268352</v>
+        <v>0.3159471498933044</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>0.2914516147994846</v>
+        <v>0.3041278927972542</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0.1888061806896815</v>
+        <v>0.2017168135378995</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.3046677992414644</v>
+        <v>0.3158498898108277</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>0.270565271251975</v>
+        <v>0.2825528519265035</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>0.1993825572420889</v>
+        <v>0.2107939981489579</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0.165083742507079</v>
+        <v>0.1766574386430122</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>0.1670799842659463</v>
+        <v>0.1532863926872068</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>0.1203631136780245</v>
+        <v>0.1306614432605357</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>0.1269602295930099</v>
+        <v>0.1126587500233356</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>0.2246293978041649</v>
+        <v>0.2093080522038946</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>0.2381711855395992</v>
+        <v>0.2221097754630179</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>0.1321925578923171</v>
+        <v>0.1155803920807585</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &gt; -0.006739</t>
+          <t>X &gt; -0.006736</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4011</v>
+        <v>4022</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-0.02067746194588693</v>
+        <v>-0.01940550518437334</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>0.2205998401104949</v>
+        <v>0.2200477285293019</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>0.3365974016418107</v>
+        <v>0.3356857225202177</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>0.2317624783090082</v>
+        <v>0.2311507936507908</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>0.4035695448260128</v>
+        <v>0.4004450150533145</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>0.316593862458781</v>
+        <v>0.3147309897067743</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>0.2455505409603305</v>
+        <v>0.2428781612082958</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0.2153571336158251</v>
+        <v>0.2127149988213972</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>0.1432606095693671</v>
+        <v>0.1398131148715152</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>0.178859518260019</v>
+        <v>0.1742251900557648</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>0.1625587345295827</v>
+        <v>0.1579444000870964</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>0.2109980639935287</v>
+        <v>0.2052570075728752</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>0.2784946595619786</v>
+        <v>0.2715239199940456</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>0.09458912613428794</v>
+        <v>0.08714599535489498</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &gt; -0.00616</t>
+          <t>X &gt; -0.006158</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3978</v>
+        <v>3989</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>0.1625317269199229</v>
+        <v>0.1635513435288161</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>0.3439881019657207</v>
+        <v>0.3431019922315954</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>0.439173119874404</v>
+        <v>0.4379731016424628</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>0.3825692881940128</v>
+        <v>0.3815418140249278</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.5352100630774999</v>
+        <v>0.5312968463274288</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>0.445085384228129</v>
+        <v>0.442655717371629</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>0.3490933811156438</v>
+        <v>0.3457174114786596</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>0.272343855709579</v>
+        <v>0.2691161855083379</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>0.1750628507677661</v>
+        <v>0.1708940048929222</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>0.2180082904747138</v>
+        <v>0.2124067619048589</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>0.2032790619142517</v>
+        <v>0.1976884845292801</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>0.276970838406335</v>
+        <v>0.2699776787849046</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>0.3736602810689078</v>
+        <v>0.3651397642280401</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>0.1612421801603006</v>
+        <v>0.1521307701190153</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &gt; -0.005582</t>
+          <t>X &gt; -0.00558</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3928</v>
+        <v>3939</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>0.1706952356417517</v>
+        <v>0.1720744099308362</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>0.3241415312241571</v>
+        <v>0.3233144815036084</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>0.4763151182017396</v>
+        <v>0.4749984180981599</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>0.3919549871904451</v>
+        <v>0.3908946206996333</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.5533729787612387</v>
+        <v>0.5487447800207264</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>0.5345499329127392</v>
+        <v>0.5315366674178392</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>0.4892632366252627</v>
+        <v>0.4848453889239295</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>0.3412519231598594</v>
+        <v>0.3371670285297981</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0.2943787406554961</v>
+        <v>0.2888955508223603</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>0.3487083430510864</v>
+        <v>0.3414113685589513</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>0.2346734153142194</v>
+        <v>0.2276570975544132</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0.3088733535264652</v>
+        <v>0.3001330696475364</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>0.4121481658286186</v>
+        <v>0.4015251439209209</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>0.1941625497285671</v>
+        <v>0.1826602708003406</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &gt; -0.005003</t>
+          <t>X &gt; -0.005001</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3867</v>
+        <v>3878</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>0.09640355709451853</v>
+        <v>0.08628920339065616</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>0.2260211040378053</v>
+        <v>0.2137308893914636</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>0.3351997252723606</v>
+        <v>0.3226438835354628</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>0.2990132292511305</v>
+        <v>0.29820693709582</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4456193576812382</v>
+        <v>0.4404616165180286</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>0.4992103053229258</v>
+        <v>0.4958737060046445</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>0.4287221386725335</v>
+        <v>0.4236524894137474</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>0.2857203671776034</v>
+        <v>0.2809551345550929</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.2907080100500821</v>
+        <v>0.2839982479172534</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>0.359285993120352</v>
+        <v>0.3502832853881941</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>0.2208431113038927</v>
+        <v>0.2121853989972209</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>0.2698208470434693</v>
+        <v>0.2591091524356628</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>0.4071933618006582</v>
+        <v>0.3940790885636289</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>0.1822069823052317</v>
+        <v>0.1678521886512314</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &gt; -0.004424</t>
+          <t>X &gt; -0.004423</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3801</v>
+        <v>3811</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>0.08856482945515864</v>
+        <v>0.09255623684464354</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>0.2745383169997737</v>
+        <v>0.2499868618043593</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>0.3137560824127803</v>
+        <v>0.3153808483056295</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>0.3271616588509971</v>
+        <v>0.3405802519908718</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.3544059141604521</v>
+        <v>0.3630320856748526</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>0.4300024021394577</v>
+        <v>0.4407951965555199</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>0.438524071836099</v>
+        <v>0.4469317740864369</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>0.2223408491996892</v>
+        <v>0.231316774861746</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0.2284558245057298</v>
+        <v>0.2350494623978321</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>0.2341056959478394</v>
+        <v>0.2383171115698488</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>0.09677949813456621</v>
+        <v>0.1013500289080227</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>0.1985680434692512</v>
+        <v>0.2004992963005279</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>0.3456000241625503</v>
+        <v>0.3447714247013636</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>0.03384457144972686</v>
+        <v>0.03145648602932027</v>
       </c>
     </row>
     <row r="14">
@@ -2630,101 +2630,101 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3714</v>
+        <v>3725</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>0.02780411972054253</v>
+        <v>0.01865456526554254</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>0.282562395993871</v>
+        <v>0.2696661220770835</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>0.2782271627877222</v>
+        <v>0.2653158057923974</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0.3963054483393265</v>
+        <v>0.3951998470070777</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>0.4099237528351196</v>
+        <v>0.4026706692860387</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>0.5340857624999487</v>
+        <v>0.5295277291356086</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>0.4373172601675961</v>
+        <v>0.430046113170711</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>0.3614097968936676</v>
+        <v>0.3542064668805622</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.2615760008678407</v>
+        <v>0.2516720083592432</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>0.3948395340292876</v>
+        <v>0.3812863720190194</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>0.2591335555856631</v>
+        <v>0.2459072396360611</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>0.3356333652493788</v>
+        <v>0.3192097280623969</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>0.442149053043714</v>
+        <v>0.4222874643963337</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>0.1447540804259759</v>
+        <v>0.1228556326184034</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &gt; -0.003267</t>
+          <t>X &gt; -0.003266</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3622</v>
+        <v>3633</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>0.06378823356468644</v>
+        <v>0.05504592545595699</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>0.228206076732036</v>
+        <v>0.2151633402315838</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>0.2062176009228622</v>
+        <v>0.1931817209122926</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>0.3515014149708264</v>
+        <v>0.3505156660523099</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.3240100303630769</v>
+        <v>0.3156069036075806</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.4988548445569023</v>
+        <v>0.4936827269861652</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>0.3191035425331634</v>
+        <v>0.3107923765536356</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>0.2255192917425717</v>
+        <v>0.2172995598210292</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0.1246625452509633</v>
+        <v>0.1130695001313811</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>0.2000981304966842</v>
+        <v>0.1842780756095337</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>0.1212618941605257</v>
+        <v>0.1055900963337422</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>0.2539806113327714</v>
+        <v>0.2342576939634782</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>0.4566518798690424</v>
+        <v>0.432479274257922</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>0.06314605289602326</v>
+        <v>0.03658455670539951</v>
       </c>
     </row>
     <row r="16">
@@ -2734,49 +2734,49 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3510</v>
+        <v>3521</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>0.05953245087353309</v>
+        <v>0.05145058666127511</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>0.138448699797614</v>
+        <v>0.1252841363897801</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>0.1850946825016493</v>
+        <v>0.1717100033700163</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>0.2172152715987821</v>
+        <v>0.2166322773799365</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>0.2627773421564967</v>
+        <v>0.2527581435482773</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>0.433703877550542</v>
+        <v>0.4278103526878851</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>0.2224741175922418</v>
+        <v>0.2126762070088901</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>0.1123180871061606</v>
+        <v>0.1026265310529624</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>0.06705759800254896</v>
+        <v>0.05294907842777974</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>0.1435125588285828</v>
+        <v>0.1242098641422871</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>-0.0167241085682619</v>
+        <v>-0.0356385554758134</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>0.1475652684151498</v>
+        <v>0.1236151527692613</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>0.3415921798748727</v>
+        <v>0.3122818955358682</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>0.04225441411371378</v>
+        <v>0.009442153760005567</v>
       </c>
     </row>
     <row r="17">
@@ -2786,985 +2786,985 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3364</v>
+        <v>3376</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>0.05091695732469503</v>
+        <v>0.07329532007906181</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-0.004424398479692115</v>
+        <v>0.01184989680890425</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>0.3575709360912214</v>
+        <v>0.3135639435922428</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>0.3854974562191416</v>
+        <v>0.3548216923401526</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>0.3970869857860535</v>
+        <v>0.3545536283827602</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>0.3846425174684782</v>
+        <v>0.3480606800501818</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>0.1975833615264548</v>
+        <v>0.1691663407508273</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>0.07320903750500918</v>
+        <v>0.04478935473449752</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>-0.03074653785754577</v>
+        <v>-0.06460416990550755</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>0.0561457045625815</v>
+        <v>0.01543484211030233</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>0.07601133856513798</v>
+        <v>0.03502222273668565</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.03800118323803758</v>
+        <v>-0.008587221310776272</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>0.2586433664872629</v>
+        <v>0.2051083561253151</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.02567193023039493</v>
+        <v>-0.03260414663666467</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &gt; -0.00153</t>
+          <t>X &gt; -0.001531</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3211</v>
+        <v>3223</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>0.3416646146269358</v>
+        <v>0.3510078781751886</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>0.2671904609503741</v>
+        <v>0.2693348523334009</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>0.5100228293252371</v>
+        <v>0.5114255931311646</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>0.3779061214195565</v>
+        <v>0.3627581023124193</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>0.6019564920773419</v>
+        <v>0.602524410573956</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>0.3263255184225642</v>
+        <v>0.3040646263295983</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>-0.05206915115850563</v>
+        <v>-0.06628486642637199</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>-0.06696800784659729</v>
+        <v>-0.08150796828986273</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>-0.1730116149653256</v>
+        <v>-0.1943967263697672</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>0.05173127250973408</v>
+        <v>0.02174452270106997</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>0.05117198578552262</v>
+        <v>0.03459105594613732</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.10307771890281</v>
+        <v>0.07917628262027421</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>0.3853968670118562</v>
+        <v>0.3528105541059645</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>0.09946515958356628</v>
+        <v>0.06100988050534539</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &gt; -0.0009514</t>
+          <t>X &gt; -0.0009527</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3067</v>
+        <v>3076</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>0.2481288037736391</v>
+        <v>0.2442627700579223</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>0.3115377854040986</v>
+        <v>0.2989315113510074</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>0.3570796776025631</v>
+        <v>0.3443609096839708</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>0.4400996027148167</v>
+        <v>0.4093941078376915</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.6353158231934515</v>
+        <v>0.6190637268484522</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>0.5277208498155375</v>
+        <v>0.4880418010615841</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.005225752508366099</v>
+        <v>-0.02686477486082595</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>0.1095304398841108</v>
+        <v>0.07679529104394334</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>-0.1614651129477238</v>
+        <v>-0.2020030029565163</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>-0.0341852122091808</v>
+        <v>-0.06612548928139006</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>-0.05771137580273944</v>
+        <v>-0.07539747303053446</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>-0.005012743125838881</v>
+        <v>-0.03149660977436497</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>0.3896995065594453</v>
+        <v>0.3715500049745302</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>0.07974569386126262</v>
+        <v>0.05390877406419037</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &gt; -0.0003727</t>
+          <t>X &gt; -0.0003743</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2883</v>
+        <v>2890</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>0.3544919915956655</v>
+        <v>0.3701917280623093</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>0.3527266553710291</v>
+        <v>0.3580568456507436</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>0.4958254535844944</v>
+        <v>0.4663731706793968</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>0.4027839647609355</v>
+        <v>0.3891464076137794</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>0.368219976876297</v>
+        <v>0.3676963996952693</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>0.407631816658494</v>
+        <v>0.3486733134702575</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.03013046491308558</v>
+        <v>-0.02286360477074112</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>0.2059430705933778</v>
+        <v>0.1521506973765767</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>-0.2709836266572978</v>
+        <v>-0.3150838384708194</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.02294506401456431</v>
+        <v>0.001771991360584479</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>-0.02361351834127134</v>
+        <v>-0.02953748486543617</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>-0.004413537514203369</v>
+        <v>-0.02111642541150616</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>0.546646153744021</v>
+        <v>0.5370586655976908</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>0.04397389554183206</v>
+        <v>0.04459456111518278</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &gt; 0.0002061</t>
+          <t>X &gt; 0.000204</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1391</v>
+        <v>1397</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>-0.1511669265916922</v>
+        <v>-0.1563315110496077</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>-0.863981607098907</v>
+        <v>-0.8835884820827786</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>0.143420820433569</v>
+        <v>0.07788037696343508</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>0.489008490942247</v>
+        <v>0.4930711228856666</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>1.02753157244814</v>
+        <v>0.9708813780651013</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>0.2480929674816394</v>
+        <v>0.1406792350098627</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>-0.443768500365195</v>
+        <v>-0.4914054256441673</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>0.350297655091147</v>
+        <v>0.3284760996867746</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>-2.298750640899641</v>
+        <v>-2.279925080878591</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>-1.207619832628495</v>
+        <v>-1.17518223312215</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>-0.3339600994436793</v>
+        <v>-0.2364655378010951</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>-0.8028170297626929</v>
+        <v>-0.7101582919096998</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>0.3586280910432293</v>
+        <v>0.5079861505801873</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>0.2249101107881017</v>
+        <v>0.368348130924943</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &gt; 0.0007849</t>
+          <t>X &gt; 0.0007824</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1222</v>
+        <v>1225</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>0.7001606415700437</v>
+        <v>0.6606198824300904</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>-0.2145511031900185</v>
+        <v>-0.2721506986607238</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>0.7418846615814232</v>
+        <v>0.6349243211546565</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>0.5453124195488712</v>
+        <v>0.4396051103368137</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>0.7423169841002348</v>
+        <v>0.6458781402290583</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>0.3043968960882637</v>
+        <v>0.1495205565547693</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>0.1010454581502316</v>
+        <v>0.007431242573609609</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>0.9063035899000269</v>
+        <v>0.7630968535257736</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>-2.100668746655494</v>
+        <v>-2.205471846816238</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>-1.313926331856052</v>
+        <v>-1.400635932517218</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>-0.5366307634386658</v>
+        <v>-0.4647112334735013</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>-0.8295848533092069</v>
+        <v>-0.7686469201241692</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>0.1414263228372903</v>
+        <v>0.1863894626993456</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>0.1216627913944279</v>
+        <v>0.1551799717500302</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &gt; 0.001364</t>
+          <t>X &gt; 0.001361</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>0.1406282973970079</v>
+        <v>0.1064438363879958</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>0.2972108535010562</v>
+        <v>0.2359213658848489</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>1.196030025553185</v>
+        <v>1.079100599263768</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.0846123802208183</v>
+        <v>-0.02793258121517539</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>1.074498567335247</v>
+        <v>0.9631318114290295</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>0.894317678154664</v>
+        <v>0.7597268540574831</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>0.2890450641718445</v>
+        <v>0.1276421934034531</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1.118599692453685</v>
+        <v>0.9951427663534389</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>-1.90888964110259</v>
+        <v>-1.994210795164307</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>-0.9406266192506294</v>
+        <v>-1.008515566455486</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>-0.2840837583720557</v>
+        <v>-0.2602750616106277</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>-0.6324807256339611</v>
+        <v>-0.6254593615147783</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>0.5741626794258394</v>
+        <v>0.559040546718613</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>0.512816989939445</v>
+        <v>0.5760520455079003</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &gt; 0.001942</t>
+          <t>X &gt; 0.001939</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>0.51343425195153</v>
+        <v>0.3582796261816341</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>0.7721512700669848</v>
+        <v>0.5748775691472687</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>0.4905020572576433</v>
+        <v>0.2936255200901527</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>-0.3973723466653141</v>
+        <v>-0.5888638920135065</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>0.5349263355331146</v>
+        <v>0.4464007946980075</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>-0.07267701039741326</v>
+        <v>-0.1817145873839578</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>-0.6618891965290032</v>
+        <v>-0.8054337396724804</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.06607660985541486</v>
+        <v>-0.03252776131709112</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>-2.262479242812489</v>
+        <v>-2.321752622706136</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>-1.18496039741899</v>
+        <v>-1.231166789106709</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>-1.049525501257413</v>
+        <v>-0.9848567861923456</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>-0.5616326096730688</v>
+        <v>-0.5262614353210537</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>0.6055181243151182</v>
+        <v>0.6085813252411896</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>0.8312537745416506</v>
+        <v>0.8576261872565567</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &gt; 0.002521</t>
+          <t>X &gt; 0.002518</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>1.061318301890715</v>
+        <v>1.032122507538084</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>1.705987917329516</v>
+        <v>1.628781934643804</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>0.3562369964216714</v>
+        <v>0.2813654722146666</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>-0.3320917481209307</v>
+        <v>-0.4061891786687468</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>0.2210238829580078</v>
+        <v>0.1944799365101275</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>-0.8458585676251928</v>
+        <v>-0.8951323648344314</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>-1.403585722901468</v>
+        <v>-1.500747582125292</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>-0.5665795533850826</v>
+        <v>-0.7404223043614948</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>-2.816344199647936</v>
+        <v>-2.957231425759872</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>-1.751078317455224</v>
+        <v>-1.873703058345967</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>-1.40858385328039</v>
+        <v>-1.396644595800318</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>-0.9638089840987973</v>
+        <v>-0.9297585123863783</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.1208281242840883</v>
+        <v>0.114615773487202</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>0.6201615857281411</v>
+        <v>0.6365119315462238</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &gt; 0.0031</t>
+          <t>X &gt; 0.003096</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.427878757739265</v>
+        <v>1.398682963386634</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>2.188485152095133</v>
+        <v>2.095636171390389</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.978053082185113</v>
+        <v>0.8875659355186798</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>0.4557496776495</v>
+        <v>0.3659841786877607</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-0.4088041495081924</v>
+        <v>-0.4489978612869621</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>-0.9270908050280724</v>
+        <v>-0.9905445900250385</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>-0.9241043128511137</v>
+        <v>-1.051200679250499</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.006139923778917478</v>
+        <v>-0.2141018435426361</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>-1.69150344387316</v>
+        <v>-1.879738947793435</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>-1.068427150186658</v>
+        <v>-1.237769483005813</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>-0.1274654606563459</v>
+        <v>-0.1389783344506981</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>-0.09308730830102263</v>
+        <v>-0.08081159708580543</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>-0.02223979827563483</v>
+        <v>-0.05830874284715293</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>-0.1238363902749597</v>
+        <v>-0.1355281548937697</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &gt; 0.003679</t>
+          <t>X &gt; 0.003674</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.062391056079825</v>
+        <v>1.124465778256436</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>2.318154286658228</v>
+        <v>2.291779852236139</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.331666925571824</v>
+        <v>1.308650901249528</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>0.8701760928288351</v>
+        <v>0.8491439797923093</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>0.3318865397331408</v>
+        <v>0.3598948388403898</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.03754459303686275</v>
+        <v>0.04328939498741136</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>0.6536941319550067</v>
+        <v>0.5720242684338572</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1.28630067307806</v>
+        <v>1.088509779170359</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0.2352195066543032</v>
+        <v>0.06921889891371791</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>0.969459126166015</v>
+        <v>0.8170995518904789</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>2.348916383747408</v>
+        <v>2.381131992370101</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.987254932142335</v>
+        <v>2.046371421287063</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>1.567104078828926</v>
+        <v>1.568837986160823</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>1.792839729055459</v>
+        <v>1.81788284817619</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &gt; 0.004258</t>
+          <t>X &gt; 0.004253</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.6143220647037424</v>
+        <v>0.696539006466935</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>1.3840883525923</v>
+        <v>1.488658833425092</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>-0.4392544607341762</v>
+        <v>-0.3302573021580173</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>-0.07093407905057347</v>
+        <v>0.03715643026806958</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.1050620821394546</v>
+        <v>0.2604963629503416</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>-1.026135316796896</v>
+        <v>-0.8918962654991276</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>1.164981122436771</v>
+        <v>1.185214866178022</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>2.745393950826895</v>
+        <v>2.619619635485897</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0.7705361962179964</v>
+        <v>0.6824094966578826</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>1.356024098452721</v>
+        <v>1.283759063111312</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>2.108260739235597</v>
+        <v>2.029737380420826</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.66416999206939</v>
+        <v>1.61284473536292</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>1.004784688995208</v>
+        <v>0.9801571175876873</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>1.469754788982513</v>
+        <v>1.466731670814461</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &gt; 0.004836</t>
+          <t>X &gt; 0.004831</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>-0.4922796668979856</v>
+        <v>-0.385465932535709</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>-0.1148293963254545</v>
+        <v>0.0143598151696267</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.05858103710131957</v>
+        <v>0.1871940648152588</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>-0.09528472840122504</v>
+        <v>0.03379198704978137</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>1.070971173048541</v>
+        <v>1.244259559978879</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>-1.188472979134559</v>
+        <v>-1.032529992023726</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>0.5883810231636346</v>
+        <v>0.6065306326318307</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>2.279228537293058</v>
+        <v>2.123700705109677</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>-0.06746790494401012</v>
+        <v>-0.1795608558684734</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>-0.06024384413100137</v>
+        <v>-0.1535310797429545</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>1.449340711894514</v>
+        <v>1.342045186601986</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.483718864249838</v>
+        <v>1.400211923966879</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.2064251537935746</v>
+        <v>0.1551956404625372</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>1.003589375448676</v>
+        <v>0.970812740438241</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &gt; 0.005415</t>
+          <t>X &gt; 0.005409</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>-1.740175289793612</v>
+        <v>-1.769371084146243</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>-2.240250271746334</v>
+        <v>-2.241437058190989</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.3279413064615966</v>
+        <v>0.3277879164572752</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.08779607967958469</v>
+        <v>0.08730158730158166</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>0.6606176376950046</v>
+        <v>0.7091635574607764</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>-0.8938601845217562</v>
+        <v>-0.8699027755721431</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>1.451554748790898</v>
+        <v>1.291663357424611</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>2.686478004244009</v>
+        <v>2.307312078522749</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>0.7598242059301867</v>
+        <v>0.4184876175341046</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>1.029308394674963</v>
+        <v>0.7057701478302292</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>2.317144549847605</v>
+        <v>1.983111181775627</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.72465703056114</v>
+        <v>2.411648289510879</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>1.558237520531314</v>
+        <v>1.275749622206312</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>1.037704514041422</v>
+        <v>0.7840537434809463</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &gt; 0.005994</t>
+          <t>X &gt; 0.005988</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>-2.966352923738235</v>
+        <v>-2.995548718090866</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>-0.6940438711709973</v>
+        <v>-0.6952306576156531</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.3674954236856109</v>
+        <v>0.3673420336812896</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>0.9831574604778552</v>
+        <v>0.9826629680998522</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>2.87205237340158</v>
+        <v>2.920598293167352</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>1.71311572342502</v>
+        <v>1.737073132374633</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>3.85431111836202</v>
+        <v>3.618164615964702</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>2.899437596526504</v>
+        <v>2.666894962377476</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.3994310497598335</v>
+        <v>0.2027378872212608</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.5251220095275215</v>
+        <v>0.3497830928140502</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>2.271640363462453</v>
+        <v>2.087390218093489</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.818213637768999</v>
+        <v>1.660120062254499</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.4224530283580279</v>
+        <v>0.2940883492829087</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.1603838005357758</v>
+        <v>0.05769631809439346</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &gt; 0.006573</t>
+          <t>X &gt; 0.006566</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>-3.671392221010542</v>
+        <v>-3.700588015363174</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>0.6698026383065852</v>
+        <v>0.6686158518619294</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.2750312535515462</v>
+        <v>0.2748778635472249</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.4052563971399081</v>
+        <v>0.4047619047619051</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>1.652681129758491</v>
+        <v>1.701227049524263</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-0.4308972215588014</v>
+        <v>-0.4069398126091883</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>2.203953297418551</v>
+        <v>1.913356479117731</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2.335687048841386</v>
+        <v>2.042761813972483</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.4782977066898653</v>
+        <v>0.2200749191214086</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.2271813055695873</v>
+        <v>-0.008515566455479018</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>1.818887332938147</v>
+        <v>1.573058271722708</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.254463090083881</v>
+        <v>1.035986913849506</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.2355098415608978</v>
+        <v>0.04559089204758493</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>-0.1375569034221584</v>
+        <v>-0.3006023411751357</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &gt; 0.007152</t>
+          <t>X &gt; 0.007145</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>-4.71972200068361</v>
+        <v>-4.748917795036242</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.3855098167003277</v>
+        <v>0.3843230302556719</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-0.009261568054711233</v>
+        <v>-0.009414958059032585</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>-0.6253050811827663</v>
+        <v>-0.6257995735607693</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-0.4173259775620437</v>
+        <v>-0.3687800577962719</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>-1.612489261359798</v>
+        <v>-1.588531852410185</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>1.708703196117391</v>
+        <v>1.335886685230022</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>5.001033048571252</v>
+        <v>4.601397208428772</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>1.93253209505599</v>
+        <v>1.579349972426307</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>1.834492997974259</v>
+        <v>1.501790048327742</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>2.381671538962181</v>
+        <v>2.043918257508075</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.66416999206939</v>
+        <v>1.355816338156544</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>1.244019138755981</v>
+        <v>0.9606584115927177</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>1.469754788982513</v>
+        <v>1.209703273608085</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &gt; 0.00773</t>
+          <t>X &gt; 0.007723</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>-5.311104709779634</v>
+        <v>-5.781139862270159</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>-2.205309670767996</v>
+        <v>-1.756840311912001</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>-1.656684829107938</v>
+        <v>-2.150578300226705</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.3603327673106094</v>
+        <v>-0.1515353805073545</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.7654394406300113</v>
+        <v>0.2937949177930648</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>-1.767375208980184</v>
+        <v>-1.302578441892678</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.97810311099893</v>
+        <v>1.440503786638871</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>2.397826920042384</v>
+        <v>2.843829904760199</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>-0.4933439157256814</v>
+        <v>0.003118977866392925</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>1.486925967189748</v>
+        <v>1.98302871480842</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>2.225621035344645</v>
+        <v>2.713467706524668</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>1.316602961284879</v>
+        <v>1.837055004637222</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>1.839848334386559</v>
+        <v>2.376476517325735</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>1.122187758198002</v>
+        <v>1.690941940088763</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &gt; 0.008309</t>
+          <t>X &gt; 0.008301</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>-8.433296982915309</v>
+        <v>-7.804229471945803</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>-4.092102123598181</v>
+        <v>-3.505053615925192</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>-4.48687350835322</v>
+        <v>-3.898791604239896</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>-0.7852197933362888</v>
+        <v>-0.2394957983193322</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2.513985536908166</v>
+        <v>-1.905215527506542</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>1.35481706415549</v>
+        <v>1.896981756018263</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>1.270106704889322</v>
+        <v>1.836325666792803</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>3.183990442054963</v>
+        <v>3.723434082880054</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>-1.63889647637258</v>
+        <v>-1.019420879197924</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>1.08261329872613</v>
+        <v>1.686162304692971</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>2.068388330942135</v>
+        <v>2.658492445392184</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>2.102766483297458</v>
+        <v>2.716659182757077</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>2.873091820460239</v>
+        <v>3.497971844428541</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>3.098827470686771</v>
+        <v>3.747016706443908</v>
       </c>
     </row>
   </sheetData>
@@ -3904,417 +3904,417 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X &lt; -0.008476</t>
+          <t>X &lt; -0.008472</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>2.280988731370414</v>
+        <v>1.607535233936545</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>-8.85400688550294</v>
+        <v>-9.387406557101656</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>-6.867825889305607</v>
+        <v>-7.42820336894578</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>-6.737600745717245</v>
+        <v>-6.121848739495803</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-9.656842679765312</v>
+        <v>-10.1405096451536</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-5.788040078701655</v>
+        <v>-6.338312361628795</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>-2.301321866539247</v>
+        <v>-2.869556686148364</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>0.8030380611025834</v>
+        <v>0.19402231817417</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>-0.4484202858963826</v>
+        <v>-1.019420879197924</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>-1.298339082226242</v>
+        <v>-0.6667788717776091</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>0.8779121404659378</v>
+        <v>0.3055512689215902</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-5.518634934889988</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-5.913792861453814</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>-4.044029672170367</v>
+        <v>-3.311806822967853</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>X &lt; -0.007897</t>
+          <t>X &lt; -0.007893</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>103</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-0.05373156451493344</v>
+        <v>-0.08292735886756475</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>-8.46103416243313</v>
+        <v>-8.462220948877786</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>-7.884931760780404</v>
+        <v>-7.885085150784725</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>-5.812959044376505</v>
+        <v>-5.813453536754508</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-10.23474374310327</v>
+        <v>-10.18619782333749</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-7.024748354244885</v>
+        <v>-7.000790945295272</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>-5.167711140695516</v>
+        <v>-5.119699461705196</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>-1.751284638851189</v>
+        <v>-1.702037076457472</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-1.812266795373965</v>
+        <v>-1.739009685594269</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>-1.69131180529606</v>
+        <v>-1.591964480001486</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-0.9251391771484876</v>
+        <v>-0.8252311411298123</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>-4.774256170424231</v>
+        <v>-4.650559549395986</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>-4.223533237329868</v>
+        <v>-4.07484368955204</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>-1.085176227880041</v>
+        <v>-0.9131774683133784</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>X &lt; -0.007318</t>
+          <t>X &lt; -0.007315</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>0.6440839694656475</v>
+        <v>0.203066469686668</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>-8.779602123598181</v>
+        <v>-9.132048599965316</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>-8.39312350835322</v>
+        <v>-8.750592789830414</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-5.137898364764858</v>
+        <v>-5.519933554817285</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-8.801187917860553</v>
+        <v>-9.109957889567653</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-7.722563888225466</v>
+        <v>-8.061978572299111</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>-5.463524247491634</v>
+        <v>-5.797053266175737</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>-4.368092891278373</v>
+        <v>-4.712498429659853</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-4.429075047801149</v>
+        <v>-3.974277240347028</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>-2.935243844131008</v>
+        <v>-3.247718224262783</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-3.139945002391201</v>
+        <v>-2.676664873349274</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>-6.230566850035878</v>
+        <v>-5.71927332978283</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>-6.650717703349287</v>
+        <v>-6.114431256346656</v>
       </c>
       <c r="P8" s="4" t="n">
-        <v>-3.299982053122754</v>
+        <v>-2.76461120053284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X &lt; -0.006739</t>
+          <t>X &lt; -0.006736</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>166</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>0.5311321622367373</v>
+        <v>0.501936367884106</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>-4.694511762152402</v>
+        <v>-4.695698548597058</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>-7.498921701124303</v>
+        <v>-7.499075091128624</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>-4.959058003319079</v>
+        <v>-4.959552495697082</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-9.11180538774007</v>
+        <v>-9.063259467974298</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-7.007202442442335</v>
+        <v>-6.983245033492722</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>-5.284683886045855</v>
+        <v>-5.236672207055534</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>-4.546933252724159</v>
+        <v>-4.497685690330442</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>-2.800686493584287</v>
+        <v>-2.727429383804591</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>-3.650605289914147</v>
+        <v>-3.551257964619573</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-3.252896809620111</v>
+        <v>-3.152988773601436</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>-4.42333793437323</v>
+        <v>-4.299641313344985</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>-6.048308064795073</v>
+        <v>-5.899618517017245</v>
       </c>
       <c r="P9" s="4" t="n">
-        <v>-1.605704944689016</v>
+        <v>-1.433706185122354</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X &lt; -0.00616</t>
+          <t>X &lt; -0.006158</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>199</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-3.234684874755459</v>
+        <v>-3.26388066910809</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>-6.353408656261493</v>
+        <v>-6.354595442706149</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>-8.255717729458745</v>
+        <v>-8.255871119463066</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>-7.120467460242246</v>
+        <v>-7.120961952620249</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-10.17131982740829</v>
+        <v>-10.12277390764252</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-8.36640810933099</v>
+        <v>-8.342450700381377</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>-6.441068217340884</v>
+        <v>-6.393056538350564</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>-4.898086609871342</v>
+        <v>-4.848839047477625</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>-2.94901851513783</v>
+        <v>-2.875761405358134</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-3.798937311467689</v>
+        <v>-3.699589986173116</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-3.501125906913821</v>
+        <v>-3.401217870895145</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>-4.974285443000703</v>
+        <v>-4.850588821972458</v>
       </c>
       <c r="O10" s="4" t="n">
-        <v>-6.901973984756324</v>
+        <v>-6.753284436978497</v>
       </c>
       <c r="P10" s="4" t="n">
-        <v>-2.65613783201723</v>
+        <v>-2.484139072450567</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X &lt; -0.005582</t>
+          <t>X &lt; -0.00558</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>249</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-2.681719243385764</v>
+        <v>-2.710915037738395</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>-4.694511762152402</v>
+        <v>-4.695698548597058</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>-7.097315275421494</v>
+        <v>-7.097468665425815</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>-5.762270854724697</v>
+        <v>-5.7627653471027</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-8.308592536334444</v>
+        <v>-8.260046616568673</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-8.011218506699358</v>
+        <v>-7.987261097749744</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>-7.292716014559907</v>
+        <v>-7.244704335569587</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>-4.948539678426961</v>
+        <v>-4.899292116033244</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>-4.206308983544119</v>
+        <v>-4.133051873764423</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>-5.056227779873979</v>
+        <v>-4.956880454579405</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>-3.252896809620111</v>
+        <v>-3.152988773601436</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>-4.42333793437323</v>
+        <v>-4.299641313344985</v>
       </c>
       <c r="O11" s="4" t="n">
-        <v>-6.048308064795073</v>
+        <v>-5.899618517017245</v>
       </c>
       <c r="P11" s="4" t="n">
-        <v>-2.609721008946046</v>
+        <v>-2.437722249379384</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X &lt; -0.005003</t>
+          <t>X &lt; -0.005001</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>310</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1.190593449889185</v>
+        <v>-1.063166487266408</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>-2.479198897791733</v>
+        <v>-2.324800164062125</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>-3.841712218030636</v>
+        <v>-3.683168377457214</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-3.388906429280993</v>
+        <v>-3.389400921658996</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-5.217518563021841</v>
+        <v>-5.168972643256069</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-5.887886468870626</v>
+        <v>-5.863929059921013</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>-5.004854892652922</v>
+        <v>-4.956843213662601</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>-3.213859020310629</v>
+        <v>-3.164611457916912</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>-3.274841176833405</v>
+        <v>-3.201584067053709</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>-4.124759973163265</v>
+        <v>-4.025412647868691</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>-2.393977260455721</v>
+        <v>-2.294069224437045</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>-3.004760398422981</v>
+        <v>-2.881063777394736</v>
       </c>
       <c r="O12" s="4" t="n">
-        <v>-4.715233832381543</v>
+        <v>-4.566544284603715</v>
       </c>
       <c r="P12" s="4" t="n">
-        <v>-1.90885302086469</v>
+        <v>-1.736854261298028</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X &lt; -0.004424</t>
+          <t>X &lt; -0.004423</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-0.88517134968329</v>
+        <v>-0.9228102375853879</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>-2.496357442747119</v>
+        <v>-2.241437058190989</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>-2.891128827502158</v>
+        <v>-2.899725311055946</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>-3.026861130722303</v>
+        <v>-3.163508904888218</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-3.29919323700949</v>
+        <v>-3.387506056450221</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-4.065648994608438</v>
+        <v>-4.175728495190967</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>-4.150359353874606</v>
+        <v>-4.236384584416427</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>-1.957853529576248</v>
+        <v>-2.049697450900567</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>-2.018835686099024</v>
+        <v>-2.086670060037363</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>-2.070882142003349</v>
+        <v>-2.114742672682588</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-0.6798386194124788</v>
+        <v>-0.7273711838791499</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>-1.709290254291197</v>
+        <v>-1.730212404073953</v>
       </c>
       <c r="O13" s="4" t="n">
-        <v>-3.193270894838655</v>
+        <v>-3.186378288197453</v>
       </c>
       <c r="P13" s="4" t="n">
-        <v>-0.04200332971850429</v>
+        <v>-0.01956154289296563</v>
       </c>
     </row>
     <row r="14">
@@ -4327,98 +4327,98 @@
         <v>463</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-0.2130974560203143</v>
+        <v>-0.1394221697145781</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>-2.040266270466439</v>
+        <v>-1.938116496249734</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>-2.003072212456892</v>
+        <v>-1.900820001805819</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-2.952760675779977</v>
+        <v>-2.95325516815798</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-3.059084786111086</v>
+        <v>-3.010538866345314</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-4.057607084769742</v>
+        <v>-4.033649675820129</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>-3.278386558506753</v>
+        <v>-3.230374879516432</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>-2.665541595382045</v>
+        <v>-2.616294032988328</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>-1.862592866375657</v>
+        <v>-1.78933575659596</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>-2.928494384087813</v>
+        <v>-2.829147058793239</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-1.837299214054269</v>
+        <v>-1.737391178035594</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>-2.450869225845821</v>
+        <v>-2.327172604817576</v>
       </c>
       <c r="O14" s="4" t="n">
-        <v>-3.302985521923794</v>
+        <v>-3.154295974145967</v>
       </c>
       <c r="P14" s="4" t="n">
-        <v>-0.9174226578743685</v>
+        <v>-0.7454238983077062</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X &lt; -0.003267</t>
+          <t>X &lt; -0.003266</t>
         </is>
       </c>
       <c r="B15" t="n">
         <v>555</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-0.4088439584622776</v>
+        <v>-0.3518384435920225</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>-1.299309330805386</v>
+        <v>-1.215591068316215</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>-1.153540175019884</v>
+        <v>-1.069760711307183</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>-2.10439611251261</v>
+        <v>-2.104890604890613</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-1.921964944887577</v>
+        <v>-1.873419025121805</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-3.066032356693938</v>
+        <v>-3.042074947744325</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>-1.889481454698839</v>
+        <v>-1.841469775708518</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>-1.275469017404497</v>
+        <v>-1.22622145501078</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>-0.6157304532065595</v>
+        <v>-0.5424733434268632</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>-1.105288889176052</v>
+        <v>-1.005941563881478</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>-0.5892693267155309</v>
+        <v>-0.4893612906968556</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>-1.455792075261108</v>
+        <v>-1.332095454232864</v>
       </c>
       <c r="O15" s="4" t="n">
-        <v>-2.776843829475411</v>
+        <v>-2.628154281697583</v>
       </c>
       <c r="P15" s="4" t="n">
-        <v>-0.2087658369065366</v>
+        <v>-0.03676707733987428</v>
       </c>
     </row>
     <row r="16">
@@ -4431,46 +4431,46 @@
         <v>667</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-0.3070029870560944</v>
+        <v>-0.2646028428510547</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>-0.5688637427885936</v>
+        <v>-0.5004745387853546</v>
       </c>
       <c r="E16" s="4" t="n">
-        <v>-0.8137100900623579</v>
+        <v>-0.7445119282976549</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>-0.983335021436524</v>
+        <v>-0.983829513814527</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-1.22177449956969</v>
+        <v>-1.173228579803919</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2.123800769784694</v>
+        <v>-2.099843360835081</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>-1.009110829200772</v>
+        <v>-0.9610991502104511</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>-0.426704210618702</v>
+        <v>-0.3774566482249853</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>-0.1878362921789574</v>
+        <v>-0.114579182399261</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>-0.5879799760650428</v>
+        <v>-0.4886326507704695</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>0.2567941280435804</v>
+        <v>0.3567021640622556</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>-0.6083779444886446</v>
+        <v>-0.4846813234603999</v>
       </c>
       <c r="O16" s="4" t="n">
-        <v>-1.628228947727095</v>
+        <v>-1.479539399949267</v>
       </c>
       <c r="P16" s="4" t="n">
-        <v>-0.0531679601692332</v>
+        <v>0.1188307993974291</v>
       </c>
     </row>
     <row r="17">
@@ -4480,985 +4480,985 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-0.2053932753067969</v>
+        <v>-0.2988096135847726</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>0.1514403118261711</v>
+        <v>0.08361526686133658</v>
       </c>
       <c r="E17" s="4" t="n">
-        <v>-1.350342143039562</v>
+        <v>-1.170073581404225</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>-1.466119459475799</v>
+        <v>-1.343612721841502</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-1.512404092522303</v>
+        <v>-1.340856942744232</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-1.461032522911808</v>
+        <v>-1.314073883949902</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>-0.6847342720918803</v>
+        <v>-0.5702231596343239</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>-0.1677930757802173</v>
+        <v>-0.05083424514081969</v>
       </c>
       <c r="K17" s="4" t="n">
-        <v>0.263229687746211</v>
+        <v>0.4048039831608108</v>
       </c>
       <c r="L17" s="4" t="n">
-        <v>-0.09468418853445826</v>
+        <v>0.07358623978424816</v>
       </c>
       <c r="M17" s="4" t="n">
-        <v>-0.1763841167823514</v>
+        <v>-0.007401498392233918</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>-0.01900473441471462</v>
+        <v>0.1739179483322673</v>
       </c>
       <c r="O17" s="4" t="n">
-        <v>-0.931160507777328</v>
+        <v>-0.7138508156699785</v>
       </c>
       <c r="P17" s="4" t="n">
-        <v>0.03258252252300053</v>
+        <v>0.2741103025030185</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X &lt; -0.00153</t>
+          <t>X &lt; -0.001531</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="C18" s="4" t="n">
-        <v>-1.135160336952566</v>
+        <v>-1.167136618275407</v>
       </c>
       <c r="D18" s="4" t="n">
-        <v>-0.7794727240122583</v>
+        <v>-0.7875037860758951</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-1.58832278371554</v>
+        <v>-1.594464914886466</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>-1.147538633916</v>
+        <v>-1.099645442458268</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-1.892867524485808</v>
+        <v>-1.899132432427763</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-0.974375482428357</v>
+        <v>-0.9024585992344853</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>0.2866698518872468</v>
+        <v>0.3346815308775675</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>0.3371995517858082</v>
+        <v>0.3864471141795249</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>0.6902960702112679</v>
+        <v>0.7635531799909643</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>-0.05610305738152732</v>
+        <v>0.04324426791304603</v>
       </c>
       <c r="M18" s="4" t="n">
-        <v>-0.05376487816759834</v>
+        <v>0.0007661424357650048</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>-0.2264260632863966</v>
+        <v>-0.1483210062097058</v>
       </c>
       <c r="O18" s="4" t="n">
-        <v>-1.164175260285106</v>
+        <v>-1.06161364779944</v>
       </c>
       <c r="P18" s="4" t="n">
-        <v>-0.2138019288991515</v>
+        <v>-0.08718018474780109</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>X &lt; -0.0009514</t>
+          <t>X &lt; -0.0009527</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C19" s="4" t="n">
-        <v>-0.6823548794552181</v>
+        <v>-0.6715468024654641</v>
       </c>
       <c r="D19" s="4" t="n">
-        <v>-0.7647639941017772</v>
+        <v>-0.730060210491267</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>-0.8897512061949442</v>
+        <v>-0.8547399028418425</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>-1.119238292822409</v>
+        <v>-1.03577840471916</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-1.657527845918104</v>
+        <v>-1.614794152493339</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-1.360153816283017</v>
+        <v>-1.252242026852151</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>0.08391280286808467</v>
+        <v>0.1725658232327376</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>-0.2032997258107443</v>
+        <v>-0.1135724178334385</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>0.5450706356520882</v>
+        <v>0.6580803099569792</v>
       </c>
       <c r="L19" s="4" t="n">
-        <v>0.1953817184252458</v>
+        <v>0.2834880274349061</v>
       </c>
       <c r="M19" s="4" t="n">
-        <v>0.2607075628653206</v>
+        <v>0.3097831775123723</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.1150677134204727</v>
+        <v>0.1880937997693479</v>
       </c>
       <c r="O19" s="4" t="n">
-        <v>-0.9750420276736165</v>
+        <v>-0.9264885872261388</v>
       </c>
       <c r="P19" s="4" t="n">
-        <v>-0.118675746816443</v>
+        <v>-0.04794732233307286</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X &lt; -0.0003727</t>
+          <t>X &lt; -0.0003743</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1294</v>
+        <v>1298</v>
       </c>
       <c r="C20" s="4" t="n">
-        <v>-0.7860007762970653</v>
+        <v>-0.8204036835659423</v>
       </c>
       <c r="D20" s="4" t="n">
-        <v>-0.7022716151235997</v>
+        <v>-0.7138726274007468</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>-1.02000139741331</v>
+        <v>-0.954000784686265</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>-0.8127346513596265</v>
+        <v>-0.7829691446140359</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-0.7346913847326633</v>
+        <v>-0.7341706299164557</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-0.8225253674242339</v>
+        <v>-0.6919769635187407</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>0.01726350289357015</v>
+        <v>0.1349682007294604</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>-0.3727635384278329</v>
+        <v>-0.2539414827308093</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>0.6879016291456566</v>
+        <v>0.7860089850554672</v>
       </c>
       <c r="L20" s="4" t="n">
-        <v>0.03543516821466852</v>
+        <v>0.08221356584409278</v>
       </c>
       <c r="M20" s="4" t="n">
-        <v>0.139375985263122</v>
+        <v>0.1523744357846439</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.09659364379128021</v>
+        <v>0.1334995706842008</v>
       </c>
       <c r="O20" s="4" t="n">
-        <v>-1.129482182113762</v>
+        <v>-1.109115982998262</v>
       </c>
       <c r="P20" s="4" t="n">
-        <v>-0.01076257862506935</v>
+        <v>-0.01261349386425792</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>X &lt; 0.0002061</t>
+          <t>X &lt; 0.000204</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>2786</v>
+        <v>2791</v>
       </c>
       <c r="C21" s="4" t="n">
-        <v>0.07722350434936942</v>
+        <v>0.08009896468072242</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>0.4696152288168491</v>
+        <v>0.4814073015368621</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>-0.03249068187737691</v>
+        <v>-7.659446050922725e-05</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>-0.2048946067118891</v>
+        <v>-0.208358880032705</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-0.4731692103775558</v>
+        <v>-0.4472503671934973</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>-0.08466990541744934</v>
+        <v>-0.03140333192249045</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>0.2604191622504857</v>
+        <v>0.2852365370443053</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>-0.1350162437138991</v>
+        <v>-0.1251490153556603</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>1.185232100174488</v>
+        <v>1.182301915182983</v>
       </c>
       <c r="L21" s="4" t="n">
-        <v>0.6422651164424664</v>
+        <v>0.6293613608197219</v>
       </c>
       <c r="M21" s="4" t="n">
-        <v>0.206908708616325</v>
+        <v>0.1588612779843359</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.4408822173959805</v>
+        <v>0.3961752743961569</v>
       </c>
       <c r="O21" s="4" t="n">
-        <v>-0.1383388013040729</v>
+        <v>-0.2139593630239816</v>
       </c>
       <c r="P21" s="4" t="n">
-        <v>-0.07178750897343633</v>
+        <v>-0.1440617600555569</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>X &lt; 0.0007849</t>
+          <t>X &lt; 0.0007824</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2955</v>
+        <v>2963</v>
       </c>
       <c r="C22" s="4" t="n">
-        <v>-0.2879335743940032</v>
+        <v>-0.2718082234059978</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>0.1251718305178855</v>
+        <v>0.1491353323814124</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>-0.2695995542371534</v>
+        <v>-0.2263330620490152</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>-0.1885754656761023</v>
+        <v>-0.1455525606469052</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-0.2696847105681854</v>
+        <v>-0.230489033135207</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>-0.0889519328050028</v>
+        <v>-0.02508895906021991</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>-0.004800421081640138</v>
+        <v>0.03375226129309539</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>-0.33677956807675</v>
+        <v>-0.2787871697477726</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>0.9045398170637142</v>
+        <v>0.9506217753006325</v>
       </c>
       <c r="L22" s="4" t="n">
-        <v>0.5805131683732228</v>
+        <v>0.6180508495846126</v>
       </c>
       <c r="M22" s="4" t="n">
-        <v>0.2597338346608637</v>
+        <v>0.2305080893142772</v>
       </c>
       <c r="N22" s="4" t="n">
-        <v>0.3808636538532042</v>
+        <v>0.3561739829397226</v>
       </c>
       <c r="O22" s="4" t="n">
-        <v>-0.02013583596092161</v>
+        <v>-0.03898394362410329</v>
       </c>
       <c r="P22" s="4" t="n">
-        <v>-0.01212249305506674</v>
+        <v>-0.02618612852065638</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>X &lt; 0.001364</t>
+          <t>X &lt; 0.001361</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3132</v>
+        <v>3141</v>
       </c>
       <c r="C23" s="4" t="n">
-        <v>-0.04538594457446976</v>
+        <v>-0.03392134869650931</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>-0.0647223082527475</v>
+        <v>-0.04438449594312033</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>-0.3639827092446524</v>
+        <v>-0.3256545984846042</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>0.006408960075908965</v>
+        <v>0.04387398429342682</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-0.3234183256337246</v>
+        <v>-0.2864936822384081</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>-0.2635932062624349</v>
+        <v>-0.2188703063578572</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>-0.06149668216339421</v>
+        <v>-0.007871471521980311</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>-0.3373607370400009</v>
+        <v>-0.2972963466963634</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>0.6710903171972618</v>
+        <v>0.7013030451156794</v>
       </c>
       <c r="L23" s="4" t="n">
-        <v>0.3491949313791949</v>
+        <v>0.3726489935760426</v>
       </c>
       <c r="M23" s="4" t="n">
-        <v>0.1305892878799284</v>
+        <v>0.122769464700383</v>
       </c>
       <c r="N23" s="4" t="n">
-        <v>0.2467783956565199</v>
+        <v>0.2446101912406888</v>
       </c>
       <c r="O23" s="4" t="n">
-        <v>-0.1553458552803448</v>
+        <v>-0.150547735323137</v>
       </c>
       <c r="P23" s="4" t="n">
-        <v>-0.1350714528673223</v>
+        <v>-0.1561988300094441</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>X &lt; 0.001942</t>
+          <t>X &lt; 0.001939</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3295</v>
+        <v>3302</v>
       </c>
       <c r="C24" s="4" t="n">
-        <v>-0.1359841092030365</v>
+        <v>-0.09465288768891611</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>-0.173796526018748</v>
+        <v>-0.1216791244795559</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>-0.09825365363166583</v>
+        <v>-0.04593928506449174</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>0.1392644417746567</v>
+        <v>0.1910590165349859</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-0.1099591171337195</v>
+        <v>-0.08664585122261315</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>0.05254214025075044</v>
+        <v>0.08177441552463449</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>0.2101825837716262</v>
+        <v>0.2493177157442261</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>0.01575859312029593</v>
+        <v>0.042070430340992</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>0.6381598006836953</v>
+        <v>0.6571831966230235</v>
       </c>
       <c r="L24" s="4" t="n">
-        <v>0.350789802428551</v>
+        <v>0.364769340727733</v>
       </c>
       <c r="M24" s="4" t="n">
-        <v>0.3148002977907254</v>
+        <v>0.2987838026253584</v>
       </c>
       <c r="N24" s="4" t="n">
-        <v>0.184355806924998</v>
+        <v>0.1752974973017842</v>
       </c>
       <c r="O24" s="4" t="n">
-        <v>-0.1276594509221027</v>
+        <v>-0.1290339079178082</v>
       </c>
       <c r="P24" s="4" t="n">
-        <v>-0.1882597465977227</v>
+        <v>-0.1960481027626386</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>X &lt; 0.002521</t>
+          <t>X &lt; 0.002518</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3446</v>
+        <v>3455</v>
       </c>
       <c r="C25" s="4" t="n">
-        <v>-0.2239715860899096</v>
+        <v>-0.2170630795740323</v>
       </c>
       <c r="D25" s="4" t="n">
-        <v>-0.3305280495241121</v>
+        <v>-0.3137159152361448</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>-0.044037039467554</v>
+        <v>-0.02815243948307966</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>0.1019503613497932</v>
+        <v>0.1174529858132587</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-0.01512326393643093</v>
+        <v>-0.009545333353223384</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>0.2112426007664254</v>
+        <v>0.2213097541152464</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>0.3293132380240138</v>
+        <v>0.3498460706203304</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>0.1519317321283395</v>
+        <v>0.1889220121557997</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0.6285622312484023</v>
+        <v>0.6594050310447486</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>0.4035242718110155</v>
+        <v>0.4300809247725894</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>0.3311698134974677</v>
+        <v>0.3290330365201584</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0.2369505513562302</v>
+        <v>0.229935326547924</v>
       </c>
       <c r="O25" s="4" t="n">
-        <v>0.007245743125913862</v>
+        <v>0.008388511095205331</v>
       </c>
       <c r="P25" s="4" t="n">
-        <v>-0.09880677744079946</v>
+        <v>-0.1024767812550778</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>X &lt; 0.0031</t>
+          <t>X &lt; 0.003096</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3566</v>
+        <v>3575</v>
       </c>
       <c r="C26" s="4" t="n">
-        <v>-0.2437795652099695</v>
+        <v>-0.2380181532951298</v>
       </c>
       <c r="D26" s="4" t="n">
-        <v>-0.3448985441798342</v>
+        <v>-0.3286486423350823</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>-0.1372231587028736</v>
+        <v>-0.1216154618163969</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>-0.04775077103234793</v>
+        <v>-0.0323660714285694</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>0.1008639293266924</v>
+        <v>0.1075572064823902</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>0.1896701543277217</v>
+        <v>0.2002628674578233</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>0.1889463572116199</v>
+        <v>0.210752790336997</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>0.02982844130841045</v>
+        <v>0.06750243647847043</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0.3203386318404071</v>
+        <v>0.3532924978544898</v>
       </c>
       <c r="L26" s="4" t="n">
-        <v>0.2142659597905592</v>
+        <v>0.2436870474016857</v>
       </c>
       <c r="M26" s="4" t="n">
-        <v>0.05335143918907193</v>
+        <v>0.05525937134064662</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.04746005579371371</v>
+        <v>0.04525505063443092</v>
       </c>
       <c r="O26" s="4" t="n">
-        <v>0.03557329749175153</v>
+        <v>0.0415960055023632</v>
       </c>
       <c r="P26" s="4" t="n">
-        <v>0.0528642732933946</v>
+        <v>0.05470901413621476</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>X &lt; 0.003679</t>
+          <t>X &lt; 0.003674</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3672</v>
+        <v>3680</v>
       </c>
       <c r="C27" s="4" t="n">
-        <v>-0.1452289039727077</v>
+        <v>-0.1536654543561085</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>-0.2898207547768905</v>
+        <v>-0.2867324212864091</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>-0.153811840328224</v>
+        <v>-0.1509835379239348</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>-0.09034401693877214</v>
+        <v>-0.0876931417728386</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-0.01589469959471757</v>
+        <v>-0.01992778985182753</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>0.02451332765272696</v>
+        <v>0.02362704391372716</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>-0.06019703161344125</v>
+        <v>-0.04934667050891051</v>
       </c>
       <c r="J27" s="4" t="n">
-        <v>-0.1466240223278561</v>
+        <v>-0.1204481104314681</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>-0.002275007007028762</v>
+        <v>0.02036962983957125</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>-0.1026812761223113</v>
+        <v>-0.08253648625430543</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>-0.2921558867449434</v>
+        <v>-0.2986599973339565</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>-0.2425428979400692</v>
+        <v>-0.2524828342779486</v>
       </c>
       <c r="O27" s="4" t="n">
-        <v>-0.1846137011712372</v>
+        <v>-0.1858097366635576</v>
       </c>
       <c r="P27" s="4" t="n">
-        <v>-0.2158317263253693</v>
+        <v>-0.2203745979039198</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>X &lt; 0.004258</t>
+          <t>X &lt; 0.004253</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>3759</v>
+        <v>3767</v>
       </c>
       <c r="C28" s="4" t="n">
-        <v>-0.06712292708607492</v>
+        <v>-0.07624939102455386</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>-0.1255327417992902</v>
+        <v>-0.1372158748483443</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.07788233028797009</v>
+        <v>0.06564647379703814</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>0.03676814704824949</v>
+        <v>0.02464162789817692</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>0.01743595362112416</v>
+        <v>6.306989959625753e-06</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>0.1434719683482371</v>
+        <v>0.1283802756910362</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>-0.1006009407187278</v>
+        <v>-0.1032609786761896</v>
       </c>
       <c r="J28" s="4" t="n">
-        <v>-0.2755049098706692</v>
+        <v>-0.2630955939257404</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>-0.05623365566511751</v>
+        <v>-0.04693008012112898</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>-0.1208337989542869</v>
+        <v>-0.1136411489080302</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>-0.2043389417851458</v>
+        <v>-0.1968672050993163</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>-0.1550550180762897</v>
+        <v>-0.1503830971424165</v>
       </c>
       <c r="O28" s="4" t="n">
-        <v>-0.08156876717907835</v>
+        <v>-0.07952284771582896</v>
       </c>
       <c r="P28" s="4" t="n">
-        <v>-0.1334151470307035</v>
+        <v>-0.1340557650187932</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>X &lt; 0.004836</t>
+          <t>X &lt; 0.004831</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3827</v>
+        <v>3835</v>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.04644196842343717</v>
+        <v>0.03666572189056438</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>0.03872925508308356</v>
+        <v>0.02680466936969594</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.02303264388869763</v>
+        <v>0.01115302883954428</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>0.03709348660411393</v>
+        <v>0.02517183726545369</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-0.06969013486629194</v>
+        <v>-0.08572602514993832</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>0.1376304765019043</v>
+        <v>0.1232449388870407</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>-0.02534755821430679</v>
+        <v>-0.02728703492505247</v>
       </c>
       <c r="J29" s="4" t="n">
-        <v>-0.1793455002008884</v>
+        <v>-0.1664842900926686</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>0.0349776661863288</v>
+        <v>0.04522372864521884</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>0.03477051243385887</v>
+        <v>0.04327123318231685</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>-0.1030651068298383</v>
+        <v>-0.09416672145329841</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>-0.1062524076227191</v>
+        <v>-0.09957286127242071</v>
       </c>
       <c r="O29" s="4" t="n">
-        <v>0.01072430292030191</v>
+        <v>0.01517726674344999</v>
       </c>
       <c r="P29" s="4" t="n">
-        <v>-0.06229587596048702</v>
+        <v>-0.06002371076599644</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>X &lt; 0.005415</t>
+          <t>X &lt; 0.005409</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3909</v>
+        <v>3918</v>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.1211247857921833</v>
+        <v>0.1228060077255861</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>0.1819473788259103</v>
+        <v>0.1815202502625084</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.005214291544682226</v>
+        <v>0.005210312128582473</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>0.02170241389227812</v>
+        <v>0.02167588012801502</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-0.01751197301887686</v>
+        <v>-0.0208254078223149</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>0.0895370057719731</v>
+        <v>0.08762632765232325</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>-0.07180170598460478</v>
+        <v>-0.06101416085800082</v>
       </c>
       <c r="J30" s="4" t="n">
-        <v>-0.1557285873192455</v>
+        <v>-0.1306763686400032</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>-0.02381508357018447</v>
+        <v>-0.0006927149778661601</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>-0.04184363968429494</v>
+        <v>-0.02005001195219336</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>-0.1299756772378302</v>
+        <v>-0.1079086827714022</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>-0.157951150726241</v>
+        <v>-0.1374824739055924</v>
       </c>
       <c r="O30" s="4" t="n">
-        <v>-0.0778276777738327</v>
+        <v>-0.05905801012618639</v>
       </c>
       <c r="P30" s="4" t="n">
-        <v>-0.04227547855124669</v>
+        <v>-0.02531611642490361</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>X &lt; 0.005994</t>
+          <t>X &lt; 0.005988</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3972</v>
+        <v>3982</v>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.154626138140344</v>
+        <v>0.155720465475973</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>0.06305730396897502</v>
+        <v>0.06294544148445169</v>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.008355020024481519</v>
+        <v>0.008339993703565085</v>
       </c>
       <c r="F31" s="4" t="n">
-        <v>-0.02356622459907243</v>
+        <v>-0.02347552247352525</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-0.1210685711268766</v>
+        <v>-0.1232649622641588</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-0.06124823102516785</v>
+        <v>-0.06232828378713151</v>
       </c>
       <c r="I31" s="4" t="n">
-        <v>-0.1710905329905046</v>
+        <v>-0.1594568527830944</v>
       </c>
       <c r="J31" s="4" t="n">
-        <v>-0.1216908048027534</v>
+        <v>-0.110125419155473</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>0.007175580813388649</v>
+        <v>0.01718337875808373</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>0.001124365124525184</v>
+        <v>0.01000162466581855</v>
       </c>
       <c r="M31" s="4" t="n">
-        <v>-0.08884437346038965</v>
+        <v>-0.07971701656072838</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>-0.06549387570271392</v>
+        <v>-0.05767344185904477</v>
       </c>
       <c r="O31" s="4" t="n">
-        <v>0.006720001156125477</v>
+        <v>0.01316140003988409</v>
       </c>
       <c r="P31" s="4" t="n">
-        <v>0.02013375755197444</v>
+        <v>0.02526884104963045</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>X &lt; 0.006573</t>
+          <t>X &lt; 0.006566</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.1545886934835465</v>
+        <v>0.1553977213565076</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>-0.001079989800622627</v>
+        <v>-0.001027005280931803</v>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.01561405383583292</v>
+        <v>0.01557791434402134</v>
       </c>
       <c r="F32" s="4" t="n">
-        <v>0.01010953521025471</v>
+        <v>0.01010280042537914</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-0.04177714135482802</v>
+        <v>-0.04371143219754003</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>0.04520434677578322</v>
+        <v>0.04406978686118634</v>
       </c>
       <c r="I32" s="4" t="n">
-        <v>-0.06440021214186942</v>
+        <v>-0.05268819551894666</v>
       </c>
       <c r="J32" s="4" t="n">
-        <v>-0.06966161637797796</v>
+        <v>-0.05786979485584709</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>0.007607704378180813</v>
+        <v>0.01821156508413679</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>0.01848062024367891</v>
+        <v>0.0281690875253986</v>
       </c>
       <c r="M32" s="4" t="n">
-        <v>-0.04765120722548488</v>
+        <v>-0.03776875856740247</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>-0.02418599260816023</v>
+        <v>-0.01537346123040351</v>
       </c>
       <c r="O32" s="4" t="n">
-        <v>0.0184421071717793</v>
+        <v>0.02619865367996255</v>
       </c>
       <c r="P32" s="4" t="n">
-        <v>0.03387081470766873</v>
+        <v>0.04054904475236754</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>X &lt; 0.007152</t>
+          <t>X &lt; 0.007145</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4044</v>
+        <v>4054</v>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.15715103060964</v>
+        <v>0.1577022887102615</v>
       </c>
       <c r="D33" s="4" t="n">
-        <v>0.01393979995299333</v>
+        <v>0.01394178351348074</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.02718667911594963</v>
+        <v>0.02711824309388078</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>0.04749671295535052</v>
+        <v>0.0473847019122573</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>0.04089623811181298</v>
+        <v>0.03916054928399859</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>0.0802934309549812</v>
+        <v>0.07927387522931895</v>
       </c>
       <c r="I33" s="4" t="n">
-        <v>-0.0291021912092404</v>
+        <v>-0.01717318165079007</v>
       </c>
       <c r="J33" s="4" t="n">
-        <v>-0.1369972122660315</v>
+        <v>-0.1247258707565777</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>-0.03620798185894358</v>
+        <v>-0.02497136251025012</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>-0.03257585994128931</v>
+        <v>-0.02201036802323131</v>
       </c>
       <c r="M33" s="4" t="n">
-        <v>-0.05046514076530428</v>
+        <v>-0.03982128976419119</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>-0.02690891627413805</v>
+        <v>-0.0171266392640419</v>
       </c>
       <c r="O33" s="4" t="n">
-        <v>-0.01289322868921516</v>
+        <v>-0.003877724005498351</v>
       </c>
       <c r="P33" s="4" t="n">
-        <v>-0.02043210257873795</v>
+        <v>-0.01223341689107116</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>X &lt; 0.00773</t>
+          <t>X &lt; 0.007723</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4071</v>
+        <v>4081</v>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.1390643808270582</v>
+        <v>0.1523210036425766</v>
       </c>
       <c r="D34" s="4" t="n">
-        <v>0.08374896628670569</v>
+        <v>0.07235975841550868</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.06971639855515832</v>
+        <v>0.08286557476073142</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>0.01727959406876778</v>
+        <v>0.0305374166288388</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>0.007022866453176846</v>
+        <v>0.01913367427685841</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>0.07269843097041928</v>
+        <v>0.06077845591612885</v>
       </c>
       <c r="I34" s="4" t="n">
-        <v>0.0013942174421544</v>
+        <v>-0.01097489726843293</v>
       </c>
       <c r="J34" s="4" t="n">
-        <v>-0.03528843947557903</v>
+        <v>-0.04748950554235165</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>0.0399202907660765</v>
+        <v>0.02690660921300747</v>
       </c>
       <c r="L34" s="4" t="n">
-        <v>-0.01116408952977821</v>
+        <v>-0.02454400965650194</v>
       </c>
       <c r="M34" s="4" t="n">
-        <v>-0.03028619041280223</v>
+        <v>-0.04358740711689535</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>-0.006653272820067002</v>
+        <v>-0.02065910973259122</v>
       </c>
       <c r="O34" s="4" t="n">
-        <v>-0.02006937329034741</v>
+        <v>-0.03461022318536777</v>
       </c>
       <c r="P34" s="4" t="n">
-        <v>-0.00149887945535454</v>
+        <v>-0.01676667998098225</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>X &lt; 0.008309</t>
+          <t>X &lt; 0.008301</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>4093</v>
+        <v>4103</v>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.1737356986424601</v>
+        <v>0.1623857455697717</v>
       </c>
       <c r="D35" s="4" t="n">
-        <v>0.110090324635685</v>
+        <v>0.09869164888790749</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.1183896495415127</v>
+        <v>0.1070421342141614</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>0.04257171810133542</v>
+        <v>0.03138133444478797</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>0.07824589491369949</v>
+        <v>0.0660593637729292</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>-0.0011239955163731</v>
+        <v>-0.01267239997641667</v>
       </c>
       <c r="I35" s="4" t="n">
-        <v>0.0006525817766629416</v>
+        <v>-0.01139152227259643</v>
       </c>
       <c r="J35" s="4" t="n">
-        <v>-0.03834020769701851</v>
+        <v>-0.05020484458189856</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>0.06053878821641945</v>
+        <v>0.04793693052771886</v>
       </c>
       <c r="L35" s="4" t="n">
-        <v>0.005169873223152877</v>
+        <v>-0.007645970991291051</v>
       </c>
       <c r="M35" s="4" t="n">
-        <v>-0.014945002391201</v>
+        <v>-0.02767700533988204</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>-0.0156706351396636</v>
+        <v>-0.02891651402590156</v>
       </c>
       <c r="O35" s="4" t="n">
-        <v>-0.03127461590424474</v>
+        <v>-0.0449131458248786</v>
       </c>
       <c r="P35" s="4" t="n">
-        <v>-0.03602529768664198</v>
+        <v>-0.05020483876690918</v>
       </c>
     </row>
   </sheetData>
